--- a/Coleccion de minerales.xlsx
+++ b/Coleccion de minerales.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pascual\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Colección Minerales\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B0D9AF9-33F8-4D0F-A027-51D18613CF87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9196FD7-52B0-4B57-A21C-DC262723D6F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1265" uniqueCount="540">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1265" uniqueCount="541">
   <si>
     <t>Mineral</t>
   </si>
@@ -1756,6 +1756,9 @@
   </si>
   <si>
     <t>Matriz de roca con incrustaciones de Libethenita que aparecen como pequeños cristales verdes más oscuros y vítreos. Agregados botroidales (en forma de racimo de uvas) de Malaquita. Los nódulos presentan un color verde oscuro profundo y un brillo sedoso a aterciopelado. Conjunto bien equilibrado sobre matriz, con un crecimiento natural muy estético.</t>
+  </si>
+  <si>
+    <t>Taouz, Er Rachidia Province, Drâa-Tafilalet Region.</t>
   </si>
 </sst>
 </file>
@@ -5892,7 +5895,7 @@
         <v>375</v>
       </c>
       <c r="P56" t="s">
-        <v>333</v>
+        <v>540</v>
       </c>
       <c r="Q56" t="s">
         <v>21</v>

--- a/Coleccion de minerales.xlsx
+++ b/Coleccion de minerales.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Colección Minerales\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9196FD7-52B0-4B57-A21C-DC262723D6F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0128076E-E918-40A2-B6EC-9F7251B90666}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1265" uniqueCount="541">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1268" uniqueCount="542">
   <si>
     <t>Mineral</t>
   </si>
@@ -1760,12 +1760,36 @@
   <si>
     <t>Taouz, Er Rachidia Province, Drâa-Tafilalet Region.</t>
   </si>
+  <si>
+    <r>
+      <t>FeO(OH)·nH</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <color rgb="FF202122"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202122"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>O</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1791,6 +1815,19 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Roboto"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF202122"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <vertAlign val="subscript"/>
+      <sz val="11"/>
+      <color rgb="FF202122"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -3188,7 +3225,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:26" ht="18.75" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>283</v>
       </c>
@@ -3198,11 +3235,20 @@
       <c r="C16" t="s">
         <v>433</v>
       </c>
+      <c r="E16" t="s">
+        <v>541</v>
+      </c>
       <c r="F16" t="s">
         <v>420</v>
       </c>
+      <c r="G16" t="s">
+        <v>400</v>
+      </c>
       <c r="I16" t="s">
         <v>421</v>
+      </c>
+      <c r="K16" t="s">
+        <v>388</v>
       </c>
       <c r="L16" t="s">
         <v>351</v>

--- a/Coleccion de minerales.xlsx
+++ b/Coleccion de minerales.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Colección Minerales\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0128076E-E918-40A2-B6EC-9F7251B90666}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD2DECC1-2C90-4E30-9F54-A646B05D3B19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1268" uniqueCount="542">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1328" uniqueCount="563">
   <si>
     <t>Mineral</t>
   </si>
@@ -599,17 +599,7 @@
     <t>Adquirido en Feria de Minerales de Cártama 2023</t>
   </si>
   <si>
-    <t>La Araña, Málaga, Andalucía.</t>
-  </si>
-  <si>
     <t>100x88x66</t>
-  </si>
-  <si>
-    <t>Morfología muy atractiva (rosetas bien definidas)
-Excelente tridimensionalidad
-Tamaño ideal de vitrina
-Yacimiento clásico español
-Buena conservación de caras cristalinas</t>
   </si>
   <si>
     <t>150x90x85</t>
@@ -777,13 +767,6 @@
     <t>20x33.5x19</t>
   </si>
   <si>
-    <t>Hidroxiapofilita-(K) (atribución probable)
-Apofilitas bien cristalizadas, hábito cúbico limpio
-Buen contraste cromático: blanco lechoso + estilbita crema
-Brillo satinado agradable, sin aspecto apagado
-Composición estética y compacta (no “desparramada”)</t>
-  </si>
-  <si>
     <t>Goethita</t>
   </si>
   <si>
@@ -845,10 +828,6 @@
   </si>
   <si>
     <t>Adquirido en tienda "PIETRA" Granada en 2024</t>
-  </si>
-  <si>
-    <t>_x000D_
-Tounfite, Midelt, Draa-Tafilalet</t>
   </si>
   <si>
     <t>106x75x37.5</t>
@@ -1249,9 +1228,6 @@
   </si>
   <si>
     <t>Vítreo–sedoso</t>
-  </si>
-  <si>
-    <t>Escalenoédrico</t>
   </si>
   <si>
     <t>CaSO₄·2H₂O</t>
@@ -1783,6 +1759,84 @@
       </rPr>
       <t>O</t>
     </r>
+  </si>
+  <si>
+    <t>Tounfite, Midelt, Draa-Tafilalet</t>
+  </si>
+  <si>
+    <t>Compuesto por múltiples cristales puntiagudos que irradian desde varios centros, formando agregados esféricos y densamente compactos ("dientes de perro"). Yacimiento clásico español. Buena conservación de caras cristalinas. Yacimiento clásico español. Buena conservación de caras cristalinas.</t>
+  </si>
+  <si>
+    <t>Hidroxiapofilita-(K) (atribución probable). Apofilitas bien cristalizadas, hábito cúbico limpio. Buen contraste cromático: blanco lechoso + estilbita crema. Brillo satinado agradable, sin aspecto apagado. Composición estética y compacta.</t>
+  </si>
+  <si>
+    <t>Cantera Torre de las Palomas, La Araña, Málaga, Andalucía.</t>
+  </si>
+  <si>
+    <t>Mango</t>
+  </si>
+  <si>
+    <t>Halloysita</t>
+  </si>
+  <si>
+    <t>85x80x40</t>
+  </si>
+  <si>
+    <t>M-069</t>
+  </si>
+  <si>
+    <t>M-070</t>
+  </si>
+  <si>
+    <t>M-071</t>
+  </si>
+  <si>
+    <t>Mina Moscona, El Llano (Solís), Corvera, Asturias, Principado de Asturias.</t>
+  </si>
+  <si>
+    <t>74x90x55</t>
+  </si>
+  <si>
+    <t>Esfalerita</t>
+  </si>
+  <si>
+    <t>Marmatita</t>
+  </si>
+  <si>
+    <t>Borieva Mine, Madan, Rhodope Mountains , Smolyan Oblast.</t>
+  </si>
+  <si>
+    <t>40x46x28</t>
+  </si>
+  <si>
+    <t>Incoloro a translúcido con zonaciones amarillo-mango</t>
+  </si>
+  <si>
+    <t>Amarillo miel a ámbar intenso (fluorita); blanco translúcido (calcita)</t>
+  </si>
+  <si>
+    <t>Ejemplar compuesto por una matriz tapizada de cristales cúbicos de fluorita en tonalidades amarillo dorado a ámbar, con variaciones de saturación que aportan profundidad cromática. Sobre la fluorita se desarrollan cristales blancos de calcita, de hábito escalenoédrico y aspecto translúcido, generando un contraste cromático y morfológico atractivo.</t>
+  </si>
+  <si>
+    <t>ZnS</t>
+  </si>
+  <si>
+    <t>Tetraédrico, dodecaédrico, cúbico deformado</t>
+  </si>
+  <si>
+    <t>Negro a pardo muy oscuro con brillo resinoso(esfalerita); incoloro a translúcido (cuarzo)</t>
+  </si>
+  <si>
+    <t>Resinoso a submetálico (esfalerita); vítreo (cuarzo)</t>
+  </si>
+  <si>
+    <t>Opaca (esfalerita), transparente (cuarzo)</t>
+  </si>
+  <si>
+    <t>Agregado tridimensional de cristales bien desarrollados de esfalerita de hábito predominantemente tetraédrico, con caras brillantes y aristas definidas. El color oscuro, casi negro, muestra matices pardo-rojizos bajo iluminación intensa. Entre y sobre la esfalerita crecen cristales prismáticos de cuarzo, aportando contraste cromático y estructural.</t>
+  </si>
+  <si>
+    <t>Ejemplar compuesto por un agregado compacto de cristales prismáticos de cuarzo con desarrollo tridimensional y múltiples terminaciones definidas. Presenta inclusiones y recubrimientos internos de halloysita, responsables de la tonalidad amarillo-mango. Las inclusiones se distribuyen en formas fibrosas y masas microgranulares, generando contrastes cromáticos cálidos frente a la transparencia del cuarzo huésped.</t>
   </si>
 </sst>
 </file>
@@ -2208,7 +2262,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z69"/>
+  <dimension ref="A1:Z72"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
@@ -2229,7 +2283,7 @@
     <col min="19" max="19" width="24.5703125" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="17.140625" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="44.140625" customWidth="1"/>
+    <col min="22" max="22" width="52.42578125" customWidth="1"/>
     <col min="23" max="23" width="57.5703125" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="17.42578125" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="14.140625" bestFit="1" customWidth="1"/>
@@ -2237,7 +2291,7 @@
   <sheetData>
     <row r="1" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>0</v>
@@ -2249,37 +2303,37 @@
         <v>2</v>
       </c>
       <c r="E1" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="I1" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>340</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>341</v>
       </c>
-      <c r="H1" s="3" t="s">
-        <v>342</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>343</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>345</v>
-      </c>
       <c r="L1" s="3" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="P1" s="3" t="s">
         <v>3</v>
@@ -2288,16 +2342,16 @@
         <v>4</v>
       </c>
       <c r="R1" s="3" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="S1" s="3" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="T1" s="3" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="U1" s="3" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="V1" s="3" t="s">
         <v>5</v>
@@ -2306,10 +2360,10 @@
         <v>6</v>
       </c>
       <c r="X1" s="3" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="Y1" s="3" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="Z1" s="3" t="s">
         <v>7</v>
@@ -2317,34 +2371,34 @@
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="B2" t="s">
         <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="E2" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="F2" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="G2" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="H2" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="I2" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="J2" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="M2" t="s">
         <v>11</v>
@@ -2359,10 +2413,10 @@
         <v>10</v>
       </c>
       <c r="R2" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="S2" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="V2" t="s">
         <v>12</v>
@@ -2382,34 +2436,34 @@
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="B3" t="s">
         <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="E3" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="F3" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="G3" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="H3" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="I3" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="J3" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="L3" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="M3" t="s">
         <v>18</v>
@@ -2424,10 +2478,10 @@
         <v>17</v>
       </c>
       <c r="R3" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="S3" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="V3" t="s">
         <v>19</v>
@@ -2444,34 +2498,34 @@
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="B4" t="s">
         <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="E4" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="F4" t="s">
+        <v>387</v>
+      </c>
+      <c r="G4" t="s">
+        <v>390</v>
+      </c>
+      <c r="H4" t="s">
+        <v>389</v>
+      </c>
+      <c r="I4" t="s">
         <v>392</v>
       </c>
-      <c r="G4" t="s">
-        <v>395</v>
-      </c>
-      <c r="H4" t="s">
-        <v>394</v>
-      </c>
-      <c r="I4" t="s">
-        <v>397</v>
-      </c>
       <c r="K4" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="L4" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="M4" t="s">
         <v>22</v>
@@ -2486,10 +2540,10 @@
         <v>21</v>
       </c>
       <c r="R4" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="S4" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="V4" t="s">
         <v>23</v>
@@ -2509,37 +2563,37 @@
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="E5" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="F5" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="G5" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="H5" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="I5" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="J5" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="K5" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="L5" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="M5" t="s">
         <v>27</v>
@@ -2554,10 +2608,10 @@
         <v>17</v>
       </c>
       <c r="R5" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="S5" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="V5" t="s">
         <v>28</v>
@@ -2574,7 +2628,7 @@
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
@@ -2583,22 +2637,22 @@
         <v>29</v>
       </c>
       <c r="E6" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="F6" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="G6" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="H6" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="K6" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="L6" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="M6" t="s">
         <v>31</v>
@@ -2613,10 +2667,10 @@
         <v>17</v>
       </c>
       <c r="R6" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="S6" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="V6" t="s">
         <v>32</v>
@@ -2633,7 +2687,7 @@
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="B7" t="s">
         <v>33</v>
@@ -2642,28 +2696,28 @@
         <v>34</v>
       </c>
       <c r="E7" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="F7" t="s">
+        <v>352</v>
+      </c>
+      <c r="G7" t="s">
+        <v>398</v>
+      </c>
+      <c r="H7" t="s">
+        <v>399</v>
+      </c>
+      <c r="I7" t="s">
+        <v>400</v>
+      </c>
+      <c r="J7" t="s">
         <v>356</v>
       </c>
-      <c r="G7" t="s">
-        <v>403</v>
-      </c>
-      <c r="H7" t="s">
-        <v>404</v>
-      </c>
-      <c r="I7" t="s">
-        <v>405</v>
-      </c>
-      <c r="J7" t="s">
-        <v>360</v>
-      </c>
       <c r="K7" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="L7" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="M7" t="s">
         <v>36</v>
@@ -2678,10 +2732,10 @@
         <v>17</v>
       </c>
       <c r="R7" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="S7" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="V7" t="s">
         <v>37</v>
@@ -2701,37 +2755,37 @@
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="B8" t="s">
         <v>33</v>
       </c>
       <c r="C8" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="E8" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="F8" t="s">
+        <v>352</v>
+      </c>
+      <c r="G8" t="s">
+        <v>398</v>
+      </c>
+      <c r="H8" t="s">
+        <v>399</v>
+      </c>
+      <c r="I8" t="s">
+        <v>400</v>
+      </c>
+      <c r="J8" t="s">
         <v>356</v>
       </c>
-      <c r="G8" t="s">
-        <v>403</v>
-      </c>
-      <c r="H8" t="s">
-        <v>404</v>
-      </c>
-      <c r="I8" t="s">
-        <v>405</v>
-      </c>
-      <c r="J8" t="s">
-        <v>360</v>
-      </c>
       <c r="K8" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="L8" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="M8" t="s">
         <v>39</v>
@@ -2740,16 +2794,16 @@
         <v>572</v>
       </c>
       <c r="P8" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="Q8" t="s">
         <v>38</v>
       </c>
       <c r="R8" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="S8" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="V8" t="s">
         <v>40</v>
@@ -2769,37 +2823,37 @@
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="B9" t="s">
         <v>41</v>
       </c>
       <c r="C9" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="E9" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="F9" t="s">
+        <v>352</v>
+      </c>
+      <c r="G9" t="s">
+        <v>398</v>
+      </c>
+      <c r="H9" t="s">
+        <v>486</v>
+      </c>
+      <c r="I9" t="s">
+        <v>400</v>
+      </c>
+      <c r="J9" t="s">
         <v>356</v>
       </c>
-      <c r="G9" t="s">
-        <v>403</v>
-      </c>
-      <c r="H9" t="s">
-        <v>491</v>
-      </c>
-      <c r="I9" t="s">
-        <v>405</v>
-      </c>
-      <c r="J9" t="s">
-        <v>360</v>
-      </c>
       <c r="K9" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="L9" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="M9" t="s">
         <v>43</v>
@@ -2808,16 +2862,16 @@
         <v>81</v>
       </c>
       <c r="P9" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="Q9" t="s">
         <v>42</v>
       </c>
       <c r="R9" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="S9" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="V9" t="s">
         <v>44</v>
@@ -2837,31 +2891,31 @@
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="B10" t="s">
         <v>45</v>
       </c>
       <c r="C10" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="E10" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="F10" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="G10" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="I10" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="J10" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="L10" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="M10" t="s">
         <v>47</v>
@@ -2876,10 +2930,10 @@
         <v>17</v>
       </c>
       <c r="R10" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="S10" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="V10" t="s">
         <v>48</v>
@@ -2896,7 +2950,7 @@
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="B11" t="s">
         <v>49</v>
@@ -2905,22 +2959,22 @@
         <v>50</v>
       </c>
       <c r="E11" t="s">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="G11" t="s">
+        <v>402</v>
+      </c>
+      <c r="H11" t="s">
+        <v>487</v>
+      </c>
+      <c r="I11" t="s">
+        <v>406</v>
+      </c>
+      <c r="J11" t="s">
         <v>407</v>
       </c>
-      <c r="H11" t="s">
-        <v>492</v>
-      </c>
-      <c r="I11" t="s">
-        <v>411</v>
-      </c>
-      <c r="J11" t="s">
-        <v>412</v>
-      </c>
       <c r="L11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="M11" t="s">
         <v>52</v>
@@ -2929,16 +2983,16 @@
         <v>204</v>
       </c>
       <c r="P11" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="Q11" t="s">
         <v>51</v>
       </c>
       <c r="R11" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="S11" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="V11" t="s">
         <v>53</v>
@@ -2958,7 +3012,7 @@
     </row>
     <row r="12" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="B12" t="s">
         <v>54</v>
@@ -2967,28 +3021,28 @@
         <v>55</v>
       </c>
       <c r="E12" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="F12" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="G12" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="H12" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="I12" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="J12" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="K12" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="L12" s="4" t="s">
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="M12" t="s">
         <v>56</v>
@@ -2997,16 +3051,16 @@
         <v>500</v>
       </c>
       <c r="P12" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="Q12" t="s">
         <v>38</v>
       </c>
       <c r="R12" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="S12" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="V12" t="s">
         <v>57</v>
@@ -3026,34 +3080,34 @@
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="B13" t="s">
         <v>58</v>
       </c>
       <c r="C13" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="D13" t="s">
         <v>59</v>
       </c>
       <c r="E13" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="F13" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="G13" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="H13" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="I13" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="L13" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="M13" t="s">
         <v>60</v>
@@ -3062,16 +3116,16 @@
         <v>550</v>
       </c>
       <c r="P13" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="Q13" t="s">
         <v>21</v>
       </c>
       <c r="R13" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="S13" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="V13" t="s">
         <v>61</v>
@@ -3091,7 +3145,7 @@
     </row>
     <row r="14" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="B14" t="s">
         <v>54</v>
@@ -3100,28 +3154,28 @@
         <v>62</v>
       </c>
       <c r="E14" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="F14" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="G14" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="H14" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="I14" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="J14" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="K14" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="L14" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="M14" t="s">
         <v>64</v>
@@ -3136,13 +3190,13 @@
         <v>10</v>
       </c>
       <c r="R14" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="S14" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="V14" s="5" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="W14" t="s">
         <v>13</v>
@@ -3159,37 +3213,37 @@
     </row>
     <row r="15" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="B15" t="s">
         <v>66</v>
       </c>
       <c r="C15" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="D15" t="s">
         <v>67</v>
       </c>
       <c r="E15" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="F15" t="s">
+        <v>409</v>
+      </c>
+      <c r="G15" t="s">
+        <v>390</v>
+      </c>
+      <c r="H15" t="s">
+        <v>412</v>
+      </c>
+      <c r="I15" t="s">
+        <v>413</v>
+      </c>
+      <c r="J15" t="s">
         <v>414</v>
       </c>
-      <c r="G15" t="s">
-        <v>395</v>
-      </c>
-      <c r="H15" t="s">
-        <v>417</v>
-      </c>
-      <c r="I15" t="s">
-        <v>418</v>
-      </c>
-      <c r="J15" t="s">
-        <v>419</v>
-      </c>
       <c r="L15" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="M15" t="s">
         <v>68</v>
@@ -3198,16 +3252,16 @@
         <v>207</v>
       </c>
       <c r="P15" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="Q15" t="s">
         <v>38</v>
       </c>
       <c r="R15" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="S15" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="V15" t="s">
         <v>69</v>
@@ -3227,31 +3281,31 @@
     </row>
     <row r="16" spans="1:26" ht="18.75" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="B16" t="s">
         <v>70</v>
       </c>
       <c r="C16" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="E16" t="s">
-        <v>541</v>
+        <v>536</v>
       </c>
       <c r="F16" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="G16" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="I16" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="K16" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="L16" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="M16" t="s">
         <v>72</v>
@@ -3266,10 +3320,10 @@
         <v>17</v>
       </c>
       <c r="R16" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="S16" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="V16" t="s">
         <v>73</v>
@@ -3289,34 +3343,34 @@
     </row>
     <row r="17" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="B17" t="s">
         <v>74</v>
       </c>
       <c r="C17" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="E17" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="F17" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="G17" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="H17" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="I17" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="J17" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="L17" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="M17" t="s">
         <v>76</v>
@@ -3334,10 +3388,10 @@
         <v>21</v>
       </c>
       <c r="R17" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="S17" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="V17" t="s">
         <v>78</v>
@@ -3357,7 +3411,7 @@
     </row>
     <row r="18" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="B18" t="s">
         <v>79</v>
@@ -3366,25 +3420,25 @@
         <v>80</v>
       </c>
       <c r="E18" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="F18" t="s">
+        <v>352</v>
+      </c>
+      <c r="G18" t="s">
+        <v>419</v>
+      </c>
+      <c r="H18" t="s">
+        <v>420</v>
+      </c>
+      <c r="I18" t="s">
+        <v>421</v>
+      </c>
+      <c r="J18" t="s">
         <v>356</v>
       </c>
-      <c r="G18" t="s">
-        <v>424</v>
-      </c>
-      <c r="H18" t="s">
-        <v>425</v>
-      </c>
-      <c r="I18" t="s">
-        <v>426</v>
-      </c>
-      <c r="J18" t="s">
-        <v>360</v>
-      </c>
       <c r="L18" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="M18" t="s">
         <v>82</v>
@@ -3399,10 +3453,10 @@
         <v>42</v>
       </c>
       <c r="R18" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="S18" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="V18" t="s">
         <v>83</v>
@@ -3422,7 +3476,7 @@
     </row>
     <row r="19" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="B19" t="s">
         <v>84</v>
@@ -3434,25 +3488,25 @@
         <v>86</v>
       </c>
       <c r="E19" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="F19" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="G19" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="H19" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="I19" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="J19" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="L19" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="M19" t="s">
         <v>89</v>
@@ -3467,10 +3521,10 @@
         <v>88</v>
       </c>
       <c r="R19" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="S19" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="V19" t="s">
         <v>90</v>
@@ -3490,7 +3544,7 @@
     </row>
     <row r="20" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="B20" t="s">
         <v>92</v>
@@ -3499,22 +3553,22 @@
         <v>93</v>
       </c>
       <c r="E20" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="F20" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="G20" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="H20" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="J20" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="L20" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="M20" t="s">
         <v>95</v>
@@ -3529,10 +3583,10 @@
         <v>17</v>
       </c>
       <c r="R20" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="S20" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="V20" t="s">
         <v>96</v>
@@ -3552,7 +3606,7 @@
     </row>
     <row r="21" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="B21" t="s">
         <v>67</v>
@@ -3561,25 +3615,25 @@
         <v>97</v>
       </c>
       <c r="E21" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="F21" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="G21" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="H21" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="I21" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="J21" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="L21" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="M21" t="s">
         <v>99</v>
@@ -3588,16 +3642,16 @@
         <v>414</v>
       </c>
       <c r="P21" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="Q21" t="s">
         <v>98</v>
       </c>
       <c r="R21" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="S21" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="V21" t="s">
         <v>100</v>
@@ -3617,7 +3671,7 @@
     </row>
     <row r="22" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="B22" t="s">
         <v>67</v>
@@ -3626,25 +3680,25 @@
         <v>101</v>
       </c>
       <c r="E22" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="F22" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="G22" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="H22" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="I22" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="J22" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="L22" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="M22" t="s">
         <v>103</v>
@@ -3659,10 +3713,10 @@
         <v>51</v>
       </c>
       <c r="R22" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="S22" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="V22" t="s">
         <v>104</v>
@@ -3682,7 +3736,7 @@
     </row>
     <row r="23" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="B23" t="s">
         <v>67</v>
@@ -3691,25 +3745,25 @@
         <v>105</v>
       </c>
       <c r="E23" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="F23" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="G23" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="H23" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="I23" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="J23" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="L23" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="M23" t="s">
         <v>106</v>
@@ -3724,10 +3778,10 @@
         <v>51</v>
       </c>
       <c r="R23" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="S23" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="V23" t="s">
         <v>107</v>
@@ -3747,37 +3801,37 @@
     </row>
     <row r="24" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="B24" t="s">
         <v>108</v>
       </c>
       <c r="C24" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="D24" t="s">
         <v>67</v>
       </c>
       <c r="E24" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="F24" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="G24" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="H24" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="I24" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="J24" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="L24" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="M24" t="s">
         <v>111</v>
@@ -3795,10 +3849,10 @@
         <v>110</v>
       </c>
       <c r="R24" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="S24" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="V24" t="s">
         <v>113</v>
@@ -3818,37 +3872,37 @@
     </row>
     <row r="25" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="B25" t="s">
         <v>115</v>
       </c>
       <c r="C25" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="E25" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="F25" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="G25" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="H25" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="I25" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="J25" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="K25" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="L25" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="M25" t="s">
         <v>118</v>
@@ -3863,10 +3917,10 @@
         <v>117</v>
       </c>
       <c r="R25" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="S25" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="V25" t="s">
         <v>119</v>
@@ -3886,7 +3940,7 @@
     </row>
     <row r="26" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="B26" t="s">
         <v>120</v>
@@ -3895,28 +3949,28 @@
         <v>121</v>
       </c>
       <c r="E26" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="F26" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="G26" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="H26" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="I26" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="J26" t="s">
+        <v>350</v>
+      </c>
+      <c r="K26" t="s">
         <v>354</v>
       </c>
-      <c r="K26" t="s">
-        <v>358</v>
-      </c>
       <c r="L26" s="4" t="s">
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="M26" t="s">
         <v>123</v>
@@ -3931,10 +3985,10 @@
         <v>17</v>
       </c>
       <c r="R26" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="S26" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="V26" t="s">
         <v>124</v>
@@ -3954,7 +4008,7 @@
     </row>
     <row r="27" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="B27" t="s">
         <v>120</v>
@@ -3963,28 +4017,28 @@
         <v>125</v>
       </c>
       <c r="E27" t="s">
+        <v>443</v>
+      </c>
+      <c r="F27" t="s">
+        <v>352</v>
+      </c>
+      <c r="G27" t="s">
+        <v>444</v>
+      </c>
+      <c r="H27" t="s">
+        <v>474</v>
+      </c>
+      <c r="I27" t="s">
+        <v>447</v>
+      </c>
+      <c r="J27" t="s">
+        <v>350</v>
+      </c>
+      <c r="K27" t="s">
         <v>448</v>
       </c>
-      <c r="F27" t="s">
-        <v>356</v>
-      </c>
-      <c r="G27" t="s">
-        <v>449</v>
-      </c>
-      <c r="H27" t="s">
-        <v>479</v>
-      </c>
-      <c r="I27" t="s">
-        <v>452</v>
-      </c>
-      <c r="J27" t="s">
-        <v>354</v>
-      </c>
-      <c r="K27" t="s">
-        <v>453</v>
-      </c>
       <c r="L27" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="M27" t="s">
         <v>126</v>
@@ -3999,10 +4053,10 @@
         <v>17</v>
       </c>
       <c r="R27" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="S27" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="V27" t="s">
         <v>127</v>
@@ -4019,7 +4073,7 @@
     </row>
     <row r="28" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="B28" t="s">
         <v>67</v>
@@ -4031,25 +4085,25 @@
         <v>129</v>
       </c>
       <c r="E28" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="F28" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="G28" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="H28" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="I28" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="J28" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="L28" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="M28" t="s">
         <v>131</v>
@@ -4064,10 +4118,10 @@
         <v>38</v>
       </c>
       <c r="R28" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="S28" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="V28" t="s">
         <v>132</v>
@@ -4087,7 +4141,7 @@
     </row>
     <row r="29" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="B29" t="s">
         <v>67</v>
@@ -4096,25 +4150,25 @@
         <v>133</v>
       </c>
       <c r="E29" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="F29" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="G29" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="H29" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="I29" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="J29" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="L29" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="M29" t="s">
         <v>136</v>
@@ -4129,10 +4183,10 @@
         <v>135</v>
       </c>
       <c r="R29" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="S29" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="V29" t="s">
         <v>137</v>
@@ -4152,34 +4206,34 @@
     </row>
     <row r="30" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="B30" t="s">
         <v>59</v>
       </c>
       <c r="C30" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="E30" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="F30" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="G30" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="H30" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="I30" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="J30" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="L30" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="M30" t="s">
         <v>138</v>
@@ -4188,16 +4242,16 @@
         <v>160</v>
       </c>
       <c r="P30" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="Q30" t="s">
         <v>21</v>
       </c>
       <c r="R30" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="S30" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="V30" t="s">
         <v>139</v>
@@ -4217,7 +4271,7 @@
     </row>
     <row r="31" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="B31" t="s">
         <v>67</v>
@@ -4226,25 +4280,25 @@
         <v>128</v>
       </c>
       <c r="E31" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="F31" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="G31" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="H31" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="J31" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="K31" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="L31" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="M31" t="s">
         <v>140</v>
@@ -4253,16 +4307,16 @@
         <v>125</v>
       </c>
       <c r="P31" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="Q31" t="s">
         <v>17</v>
       </c>
       <c r="R31" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="S31" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="V31" t="s">
         <v>141</v>
@@ -4279,7 +4333,7 @@
     </row>
     <row r="32" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="B32" t="s">
         <v>33</v>
@@ -4288,28 +4342,28 @@
         <v>34</v>
       </c>
       <c r="E32" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="F32" t="s">
+        <v>352</v>
+      </c>
+      <c r="G32" t="s">
+        <v>398</v>
+      </c>
+      <c r="H32" t="s">
+        <v>399</v>
+      </c>
+      <c r="I32" t="s">
+        <v>400</v>
+      </c>
+      <c r="J32" t="s">
         <v>356</v>
       </c>
-      <c r="G32" t="s">
-        <v>403</v>
-      </c>
-      <c r="H32" t="s">
-        <v>404</v>
-      </c>
-      <c r="I32" t="s">
-        <v>405</v>
-      </c>
-      <c r="J32" t="s">
-        <v>360</v>
-      </c>
       <c r="K32" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="L32" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="M32" t="s">
         <v>142</v>
@@ -4324,10 +4378,10 @@
         <v>17</v>
       </c>
       <c r="R32" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="S32" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="V32" t="s">
         <v>143</v>
@@ -4344,7 +4398,7 @@
     </row>
     <row r="33" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="B33" t="s">
         <v>92</v>
@@ -4353,25 +4407,25 @@
         <v>93</v>
       </c>
       <c r="E33" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="F33" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="G33" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="H33" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="J33" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="K33" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="L33" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="M33" t="s">
         <v>144</v>
@@ -4386,10 +4440,10 @@
         <v>17</v>
       </c>
       <c r="R33" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="S33" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="V33" t="s">
         <v>145</v>
@@ -4409,7 +4463,7 @@
     </row>
     <row r="34" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="B34" t="s">
         <v>120</v>
@@ -4418,28 +4472,28 @@
         <v>125</v>
       </c>
       <c r="E34" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="F34" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="G34" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="H34" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="I34" t="s">
+        <v>349</v>
+      </c>
+      <c r="J34" t="s">
+        <v>350</v>
+      </c>
+      <c r="K34" t="s">
         <v>353</v>
       </c>
-      <c r="J34" t="s">
-        <v>354</v>
-      </c>
-      <c r="K34" t="s">
-        <v>357</v>
-      </c>
       <c r="L34" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="M34" t="s">
         <v>148</v>
@@ -4454,10 +4508,10 @@
         <v>17</v>
       </c>
       <c r="R34" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="S34" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="V34" t="s">
         <v>149</v>
@@ -4477,34 +4531,34 @@
     </row>
     <row r="35" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="B35" t="s">
         <v>150</v>
       </c>
       <c r="C35" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="E35" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="F35" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="G35" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="H35" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="I35" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="K35" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="L35" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="M35" t="s">
         <v>151</v>
@@ -4513,16 +4567,16 @@
         <v>565</v>
       </c>
       <c r="P35" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="Q35" t="s">
         <v>88</v>
       </c>
       <c r="R35" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="S35" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="V35" t="s">
         <v>152</v>
@@ -4542,37 +4596,37 @@
     </row>
     <row r="36" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="B36" t="s">
         <v>153</v>
       </c>
       <c r="C36" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="E36" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="F36" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="G36" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="H36" t="s">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="I36" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="J36" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="K36" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="L36" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="M36" t="s">
         <v>155</v>
@@ -4587,10 +4641,10 @@
         <v>88</v>
       </c>
       <c r="R36" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="S36" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="V36" t="s">
         <v>156</v>
@@ -4610,7 +4664,7 @@
     </row>
     <row r="37" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="B37" t="s">
         <v>92</v>
@@ -4619,22 +4673,22 @@
         <v>157</v>
       </c>
       <c r="E37" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="F37" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="G37" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="H37" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="K37" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="L37" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="M37" t="s">
         <v>158</v>
@@ -4643,16 +4697,16 @@
         <v>2064</v>
       </c>
       <c r="P37" t="s">
-        <v>21</v>
+        <v>329</v>
       </c>
       <c r="Q37" t="s">
         <v>21</v>
       </c>
       <c r="R37" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="S37" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="V37" t="s">
         <v>159</v>
@@ -4672,7 +4726,7 @@
     </row>
     <row r="38" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="B38" t="s">
         <v>92</v>
@@ -4681,22 +4735,22 @@
         <v>157</v>
       </c>
       <c r="E38" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="F38" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="G38" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="H38" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="K38" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="L38" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="M38" t="s">
         <v>160</v>
@@ -4705,16 +4759,16 @@
         <v>109</v>
       </c>
       <c r="P38" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="Q38" t="s">
         <v>21</v>
       </c>
       <c r="R38" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="S38" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="V38" t="s">
         <v>161</v>
@@ -4731,7 +4785,7 @@
     </row>
     <row r="39" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="B39" t="s">
         <v>92</v>
@@ -4740,22 +4794,22 @@
         <v>157</v>
       </c>
       <c r="E39" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="F39" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="G39" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="H39" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="K39" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="L39" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="M39" t="s">
         <v>162</v>
@@ -4764,16 +4818,16 @@
         <v>300</v>
       </c>
       <c r="P39" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="Q39" t="s">
         <v>21</v>
       </c>
       <c r="R39" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="S39" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="V39" t="s">
         <v>163</v>
@@ -4790,7 +4844,7 @@
     </row>
     <row r="40" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="B40" t="s">
         <v>92</v>
@@ -4799,22 +4853,22 @@
         <v>157</v>
       </c>
       <c r="E40" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="F40" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="G40" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="H40" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="K40" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="L40" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="M40" t="s">
         <v>164</v>
@@ -4823,16 +4877,16 @@
         <v>115</v>
       </c>
       <c r="P40" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="Q40" t="s">
         <v>21</v>
       </c>
       <c r="R40" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="S40" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="V40" t="s">
         <v>165</v>
@@ -4849,34 +4903,34 @@
     </row>
     <row r="41" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="B41" t="s">
         <v>166</v>
       </c>
       <c r="C41" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="E41" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="F41" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="G41" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="H41" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="I41" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="K41" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="L41" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="M41" t="s">
         <v>167</v>
@@ -4885,16 +4939,16 @@
         <v>819</v>
       </c>
       <c r="P41" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="Q41" t="s">
         <v>88</v>
       </c>
       <c r="R41" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="S41" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="V41" t="s">
         <v>168</v>
@@ -4914,37 +4968,37 @@
     </row>
     <row r="42" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="B42" t="s">
         <v>169</v>
       </c>
       <c r="C42" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="E42" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="F42" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="G42" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="H42" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="I42" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="J42" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="K42" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="L42" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="M42" t="s">
         <v>171</v>
@@ -4959,10 +5013,10 @@
         <v>17</v>
       </c>
       <c r="R42" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="S42" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="T42" s="1">
         <v>45199</v>
@@ -4988,52 +5042,52 @@
     </row>
     <row r="43" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="B43" t="s">
         <v>54</v>
       </c>
       <c r="C43" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="E43" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="F43" t="s">
-        <v>373</v>
+        <v>409</v>
       </c>
       <c r="G43" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="H43" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="I43" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="K43" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="L43" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="M43" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="O43">
         <v>450</v>
       </c>
       <c r="P43" t="s">
-        <v>174</v>
+        <v>540</v>
       </c>
       <c r="Q43" t="s">
         <v>17</v>
       </c>
       <c r="R43" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="S43" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="T43" s="1">
         <v>45199</v>
@@ -5042,7 +5096,7 @@
         <v>50</v>
       </c>
       <c r="V43" t="s">
-        <v>176</v>
+        <v>538</v>
       </c>
       <c r="W43" t="s">
         <v>173</v>
@@ -5059,43 +5113,43 @@
     </row>
     <row r="44" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="B44" t="s">
         <v>33</v>
       </c>
       <c r="C44" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="E44" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="F44" t="s">
+        <v>352</v>
+      </c>
+      <c r="G44" t="s">
+        <v>398</v>
+      </c>
+      <c r="H44" t="s">
+        <v>399</v>
+      </c>
+      <c r="I44" t="s">
+        <v>400</v>
+      </c>
+      <c r="J44" t="s">
         <v>356</v>
       </c>
-      <c r="G44" t="s">
-        <v>403</v>
-      </c>
-      <c r="H44" t="s">
-        <v>404</v>
-      </c>
-      <c r="I44" t="s">
-        <v>405</v>
-      </c>
-      <c r="J44" t="s">
-        <v>360</v>
-      </c>
       <c r="K44" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="L44" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="M44" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="N44" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="O44">
         <v>1100</v>
@@ -5107,10 +5161,10 @@
         <v>17</v>
       </c>
       <c r="R44" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="S44" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="T44" s="1">
         <v>45199</v>
@@ -5119,7 +5173,7 @@
         <v>50</v>
       </c>
       <c r="V44" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="W44" t="s">
         <v>173</v>
@@ -5136,55 +5190,55 @@
     </row>
     <row r="45" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="B45" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C45" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="D45" t="s">
         <v>70</v>
       </c>
       <c r="E45" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="F45" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="G45" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="H45" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="I45" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="K45" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="L45" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="M45" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="O45">
         <v>260</v>
       </c>
       <c r="P45" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="Q45" t="s">
         <v>17</v>
       </c>
       <c r="R45" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="S45" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="T45" s="1">
         <v>45213</v>
@@ -5193,7 +5247,7 @@
         <v>40</v>
       </c>
       <c r="V45" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="W45" t="s">
         <v>91</v>
@@ -5210,55 +5264,55 @@
     </row>
     <row r="46" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="B46" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="C46" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="E46" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="F46" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="G46" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="H46" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="I46" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="J46" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="K46" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="L46" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="M46" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="O46">
         <v>110</v>
       </c>
       <c r="P46" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="Q46" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="R46" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="S46" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="T46" s="1">
         <v>45215</v>
@@ -5267,10 +5321,10 @@
         <v>65</v>
       </c>
       <c r="V46" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="W46" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="X46">
         <v>95</v>
@@ -5284,7 +5338,7 @@
     </row>
     <row r="47" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="B47" t="s">
         <v>67</v>
@@ -5293,40 +5347,40 @@
         <v>128</v>
       </c>
       <c r="E47" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="F47" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="G47" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="H47" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="K47" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="L47" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="M47" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="O47">
         <v>100</v>
       </c>
       <c r="P47" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="Q47" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="R47" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="S47" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="T47" s="1">
         <v>45233</v>
@@ -5335,10 +5389,10 @@
         <v>60</v>
       </c>
       <c r="V47" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="W47" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="X47">
         <v>85</v>
@@ -5352,46 +5406,46 @@
     </row>
     <row r="48" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="B48" t="s">
         <v>49</v>
       </c>
       <c r="C48" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="E48" t="s">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="F48" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="G48" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="H48" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="L48" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="M48" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="O48">
         <v>123</v>
       </c>
       <c r="P48" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="Q48" t="s">
         <v>17</v>
       </c>
       <c r="R48" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="S48" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="T48" s="1">
         <v>45233</v>
@@ -5400,10 +5454,10 @@
         <v>20</v>
       </c>
       <c r="V48" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="W48" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="X48">
         <v>30</v>
@@ -5417,7 +5471,7 @@
     </row>
     <row r="49" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="B49" t="s">
         <v>67</v>
@@ -5426,46 +5480,46 @@
         <v>105</v>
       </c>
       <c r="E49" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="F49" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="G49" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="H49" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="I49" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="J49" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="K49" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="L49" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="M49" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="N49" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="O49">
         <v>155</v>
       </c>
       <c r="P49" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="R49" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="S49" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="T49" s="1">
         <v>45236</v>
@@ -5474,10 +5528,10 @@
         <v>55</v>
       </c>
       <c r="V49" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="W49" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="X49">
         <v>65</v>
@@ -5491,7 +5545,7 @@
     </row>
     <row r="50" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="B50" t="s">
         <v>120</v>
@@ -5500,43 +5554,43 @@
         <v>125</v>
       </c>
       <c r="E50" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="F50" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="G50" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="H50" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="I50" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="J50" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="L50" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="M50" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="O50">
         <v>790</v>
       </c>
       <c r="P50" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="Q50" t="s">
         <v>17</v>
       </c>
       <c r="R50" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="S50" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="T50" s="1">
         <v>45247</v>
@@ -5545,10 +5599,10 @@
         <v>50</v>
       </c>
       <c r="V50" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="W50" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="X50">
         <v>140</v>
@@ -5562,58 +5616,58 @@
     </row>
     <row r="51" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="B51" t="s">
         <v>54</v>
       </c>
       <c r="C51" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="E51" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="F51" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="G51" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="H51" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="I51" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="J51" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="L51" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="M51" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="O51">
         <v>3900</v>
       </c>
       <c r="P51" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="Q51" t="s">
+        <v>203</v>
+      </c>
+      <c r="R51" t="s">
+        <v>348</v>
+      </c>
+      <c r="S51" t="s">
+        <v>427</v>
+      </c>
+      <c r="V51" t="s">
         <v>205</v>
       </c>
-      <c r="R51" t="s">
-        <v>352</v>
-      </c>
-      <c r="S51" t="s">
-        <v>432</v>
-      </c>
-      <c r="V51" t="s">
-        <v>207</v>
-      </c>
       <c r="W51" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="X51">
         <v>85</v>
@@ -5627,61 +5681,61 @@
     </row>
     <row r="52" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="B52" t="s">
         <v>67</v>
       </c>
       <c r="C52" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="E52" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="F52" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="G52" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="H52" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="I52" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="J52" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="K52" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="L52" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="M52" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="O52">
         <v>1850</v>
       </c>
       <c r="P52" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="Q52" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="R52" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="S52" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="V52" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="W52" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="X52">
         <v>130</v>
@@ -5695,58 +5749,58 @@
     </row>
     <row r="53" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="B53" t="s">
         <v>54</v>
       </c>
       <c r="C53" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="E53" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="F53" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="G53" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="H53" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="I53" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="J53" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="L53" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="M53" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="O53">
         <v>350</v>
       </c>
       <c r="P53" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="Q53" t="s">
         <v>21</v>
       </c>
       <c r="R53" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="S53" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="V53" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="W53" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="X53">
         <v>35</v>
@@ -5760,7 +5814,7 @@
     </row>
     <row r="54" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="B54" t="s">
         <v>67</v>
@@ -5769,49 +5823,49 @@
         <v>133</v>
       </c>
       <c r="E54" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="F54" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="G54" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="H54" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="I54" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="J54" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="L54" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="M54" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="O54">
         <v>269</v>
       </c>
       <c r="P54" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="Q54" t="s">
         <v>21</v>
       </c>
       <c r="R54" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="S54" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="V54" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="W54" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="X54">
         <v>20</v>
@@ -5825,43 +5879,43 @@
     </row>
     <row r="55" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="B55" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C55" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D55" t="s">
         <v>86</v>
       </c>
       <c r="E55" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="F55" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="G55" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="H55" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="I55" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="J55" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="L55" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="M55" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="N55" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="O55">
         <v>200</v>
@@ -5873,10 +5927,10 @@
         <v>88</v>
       </c>
       <c r="R55" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="S55" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="T55" s="1">
         <v>45267</v>
@@ -5885,7 +5939,7 @@
         <v>40</v>
       </c>
       <c r="V55" t="s">
-        <v>223</v>
+        <v>539</v>
       </c>
       <c r="W55" t="s">
         <v>91</v>
@@ -5902,55 +5956,55 @@
     </row>
     <row r="56" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="B56" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="C56" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="E56" t="s">
-        <v>499</v>
+        <v>494</v>
       </c>
       <c r="F56" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="G56" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="H56" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="I56" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="J56" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="K56" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="L56" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="M56" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="O56">
         <v>375</v>
       </c>
       <c r="P56" t="s">
-        <v>540</v>
+        <v>535</v>
       </c>
       <c r="Q56" t="s">
         <v>21</v>
       </c>
       <c r="R56" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="S56" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="T56" s="1">
         <v>45267</v>
@@ -5959,7 +6013,7 @@
         <v>25</v>
       </c>
       <c r="V56" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="W56" t="s">
         <v>91</v>
@@ -5976,7 +6030,7 @@
     </row>
     <row r="57" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="B57" t="s">
         <v>67</v>
@@ -5985,43 +6039,43 @@
         <v>101</v>
       </c>
       <c r="E57" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="F57" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="G57" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="H57" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="I57" t="s">
         <v>121</v>
       </c>
       <c r="J57" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="L57" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="M57" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="O57">
         <v>510</v>
       </c>
       <c r="P57" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="Q57" t="s">
         <v>51</v>
       </c>
       <c r="R57" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="S57" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="T57" s="1">
         <v>45267</v>
@@ -6030,7 +6084,7 @@
         <v>15</v>
       </c>
       <c r="V57" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="W57" t="s">
         <v>91</v>
@@ -6047,55 +6101,55 @@
     </row>
     <row r="58" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B58" t="s">
         <v>67</v>
       </c>
       <c r="C58" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="E58" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="F58" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="G58" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="H58" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="I58" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="J58" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="K58" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="L58" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="M58" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="O58">
         <v>215</v>
       </c>
       <c r="P58" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="Q58" t="s">
         <v>21</v>
       </c>
       <c r="R58" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="S58" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="T58" s="1">
         <v>45269</v>
@@ -6104,10 +6158,10 @@
         <v>35</v>
       </c>
       <c r="V58" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="W58" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="X58">
         <v>60</v>
@@ -6121,58 +6175,58 @@
     </row>
     <row r="59" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="B59" t="s">
-        <v>538</v>
+        <v>533</v>
       </c>
       <c r="C59" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="D59" t="s">
         <v>58</v>
       </c>
       <c r="E59" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="F59" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="G59" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="H59" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="I59" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="J59" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="K59" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="L59" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="M59" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="O59">
         <v>92</v>
       </c>
       <c r="P59" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="Q59" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="R59" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="S59" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="T59" s="1">
         <v>45571</v>
@@ -6181,10 +6235,10 @@
         <v>60</v>
       </c>
       <c r="V59" t="s">
-        <v>539</v>
+        <v>534</v>
       </c>
       <c r="W59" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="X59">
         <v>70</v>
@@ -6198,52 +6252,52 @@
     </row>
     <row r="60" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="B60" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="C60" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="D60" t="s">
         <v>58</v>
       </c>
       <c r="E60" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="F60" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="G60" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="H60" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="I60" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="L60" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="M60" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="O60">
         <v>250</v>
       </c>
       <c r="P60" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="Q60" t="s">
         <v>42</v>
       </c>
       <c r="R60" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="S60" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="T60" s="1">
         <v>45591</v>
@@ -6252,10 +6306,10 @@
         <v>35</v>
       </c>
       <c r="V60" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="W60" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="X60">
         <v>90</v>
@@ -6269,55 +6323,55 @@
     </row>
     <row r="61" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="B61" t="s">
         <v>54</v>
       </c>
       <c r="C61" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="E61" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="F61" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="G61" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="H61" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="I61" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="J61" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="L61" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="M61" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="N61" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="O61">
         <v>200</v>
       </c>
       <c r="P61" t="s">
-        <v>243</v>
+        <v>537</v>
       </c>
       <c r="Q61" t="s">
         <v>21</v>
       </c>
       <c r="R61" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="S61" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="T61" s="1">
         <v>45635</v>
@@ -6326,10 +6380,10 @@
         <v>36</v>
       </c>
       <c r="V61" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="W61" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="X61">
         <v>100</v>
@@ -6338,57 +6392,57 @@
         <v>46031</v>
       </c>
       <c r="Z61" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="62" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="B62" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="C62" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="D62" t="s">
         <v>67</v>
       </c>
       <c r="E62" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="F62" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="G62" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="H62" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="I62" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="L62" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="M62" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="O62">
         <v>370</v>
       </c>
       <c r="P62" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="Q62" t="s">
         <v>51</v>
       </c>
       <c r="R62" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="S62" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="T62" s="1">
         <v>45646</v>
@@ -6397,10 +6451,10 @@
         <v>50</v>
       </c>
       <c r="V62" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="W62" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="X62">
         <v>110</v>
@@ -6414,58 +6468,58 @@
     </row>
     <row r="63" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="B63" t="s">
         <v>67</v>
       </c>
       <c r="C63" t="s">
+        <v>249</v>
+      </c>
+      <c r="D63" t="s">
+        <v>250</v>
+      </c>
+      <c r="E63" t="s">
+        <v>423</v>
+      </c>
+      <c r="F63" t="s">
+        <v>409</v>
+      </c>
+      <c r="G63" t="s">
+        <v>395</v>
+      </c>
+      <c r="H63" t="s">
+        <v>485</v>
+      </c>
+      <c r="I63" t="s">
+        <v>249</v>
+      </c>
+      <c r="J63" t="s">
+        <v>350</v>
+      </c>
+      <c r="K63" t="s">
+        <v>471</v>
+      </c>
+      <c r="L63" t="s">
+        <v>347</v>
+      </c>
+      <c r="M63" t="s">
+        <v>252</v>
+      </c>
+      <c r="N63" t="s">
         <v>253</v>
-      </c>
-      <c r="D63" t="s">
-        <v>254</v>
-      </c>
-      <c r="E63" t="s">
-        <v>428</v>
-      </c>
-      <c r="F63" t="s">
-        <v>414</v>
-      </c>
-      <c r="G63" t="s">
-        <v>400</v>
-      </c>
-      <c r="H63" t="s">
-        <v>490</v>
-      </c>
-      <c r="I63" t="s">
-        <v>253</v>
-      </c>
-      <c r="J63" t="s">
-        <v>354</v>
-      </c>
-      <c r="K63" t="s">
-        <v>476</v>
-      </c>
-      <c r="L63" t="s">
-        <v>351</v>
-      </c>
-      <c r="M63" t="s">
-        <v>256</v>
-      </c>
-      <c r="N63" t="s">
-        <v>257</v>
       </c>
       <c r="O63">
         <v>3500</v>
       </c>
       <c r="P63" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="R63" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="S63" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="T63" s="1">
         <v>45839</v>
@@ -6474,10 +6528,10 @@
         <v>160</v>
       </c>
       <c r="V63" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="W63" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="X63">
         <v>300</v>
@@ -6491,55 +6545,55 @@
     </row>
     <row r="64" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="B64" t="s">
         <v>67</v>
       </c>
       <c r="C64" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="E64" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="F64" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="G64" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="H64" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="I64" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="J64" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="L64" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="M64" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="N64" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="O64">
         <v>225</v>
       </c>
       <c r="P64" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="Q64" t="s">
         <v>21</v>
       </c>
       <c r="R64" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="S64" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="T64" s="1">
         <v>45996</v>
@@ -6548,10 +6602,10 @@
         <v>75</v>
       </c>
       <c r="V64" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="W64" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="X64">
         <v>120</v>
@@ -6565,58 +6619,58 @@
     </row>
     <row r="65" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="B65" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="C65" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="D65" t="s">
         <v>33</v>
       </c>
       <c r="E65" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="F65" t="s">
+        <v>352</v>
+      </c>
+      <c r="G65" t="s">
+        <v>398</v>
+      </c>
+      <c r="H65" t="s">
+        <v>492</v>
+      </c>
+      <c r="I65" t="s">
+        <v>355</v>
+      </c>
+      <c r="J65" t="s">
         <v>356</v>
       </c>
-      <c r="G65" t="s">
-        <v>403</v>
-      </c>
-      <c r="H65" t="s">
-        <v>497</v>
-      </c>
-      <c r="I65" t="s">
-        <v>359</v>
-      </c>
-      <c r="J65" t="s">
-        <v>360</v>
-      </c>
       <c r="K65" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="L65" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="M65" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="O65">
         <v>105</v>
       </c>
       <c r="P65" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="Q65" t="s">
         <v>38</v>
       </c>
       <c r="R65" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="S65" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="T65" s="1">
         <v>46013</v>
@@ -6625,10 +6679,10 @@
         <v>30</v>
       </c>
       <c r="V65" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="W65" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="X65">
         <v>150</v>
@@ -6642,52 +6696,52 @@
     </row>
     <row r="66" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="B66" t="s">
+        <v>207</v>
+      </c>
+      <c r="C66" t="s">
+        <v>428</v>
+      </c>
+      <c r="E66" t="s">
+        <v>423</v>
+      </c>
+      <c r="F66" t="s">
+        <v>409</v>
+      </c>
+      <c r="G66" t="s">
+        <v>395</v>
+      </c>
+      <c r="H66" t="s">
+        <v>508</v>
+      </c>
+      <c r="I66" t="s">
         <v>509</v>
       </c>
-      <c r="B66" t="s">
-        <v>209</v>
-      </c>
-      <c r="C66" t="s">
-        <v>433</v>
-      </c>
-      <c r="E66" t="s">
-        <v>428</v>
-      </c>
-      <c r="F66" t="s">
-        <v>414</v>
-      </c>
-      <c r="G66" t="s">
-        <v>400</v>
-      </c>
-      <c r="H66" t="s">
-        <v>513</v>
-      </c>
-      <c r="I66" t="s">
-        <v>514</v>
-      </c>
       <c r="K66" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="L66" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="M66" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="O66">
         <v>86</v>
       </c>
       <c r="P66" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="Q66" t="s">
         <v>17</v>
       </c>
       <c r="R66" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="S66" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="T66" s="6">
         <v>46041</v>
@@ -6696,10 +6750,10 @@
         <v>0</v>
       </c>
       <c r="V66" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="W66" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="X66">
         <v>15</v>
@@ -6713,55 +6767,55 @@
     </row>
     <row r="67" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="B67" t="s">
         <v>169</v>
       </c>
       <c r="C67" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="E67" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="F67" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="G67" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="H67" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="I67" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="J67" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="K67" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="L67" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="M67" t="s">
-        <v>522</v>
+        <v>517</v>
       </c>
       <c r="O67">
         <v>28</v>
       </c>
       <c r="P67" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="Q67" t="s">
         <v>38</v>
       </c>
       <c r="R67" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="S67" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="T67" s="6">
         <v>46041</v>
@@ -6770,10 +6824,10 @@
         <v>25</v>
       </c>
       <c r="V67" t="s">
-        <v>523</v>
+        <v>518</v>
       </c>
       <c r="W67" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="X67">
         <v>60</v>
@@ -6787,7 +6841,7 @@
     </row>
     <row r="68" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="B68" t="s">
         <v>67</v>
@@ -6796,46 +6850,46 @@
         <v>101</v>
       </c>
       <c r="E68" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="F68" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="G68" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="H68" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="I68" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="J68" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="K68" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="L68" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="M68" t="s">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="O68">
         <v>92</v>
       </c>
       <c r="P68" t="s">
-        <v>526</v>
+        <v>521</v>
       </c>
       <c r="Q68" t="s">
         <v>10</v>
       </c>
       <c r="R68" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="S68" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="T68" s="6">
         <v>46041</v>
@@ -6844,10 +6898,10 @@
         <v>30</v>
       </c>
       <c r="V68" t="s">
-        <v>527</v>
+        <v>522</v>
       </c>
       <c r="W68" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="X68">
         <v>85</v>
@@ -6861,55 +6915,55 @@
     </row>
     <row r="69" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="B69" t="s">
+        <v>523</v>
+      </c>
+      <c r="C69" t="s">
+        <v>428</v>
+      </c>
+      <c r="E69" t="s">
+        <v>524</v>
+      </c>
+      <c r="F69" t="s">
+        <v>387</v>
+      </c>
+      <c r="G69" t="s">
+        <v>419</v>
+      </c>
+      <c r="H69" t="s">
+        <v>525</v>
+      </c>
+      <c r="I69" t="s">
+        <v>526</v>
+      </c>
+      <c r="J69" t="s">
+        <v>359</v>
+      </c>
+      <c r="K69" t="s">
+        <v>527</v>
+      </c>
+      <c r="L69" t="s">
+        <v>347</v>
+      </c>
+      <c r="M69" t="s">
         <v>528</v>
-      </c>
-      <c r="C69" t="s">
-        <v>433</v>
-      </c>
-      <c r="E69" t="s">
-        <v>529</v>
-      </c>
-      <c r="F69" t="s">
-        <v>392</v>
-      </c>
-      <c r="G69" t="s">
-        <v>424</v>
-      </c>
-      <c r="H69" t="s">
-        <v>530</v>
-      </c>
-      <c r="I69" t="s">
-        <v>531</v>
-      </c>
-      <c r="J69" t="s">
-        <v>363</v>
-      </c>
-      <c r="K69" t="s">
-        <v>532</v>
-      </c>
-      <c r="L69" t="s">
-        <v>351</v>
-      </c>
-      <c r="M69" t="s">
-        <v>533</v>
       </c>
       <c r="O69">
         <v>160</v>
       </c>
       <c r="P69" t="s">
-        <v>534</v>
+        <v>529</v>
       </c>
       <c r="Q69" t="s">
-        <v>536</v>
+        <v>531</v>
       </c>
       <c r="R69" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="S69" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="T69" s="6">
         <v>46041</v>
@@ -6918,10 +6972,10 @@
         <v>60</v>
       </c>
       <c r="V69" t="s">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="W69" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="X69">
         <v>150</v>
@@ -6930,6 +6984,237 @@
         <v>46043</v>
       </c>
       <c r="Z69" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="70" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A70" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="B70" t="s">
+        <v>67</v>
+      </c>
+      <c r="C70" t="s">
+        <v>541</v>
+      </c>
+      <c r="D70" t="s">
+        <v>542</v>
+      </c>
+      <c r="E70" t="s">
+        <v>423</v>
+      </c>
+      <c r="F70" t="s">
+        <v>409</v>
+      </c>
+      <c r="G70" t="s">
+        <v>395</v>
+      </c>
+      <c r="H70" t="s">
+        <v>485</v>
+      </c>
+      <c r="I70" t="s">
+        <v>553</v>
+      </c>
+      <c r="J70" t="s">
+        <v>368</v>
+      </c>
+      <c r="K70" t="s">
+        <v>516</v>
+      </c>
+      <c r="L70" t="s">
+        <v>347</v>
+      </c>
+      <c r="M70" t="s">
+        <v>543</v>
+      </c>
+      <c r="O70">
+        <v>97</v>
+      </c>
+      <c r="P70" t="s">
+        <v>188</v>
+      </c>
+      <c r="Q70" t="s">
+        <v>189</v>
+      </c>
+      <c r="R70" t="s">
+        <v>351</v>
+      </c>
+      <c r="S70" t="s">
+        <v>427</v>
+      </c>
+      <c r="T70" s="1">
+        <v>46071</v>
+      </c>
+      <c r="U70">
+        <v>155</v>
+      </c>
+      <c r="V70" t="s">
+        <v>562</v>
+      </c>
+      <c r="W70" t="s">
+        <v>513</v>
+      </c>
+      <c r="X70">
+        <v>200</v>
+      </c>
+      <c r="Y70" s="1">
+        <v>46071</v>
+      </c>
+      <c r="Z70" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="71" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A71" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="B71" t="s">
+        <v>120</v>
+      </c>
+      <c r="C71" t="s">
+        <v>125</v>
+      </c>
+      <c r="D71" t="s">
+        <v>54</v>
+      </c>
+      <c r="E71" t="s">
+        <v>443</v>
+      </c>
+      <c r="F71" t="s">
+        <v>352</v>
+      </c>
+      <c r="G71" t="s">
+        <v>444</v>
+      </c>
+      <c r="H71" t="s">
+        <v>474</v>
+      </c>
+      <c r="I71" t="s">
+        <v>554</v>
+      </c>
+      <c r="J71" t="s">
+        <v>350</v>
+      </c>
+      <c r="K71" t="s">
+        <v>373</v>
+      </c>
+      <c r="L71" t="s">
+        <v>347</v>
+      </c>
+      <c r="M71" t="s">
+        <v>548</v>
+      </c>
+      <c r="O71">
+        <v>318</v>
+      </c>
+      <c r="P71" t="s">
+        <v>547</v>
+      </c>
+      <c r="Q71" t="s">
+        <v>17</v>
+      </c>
+      <c r="R71" t="s">
+        <v>351</v>
+      </c>
+      <c r="S71" t="s">
+        <v>427</v>
+      </c>
+      <c r="T71" s="1">
+        <v>46071</v>
+      </c>
+      <c r="U71">
+        <v>60</v>
+      </c>
+      <c r="V71" t="s">
+        <v>555</v>
+      </c>
+      <c r="W71" t="s">
+        <v>513</v>
+      </c>
+      <c r="X71">
+        <v>100</v>
+      </c>
+      <c r="Y71" s="1">
+        <v>46071</v>
+      </c>
+      <c r="Z71" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="72" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A72" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="B72" t="s">
+        <v>549</v>
+      </c>
+      <c r="C72" t="s">
+        <v>550</v>
+      </c>
+      <c r="D72" t="s">
+        <v>67</v>
+      </c>
+      <c r="E72" t="s">
+        <v>556</v>
+      </c>
+      <c r="F72" t="s">
+        <v>352</v>
+      </c>
+      <c r="G72" t="s">
+        <v>398</v>
+      </c>
+      <c r="H72" t="s">
+        <v>557</v>
+      </c>
+      <c r="I72" t="s">
+        <v>558</v>
+      </c>
+      <c r="J72" t="s">
+        <v>559</v>
+      </c>
+      <c r="K72" t="s">
+        <v>560</v>
+      </c>
+      <c r="L72" t="s">
+        <v>347</v>
+      </c>
+      <c r="M72" t="s">
+        <v>552</v>
+      </c>
+      <c r="O72">
+        <v>47</v>
+      </c>
+      <c r="P72" t="s">
+        <v>551</v>
+      </c>
+      <c r="Q72" t="s">
+        <v>135</v>
+      </c>
+      <c r="R72" t="s">
+        <v>351</v>
+      </c>
+      <c r="S72" t="s">
+        <v>427</v>
+      </c>
+      <c r="T72" s="1">
+        <v>46071</v>
+      </c>
+      <c r="U72">
+        <v>60</v>
+      </c>
+      <c r="V72" t="s">
+        <v>561</v>
+      </c>
+      <c r="W72" t="s">
+        <v>513</v>
+      </c>
+      <c r="X72">
+        <v>90</v>
+      </c>
+      <c r="Y72" s="1">
+        <v>46071</v>
+      </c>
+      <c r="Z72" t="s">
         <v>14</v>
       </c>
     </row>

--- a/Coleccion de minerales.xlsx
+++ b/Coleccion de minerales.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Colección Minerales\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD2DECC1-2C90-4E30-9F54-A646B05D3B19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC158D4D-FA1D-4474-8493-4B189F9C45D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1328" uniqueCount="563">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1330" uniqueCount="565">
   <si>
     <t>Mineral</t>
   </si>
@@ -110,14 +110,7 @@
     <t>Pirolusita</t>
   </si>
   <si>
-    <t>Cartagena</t>
-  </si>
-  <si>
     <t>88.5x165x26</t>
-  </si>
-  <si>
-    <t>Agregado laminar y escalonado de pirolusita, con cristales tabulares superpuestos formando estructuras en “libro” o crecimientos dentados, muy característicos de Cartagena.
-Color gris plateado a gris oscuro, con brillo metálico mate a satinado.</t>
   </si>
   <si>
     <t>Dendrítica</t>
@@ -1300,9 +1293,6 @@
   </si>
   <si>
     <t>Marrón miel a caramelo</t>
-  </si>
-  <si>
-    <t>Gris plateado a gris oscuro</t>
   </si>
   <si>
     <t>Tetragonal</t>
@@ -1764,9 +1754,6 @@
     <t>Tounfite, Midelt, Draa-Tafilalet</t>
   </si>
   <si>
-    <t>Compuesto por múltiples cristales puntiagudos que irradian desde varios centros, formando agregados esféricos y densamente compactos ("dientes de perro"). Yacimiento clásico español. Buena conservación de caras cristalinas. Yacimiento clásico español. Buena conservación de caras cristalinas.</t>
-  </si>
-  <si>
     <t>Hidroxiapofilita-(K) (atribución probable). Apofilitas bien cristalizadas, hábito cúbico limpio. Buen contraste cromático: blanco lechoso + estilbita crema. Brillo satinado agradable, sin aspecto apagado. Composición estética y compacta.</t>
   </si>
   <si>
@@ -1837,13 +1824,44 @@
   </si>
   <si>
     <t>Ejemplar compuesto por un agregado compacto de cristales prismáticos de cuarzo con desarrollo tridimensional y múltiples terminaciones definidas. Presenta inclusiones y recubrimientos internos de halloysita, responsables de la tonalidad amarillo-mango. Las inclusiones se distribuyen en formas fibrosas y masas microgranulares, generando contrastes cromáticos cálidos frente a la transparencia del cuarzo huésped.</t>
+  </si>
+  <si>
+    <t>Compuesto por múltiples cristales puntiagudos que irradian desde varios centros, formando agregados esféricos y densamente compactos ("dientes de perro"). Yacimiento clásico español. Buena conservación de caras cristalinas.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Cristales romboédricos aplanados con un crecimiento </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>escalonado</t>
+    </r>
+  </si>
+  <si>
+    <t>blanco lechoso a grisáceo</t>
+  </si>
+  <si>
+    <t>Vítreo a perlado</t>
+  </si>
+  <si>
+    <t>Ejemplar de calcita que presenta un excelente desarrollo de cristales romboédricos aplanados, dispuestos en un crecimiento paralelo y escalonado. Depósitos de color negro-grisáceo de aspecto terroso y hábito masivo, identificados como pirolusita (MnO₂).</t>
+  </si>
+  <si>
+    <t>Sierra Minera de Cartagena-La Unión, Murcia</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1882,6 +1900,14 @@
       <color rgb="FF202122"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -2291,7 +2317,7 @@
   <sheetData>
     <row r="1" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>0</v>
@@ -2303,37 +2329,37 @@
         <v>2</v>
       </c>
       <c r="E1" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="G1" s="3" t="s">
         <v>335</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>337</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>338</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="J1" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>341</v>
-      </c>
       <c r="L1" s="3" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="P1" s="3" t="s">
         <v>3</v>
@@ -2342,16 +2368,16 @@
         <v>4</v>
       </c>
       <c r="R1" s="3" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="S1" s="3" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="T1" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="U1" s="3" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="V1" s="3" t="s">
         <v>5</v>
@@ -2360,10 +2386,10 @@
         <v>6</v>
       </c>
       <c r="X1" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="Y1" s="3" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="Z1" s="3" t="s">
         <v>7</v>
@@ -2371,34 +2397,34 @@
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B2" t="s">
         <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="E2" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="F2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="G2" t="s">
+        <v>384</v>
+      </c>
+      <c r="H2" t="s">
         <v>386</v>
       </c>
-      <c r="H2" t="s">
-        <v>388</v>
-      </c>
       <c r="I2" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="J2" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="M2" t="s">
         <v>11</v>
@@ -2413,10 +2439,10 @@
         <v>10</v>
       </c>
       <c r="R2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="S2" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="V2" t="s">
         <v>12</v>
@@ -2436,34 +2462,34 @@
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B3" t="s">
         <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="E3" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="F3" t="s">
+        <v>385</v>
+      </c>
+      <c r="G3" t="s">
+        <v>388</v>
+      </c>
+      <c r="H3" t="s">
         <v>387</v>
       </c>
-      <c r="G3" t="s">
-        <v>390</v>
-      </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
         <v>389</v>
       </c>
-      <c r="I3" t="s">
-        <v>391</v>
-      </c>
       <c r="J3" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="L3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="M3" t="s">
         <v>18</v>
@@ -2478,10 +2504,10 @@
         <v>17</v>
       </c>
       <c r="R3" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="S3" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="V3" t="s">
         <v>19</v>
@@ -2498,34 +2524,34 @@
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B4" t="s">
         <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="E4" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="F4" t="s">
+        <v>385</v>
+      </c>
+      <c r="G4" t="s">
+        <v>388</v>
+      </c>
+      <c r="H4" t="s">
         <v>387</v>
       </c>
-      <c r="G4" t="s">
+      <c r="I4" t="s">
         <v>390</v>
       </c>
-      <c r="H4" t="s">
-        <v>389</v>
-      </c>
-      <c r="I4" t="s">
-        <v>392</v>
-      </c>
       <c r="K4" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="L4" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="M4" t="s">
         <v>22</v>
@@ -2540,10 +2566,10 @@
         <v>21</v>
       </c>
       <c r="R4" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="S4" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="V4" t="s">
         <v>23</v>
@@ -2563,61 +2589,67 @@
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C5" t="s">
+        <v>425</v>
+      </c>
+      <c r="D5" t="s">
         <v>25</v>
       </c>
-      <c r="C5" t="s">
-        <v>428</v>
-      </c>
       <c r="E5" t="s">
-        <v>430</v>
+        <v>377</v>
       </c>
       <c r="F5" t="s">
-        <v>394</v>
+        <v>406</v>
       </c>
       <c r="G5" t="s">
-        <v>395</v>
+        <v>388</v>
       </c>
       <c r="H5" t="s">
-        <v>396</v>
+        <v>560</v>
       </c>
       <c r="I5" t="s">
-        <v>393</v>
+        <v>561</v>
       </c>
       <c r="J5" t="s">
-        <v>365</v>
+        <v>562</v>
       </c>
       <c r="K5" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="L5" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="M5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O5">
         <v>410</v>
       </c>
       <c r="P5" t="s">
-        <v>26</v>
+        <v>564</v>
       </c>
       <c r="Q5" t="s">
         <v>17</v>
       </c>
       <c r="R5" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="S5" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="V5" t="s">
-        <v>28</v>
+        <v>563</v>
+      </c>
+      <c r="W5" t="s">
+        <v>13</v>
       </c>
       <c r="X5">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="Y5" s="1">
         <v>46032</v>
@@ -2628,52 +2660,52 @@
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" t="s">
+        <v>427</v>
+      </c>
+      <c r="F6" t="s">
+        <v>391</v>
+      </c>
+      <c r="G6" t="s">
+        <v>392</v>
+      </c>
+      <c r="H6" t="s">
+        <v>393</v>
+      </c>
+      <c r="K6" t="s">
+        <v>381</v>
+      </c>
+      <c r="L6" t="s">
+        <v>345</v>
+      </c>
+      <c r="M6" t="s">
         <v>29</v>
-      </c>
-      <c r="E6" t="s">
-        <v>430</v>
-      </c>
-      <c r="F6" t="s">
-        <v>394</v>
-      </c>
-      <c r="G6" t="s">
-        <v>395</v>
-      </c>
-      <c r="H6" t="s">
-        <v>396</v>
-      </c>
-      <c r="K6" t="s">
-        <v>383</v>
-      </c>
-      <c r="L6" t="s">
-        <v>347</v>
-      </c>
-      <c r="M6" t="s">
-        <v>31</v>
       </c>
       <c r="O6">
         <v>120</v>
       </c>
       <c r="P6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="Q6" t="s">
         <v>17</v>
       </c>
       <c r="R6" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="S6" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="V6" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="X6">
         <v>60</v>
@@ -2687,58 +2719,58 @@
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B7" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E7" t="s">
+        <v>394</v>
+      </c>
+      <c r="F7" t="s">
+        <v>350</v>
+      </c>
+      <c r="G7" t="s">
+        <v>395</v>
+      </c>
+      <c r="H7" t="s">
+        <v>396</v>
+      </c>
+      <c r="I7" t="s">
+        <v>397</v>
+      </c>
+      <c r="J7" t="s">
+        <v>354</v>
+      </c>
+      <c r="K7" t="s">
+        <v>381</v>
+      </c>
+      <c r="L7" t="s">
+        <v>345</v>
+      </c>
+      <c r="M7" t="s">
         <v>34</v>
-      </c>
-      <c r="E7" t="s">
-        <v>397</v>
-      </c>
-      <c r="F7" t="s">
-        <v>352</v>
-      </c>
-      <c r="G7" t="s">
-        <v>398</v>
-      </c>
-      <c r="H7" t="s">
-        <v>399</v>
-      </c>
-      <c r="I7" t="s">
-        <v>400</v>
-      </c>
-      <c r="J7" t="s">
-        <v>356</v>
-      </c>
-      <c r="K7" t="s">
-        <v>383</v>
-      </c>
-      <c r="L7" t="s">
-        <v>347</v>
-      </c>
-      <c r="M7" t="s">
-        <v>36</v>
       </c>
       <c r="O7">
         <v>118</v>
       </c>
       <c r="P7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="Q7" t="s">
         <v>17</v>
       </c>
       <c r="R7" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="S7" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="V7" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="W7" t="s">
         <v>13</v>
@@ -2755,58 +2787,58 @@
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B8" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C8" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="E8" t="s">
+        <v>394</v>
+      </c>
+      <c r="F8" t="s">
+        <v>350</v>
+      </c>
+      <c r="G8" t="s">
+        <v>395</v>
+      </c>
+      <c r="H8" t="s">
+        <v>396</v>
+      </c>
+      <c r="I8" t="s">
         <v>397</v>
       </c>
-      <c r="F8" t="s">
-        <v>352</v>
-      </c>
-      <c r="G8" t="s">
-        <v>398</v>
-      </c>
-      <c r="H8" t="s">
-        <v>399</v>
-      </c>
-      <c r="I8" t="s">
-        <v>400</v>
-      </c>
       <c r="J8" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="K8" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="L8" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="M8" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="O8">
         <v>572</v>
       </c>
       <c r="P8" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="Q8" t="s">
+        <v>36</v>
+      </c>
+      <c r="R8" t="s">
+        <v>346</v>
+      </c>
+      <c r="S8" t="s">
+        <v>424</v>
+      </c>
+      <c r="V8" t="s">
         <v>38</v>
-      </c>
-      <c r="R8" t="s">
-        <v>348</v>
-      </c>
-      <c r="S8" t="s">
-        <v>427</v>
-      </c>
-      <c r="V8" t="s">
-        <v>40</v>
       </c>
       <c r="W8" t="s">
         <v>13</v>
@@ -2823,58 +2855,58 @@
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B9" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9" t="s">
+        <v>425</v>
+      </c>
+      <c r="E9" t="s">
+        <v>394</v>
+      </c>
+      <c r="F9" t="s">
+        <v>350</v>
+      </c>
+      <c r="G9" t="s">
+        <v>395</v>
+      </c>
+      <c r="H9" t="s">
+        <v>483</v>
+      </c>
+      <c r="I9" t="s">
+        <v>397</v>
+      </c>
+      <c r="J9" t="s">
+        <v>354</v>
+      </c>
+      <c r="K9" t="s">
+        <v>381</v>
+      </c>
+      <c r="L9" t="s">
+        <v>345</v>
+      </c>
+      <c r="M9" t="s">
         <v>41</v>
-      </c>
-      <c r="C9" t="s">
-        <v>428</v>
-      </c>
-      <c r="E9" t="s">
-        <v>397</v>
-      </c>
-      <c r="F9" t="s">
-        <v>352</v>
-      </c>
-      <c r="G9" t="s">
-        <v>398</v>
-      </c>
-      <c r="H9" t="s">
-        <v>486</v>
-      </c>
-      <c r="I9" t="s">
-        <v>400</v>
-      </c>
-      <c r="J9" t="s">
-        <v>356</v>
-      </c>
-      <c r="K9" t="s">
-        <v>383</v>
-      </c>
-      <c r="L9" t="s">
-        <v>347</v>
-      </c>
-      <c r="M9" t="s">
-        <v>43</v>
       </c>
       <c r="O9">
         <v>81</v>
       </c>
       <c r="P9" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="Q9" t="s">
+        <v>40</v>
+      </c>
+      <c r="R9" t="s">
+        <v>346</v>
+      </c>
+      <c r="S9" t="s">
+        <v>424</v>
+      </c>
+      <c r="V9" t="s">
         <v>42</v>
-      </c>
-      <c r="R9" t="s">
-        <v>348</v>
-      </c>
-      <c r="S9" t="s">
-        <v>427</v>
-      </c>
-      <c r="V9" t="s">
-        <v>44</v>
       </c>
       <c r="W9" t="s">
         <v>13</v>
@@ -2891,52 +2923,52 @@
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C10" t="s">
+        <v>425</v>
+      </c>
+      <c r="E10" t="s">
+        <v>398</v>
+      </c>
+      <c r="F10" t="s">
+        <v>400</v>
+      </c>
+      <c r="G10" t="s">
+        <v>399</v>
+      </c>
+      <c r="I10" t="s">
+        <v>401</v>
+      </c>
+      <c r="J10" t="s">
+        <v>348</v>
+      </c>
+      <c r="L10" t="s">
+        <v>345</v>
+      </c>
+      <c r="M10" t="s">
         <v>45</v>
-      </c>
-      <c r="C10" t="s">
-        <v>428</v>
-      </c>
-      <c r="E10" t="s">
-        <v>401</v>
-      </c>
-      <c r="F10" t="s">
-        <v>403</v>
-      </c>
-      <c r="G10" t="s">
-        <v>402</v>
-      </c>
-      <c r="I10" t="s">
-        <v>404</v>
-      </c>
-      <c r="J10" t="s">
-        <v>350</v>
-      </c>
-      <c r="L10" t="s">
-        <v>347</v>
-      </c>
-      <c r="M10" t="s">
-        <v>47</v>
       </c>
       <c r="O10">
         <v>171</v>
       </c>
       <c r="P10" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q10" t="s">
         <v>17</v>
       </c>
       <c r="R10" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="S10" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="V10" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="X10">
         <v>40</v>
@@ -2950,52 +2982,52 @@
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B11" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C11" t="s">
+        <v>48</v>
+      </c>
+      <c r="E11" t="s">
+        <v>495</v>
+      </c>
+      <c r="G11" t="s">
+        <v>399</v>
+      </c>
+      <c r="H11" t="s">
+        <v>484</v>
+      </c>
+      <c r="I11" t="s">
+        <v>403</v>
+      </c>
+      <c r="J11" t="s">
+        <v>404</v>
+      </c>
+      <c r="L11" t="s">
+        <v>345</v>
+      </c>
+      <c r="M11" t="s">
         <v>50</v>
-      </c>
-      <c r="E11" t="s">
-        <v>498</v>
-      </c>
-      <c r="G11" t="s">
-        <v>402</v>
-      </c>
-      <c r="H11" t="s">
-        <v>487</v>
-      </c>
-      <c r="I11" t="s">
-        <v>406</v>
-      </c>
-      <c r="J11" t="s">
-        <v>407</v>
-      </c>
-      <c r="L11" t="s">
-        <v>347</v>
-      </c>
-      <c r="M11" t="s">
-        <v>52</v>
       </c>
       <c r="O11">
         <v>204</v>
       </c>
       <c r="P11" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="Q11" t="s">
+        <v>49</v>
+      </c>
+      <c r="R11" t="s">
+        <v>346</v>
+      </c>
+      <c r="S11" t="s">
+        <v>424</v>
+      </c>
+      <c r="V11" t="s">
         <v>51</v>
-      </c>
-      <c r="R11" t="s">
-        <v>348</v>
-      </c>
-      <c r="S11" t="s">
-        <v>427</v>
-      </c>
-      <c r="V11" t="s">
-        <v>53</v>
       </c>
       <c r="W11" t="s">
         <v>13</v>
@@ -3012,58 +3044,58 @@
     </row>
     <row r="12" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C12" t="s">
+        <v>53</v>
+      </c>
+      <c r="E12" t="s">
+        <v>377</v>
+      </c>
+      <c r="F12" t="s">
+        <v>406</v>
+      </c>
+      <c r="G12" t="s">
+        <v>388</v>
+      </c>
+      <c r="H12" t="s">
+        <v>405</v>
+      </c>
+      <c r="I12" t="s">
+        <v>379</v>
+      </c>
+      <c r="J12" t="s">
+        <v>380</v>
+      </c>
+      <c r="K12" t="s">
+        <v>381</v>
+      </c>
+      <c r="L12" s="4" t="s">
+        <v>498</v>
+      </c>
+      <c r="M12" t="s">
         <v>54</v>
-      </c>
-      <c r="C12" t="s">
-        <v>55</v>
-      </c>
-      <c r="E12" t="s">
-        <v>379</v>
-      </c>
-      <c r="F12" t="s">
-        <v>409</v>
-      </c>
-      <c r="G12" t="s">
-        <v>390</v>
-      </c>
-      <c r="H12" t="s">
-        <v>408</v>
-      </c>
-      <c r="I12" t="s">
-        <v>381</v>
-      </c>
-      <c r="J12" t="s">
-        <v>382</v>
-      </c>
-      <c r="K12" t="s">
-        <v>383</v>
-      </c>
-      <c r="L12" s="4" t="s">
-        <v>501</v>
-      </c>
-      <c r="M12" t="s">
-        <v>56</v>
       </c>
       <c r="O12">
         <v>500</v>
       </c>
       <c r="P12" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="Q12" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="R12" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="S12" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="V12" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="W12" t="s">
         <v>13</v>
@@ -3080,55 +3112,55 @@
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B13" t="s">
+        <v>56</v>
+      </c>
+      <c r="C13" t="s">
+        <v>425</v>
+      </c>
+      <c r="D13" t="s">
+        <v>57</v>
+      </c>
+      <c r="E13" t="s">
+        <v>430</v>
+      </c>
+      <c r="F13" t="s">
+        <v>369</v>
+      </c>
+      <c r="G13" t="s">
+        <v>388</v>
+      </c>
+      <c r="H13" t="s">
+        <v>407</v>
+      </c>
+      <c r="I13" t="s">
+        <v>408</v>
+      </c>
+      <c r="L13" t="s">
+        <v>345</v>
+      </c>
+      <c r="M13" t="s">
         <v>58</v>
-      </c>
-      <c r="C13" t="s">
-        <v>428</v>
-      </c>
-      <c r="D13" t="s">
-        <v>59</v>
-      </c>
-      <c r="E13" t="s">
-        <v>433</v>
-      </c>
-      <c r="F13" t="s">
-        <v>371</v>
-      </c>
-      <c r="G13" t="s">
-        <v>390</v>
-      </c>
-      <c r="H13" t="s">
-        <v>410</v>
-      </c>
-      <c r="I13" t="s">
-        <v>411</v>
-      </c>
-      <c r="L13" t="s">
-        <v>347</v>
-      </c>
-      <c r="M13" t="s">
-        <v>60</v>
       </c>
       <c r="O13">
         <v>550</v>
       </c>
       <c r="P13" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="Q13" t="s">
         <v>21</v>
       </c>
       <c r="R13" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="S13" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="V13" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="W13" t="s">
         <v>13</v>
@@ -3145,58 +3177,58 @@
     </row>
     <row r="14" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B14" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C14" t="s">
+        <v>60</v>
+      </c>
+      <c r="E14" t="s">
+        <v>377</v>
+      </c>
+      <c r="F14" t="s">
+        <v>406</v>
+      </c>
+      <c r="G14" t="s">
+        <v>388</v>
+      </c>
+      <c r="H14" t="s">
+        <v>405</v>
+      </c>
+      <c r="I14" t="s">
+        <v>375</v>
+      </c>
+      <c r="J14" t="s">
+        <v>376</v>
+      </c>
+      <c r="K14" t="s">
+        <v>378</v>
+      </c>
+      <c r="L14" t="s">
+        <v>345</v>
+      </c>
+      <c r="M14" t="s">
         <v>62</v>
-      </c>
-      <c r="E14" t="s">
-        <v>379</v>
-      </c>
-      <c r="F14" t="s">
-        <v>409</v>
-      </c>
-      <c r="G14" t="s">
-        <v>390</v>
-      </c>
-      <c r="H14" t="s">
-        <v>408</v>
-      </c>
-      <c r="I14" t="s">
-        <v>377</v>
-      </c>
-      <c r="J14" t="s">
-        <v>378</v>
-      </c>
-      <c r="K14" t="s">
-        <v>380</v>
-      </c>
-      <c r="L14" t="s">
-        <v>347</v>
-      </c>
-      <c r="M14" t="s">
-        <v>64</v>
       </c>
       <c r="O14">
         <v>450</v>
       </c>
       <c r="P14" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="Q14" t="s">
         <v>10</v>
       </c>
       <c r="R14" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="S14" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="V14" s="5" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="W14" t="s">
         <v>13</v>
@@ -3208,63 +3240,63 @@
         <v>46032</v>
       </c>
       <c r="Z14" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B15" t="s">
+        <v>64</v>
+      </c>
+      <c r="C15" t="s">
+        <v>425</v>
+      </c>
+      <c r="D15" t="s">
+        <v>65</v>
+      </c>
+      <c r="E15" t="s">
+        <v>431</v>
+      </c>
+      <c r="F15" t="s">
+        <v>406</v>
+      </c>
+      <c r="G15" t="s">
+        <v>388</v>
+      </c>
+      <c r="H15" t="s">
+        <v>409</v>
+      </c>
+      <c r="I15" t="s">
+        <v>410</v>
+      </c>
+      <c r="J15" t="s">
+        <v>411</v>
+      </c>
+      <c r="L15" t="s">
+        <v>345</v>
+      </c>
+      <c r="M15" t="s">
         <v>66</v>
-      </c>
-      <c r="C15" t="s">
-        <v>428</v>
-      </c>
-      <c r="D15" t="s">
-        <v>67</v>
-      </c>
-      <c r="E15" t="s">
-        <v>434</v>
-      </c>
-      <c r="F15" t="s">
-        <v>409</v>
-      </c>
-      <c r="G15" t="s">
-        <v>390</v>
-      </c>
-      <c r="H15" t="s">
-        <v>412</v>
-      </c>
-      <c r="I15" t="s">
-        <v>413</v>
-      </c>
-      <c r="J15" t="s">
-        <v>414</v>
-      </c>
-      <c r="L15" t="s">
-        <v>347</v>
-      </c>
-      <c r="M15" t="s">
-        <v>68</v>
       </c>
       <c r="O15">
         <v>207</v>
       </c>
       <c r="P15" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="Q15" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="R15" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="S15" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="V15" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="W15" t="s">
         <v>13</v>
@@ -3281,52 +3313,52 @@
     </row>
     <row r="16" spans="1:26" ht="18.75" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B16" t="s">
+        <v>68</v>
+      </c>
+      <c r="C16" t="s">
+        <v>425</v>
+      </c>
+      <c r="E16" t="s">
+        <v>533</v>
+      </c>
+      <c r="F16" t="s">
+        <v>412</v>
+      </c>
+      <c r="G16" t="s">
+        <v>392</v>
+      </c>
+      <c r="I16" t="s">
+        <v>413</v>
+      </c>
+      <c r="K16" t="s">
+        <v>381</v>
+      </c>
+      <c r="L16" t="s">
+        <v>345</v>
+      </c>
+      <c r="M16" t="s">
         <v>70</v>
-      </c>
-      <c r="C16" t="s">
-        <v>428</v>
-      </c>
-      <c r="E16" t="s">
-        <v>536</v>
-      </c>
-      <c r="F16" t="s">
-        <v>415</v>
-      </c>
-      <c r="G16" t="s">
-        <v>395</v>
-      </c>
-      <c r="I16" t="s">
-        <v>416</v>
-      </c>
-      <c r="K16" t="s">
-        <v>383</v>
-      </c>
-      <c r="L16" t="s">
-        <v>347</v>
-      </c>
-      <c r="M16" t="s">
-        <v>72</v>
       </c>
       <c r="O16">
         <v>2900</v>
       </c>
       <c r="P16" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="Q16" t="s">
         <v>17</v>
       </c>
       <c r="R16" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="S16" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="V16" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="W16" t="s">
         <v>13</v>
@@ -3343,58 +3375,58 @@
     </row>
     <row r="17" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B17" t="s">
+        <v>72</v>
+      </c>
+      <c r="C17" t="s">
+        <v>425</v>
+      </c>
+      <c r="E17" t="s">
+        <v>432</v>
+      </c>
+      <c r="F17" t="s">
+        <v>414</v>
+      </c>
+      <c r="G17" t="s">
+        <v>384</v>
+      </c>
+      <c r="H17" t="s">
+        <v>364</v>
+      </c>
+      <c r="I17" t="s">
+        <v>356</v>
+      </c>
+      <c r="J17" t="s">
+        <v>357</v>
+      </c>
+      <c r="L17" t="s">
+        <v>345</v>
+      </c>
+      <c r="M17" t="s">
         <v>74</v>
       </c>
-      <c r="C17" t="s">
-        <v>428</v>
-      </c>
-      <c r="E17" t="s">
-        <v>435</v>
-      </c>
-      <c r="F17" t="s">
-        <v>417</v>
-      </c>
-      <c r="G17" t="s">
-        <v>386</v>
-      </c>
-      <c r="H17" t="s">
-        <v>366</v>
-      </c>
-      <c r="I17" t="s">
-        <v>358</v>
-      </c>
-      <c r="J17" t="s">
-        <v>359</v>
-      </c>
-      <c r="L17" t="s">
-        <v>347</v>
-      </c>
-      <c r="M17" t="s">
-        <v>76</v>
-      </c>
       <c r="N17" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="O17">
         <v>75</v>
       </c>
       <c r="P17" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="Q17" t="s">
         <v>21</v>
       </c>
       <c r="R17" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="S17" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="V17" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="W17" t="s">
         <v>13</v>
@@ -3411,55 +3443,55 @@
     </row>
     <row r="18" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B18" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C18" t="s">
+        <v>78</v>
+      </c>
+      <c r="E18" t="s">
+        <v>415</v>
+      </c>
+      <c r="F18" t="s">
+        <v>350</v>
+      </c>
+      <c r="G18" t="s">
+        <v>416</v>
+      </c>
+      <c r="H18" t="s">
+        <v>417</v>
+      </c>
+      <c r="I18" t="s">
+        <v>418</v>
+      </c>
+      <c r="J18" t="s">
+        <v>354</v>
+      </c>
+      <c r="L18" t="s">
+        <v>345</v>
+      </c>
+      <c r="M18" t="s">
         <v>80</v>
-      </c>
-      <c r="E18" t="s">
-        <v>418</v>
-      </c>
-      <c r="F18" t="s">
-        <v>352</v>
-      </c>
-      <c r="G18" t="s">
-        <v>419</v>
-      </c>
-      <c r="H18" t="s">
-        <v>420</v>
-      </c>
-      <c r="I18" t="s">
-        <v>421</v>
-      </c>
-      <c r="J18" t="s">
-        <v>356</v>
-      </c>
-      <c r="L18" t="s">
-        <v>347</v>
-      </c>
-      <c r="M18" t="s">
-        <v>82</v>
       </c>
       <c r="O18">
         <v>156</v>
       </c>
       <c r="P18" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>40</v>
+      </c>
+      <c r="R18" t="s">
+        <v>346</v>
+      </c>
+      <c r="S18" t="s">
+        <v>424</v>
+      </c>
+      <c r="V18" t="s">
         <v>81</v>
-      </c>
-      <c r="Q18" t="s">
-        <v>42</v>
-      </c>
-      <c r="R18" t="s">
-        <v>348</v>
-      </c>
-      <c r="S18" t="s">
-        <v>427</v>
-      </c>
-      <c r="V18" t="s">
-        <v>83</v>
       </c>
       <c r="W18" t="s">
         <v>13</v>
@@ -3476,61 +3508,61 @@
     </row>
     <row r="19" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B19" t="s">
+        <v>82</v>
+      </c>
+      <c r="C19" t="s">
+        <v>83</v>
+      </c>
+      <c r="D19" t="s">
         <v>84</v>
       </c>
-      <c r="C19" t="s">
-        <v>85</v>
-      </c>
-      <c r="D19" t="s">
-        <v>86</v>
-      </c>
       <c r="E19" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="F19" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="G19" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="H19" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="I19" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="J19" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="L19" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="M19" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="O19">
         <v>341</v>
       </c>
       <c r="P19" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="Q19" t="s">
+        <v>86</v>
+      </c>
+      <c r="R19" t="s">
+        <v>349</v>
+      </c>
+      <c r="S19" t="s">
+        <v>424</v>
+      </c>
+      <c r="V19" t="s">
         <v>88</v>
       </c>
-      <c r="R19" t="s">
-        <v>351</v>
-      </c>
-      <c r="S19" t="s">
-        <v>427</v>
-      </c>
-      <c r="V19" t="s">
-        <v>90</v>
-      </c>
       <c r="W19" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="X19">
         <v>180</v>
@@ -3544,52 +3576,52 @@
     </row>
     <row r="20" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B20" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C20" t="s">
+        <v>91</v>
+      </c>
+      <c r="E20" t="s">
+        <v>367</v>
+      </c>
+      <c r="F20" t="s">
+        <v>369</v>
+      </c>
+      <c r="G20" t="s">
+        <v>438</v>
+      </c>
+      <c r="H20" t="s">
+        <v>368</v>
+      </c>
+      <c r="J20" t="s">
+        <v>348</v>
+      </c>
+      <c r="L20" t="s">
+        <v>343</v>
+      </c>
+      <c r="M20" t="s">
         <v>93</v>
-      </c>
-      <c r="E20" t="s">
-        <v>369</v>
-      </c>
-      <c r="F20" t="s">
-        <v>371</v>
-      </c>
-      <c r="G20" t="s">
-        <v>441</v>
-      </c>
-      <c r="H20" t="s">
-        <v>370</v>
-      </c>
-      <c r="J20" t="s">
-        <v>350</v>
-      </c>
-      <c r="L20" t="s">
-        <v>345</v>
-      </c>
-      <c r="M20" t="s">
-        <v>95</v>
       </c>
       <c r="O20">
         <v>1400</v>
       </c>
       <c r="P20" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="Q20" t="s">
         <v>17</v>
       </c>
       <c r="R20" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="S20" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="V20" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="W20" t="s">
         <v>13</v>
@@ -3606,55 +3638,55 @@
     </row>
     <row r="21" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B21" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C21" t="s">
+        <v>95</v>
+      </c>
+      <c r="E21" t="s">
+        <v>420</v>
+      </c>
+      <c r="F21" t="s">
+        <v>406</v>
+      </c>
+      <c r="G21" t="s">
+        <v>392</v>
+      </c>
+      <c r="H21" t="s">
+        <v>482</v>
+      </c>
+      <c r="I21" t="s">
+        <v>421</v>
+      </c>
+      <c r="J21" t="s">
+        <v>348</v>
+      </c>
+      <c r="L21" t="s">
+        <v>345</v>
+      </c>
+      <c r="M21" t="s">
         <v>97</v>
-      </c>
-      <c r="E21" t="s">
-        <v>423</v>
-      </c>
-      <c r="F21" t="s">
-        <v>409</v>
-      </c>
-      <c r="G21" t="s">
-        <v>395</v>
-      </c>
-      <c r="H21" t="s">
-        <v>485</v>
-      </c>
-      <c r="I21" t="s">
-        <v>424</v>
-      </c>
-      <c r="J21" t="s">
-        <v>350</v>
-      </c>
-      <c r="L21" t="s">
-        <v>347</v>
-      </c>
-      <c r="M21" t="s">
-        <v>99</v>
       </c>
       <c r="O21">
         <v>414</v>
       </c>
       <c r="P21" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="Q21" t="s">
+        <v>96</v>
+      </c>
+      <c r="R21" t="s">
+        <v>346</v>
+      </c>
+      <c r="S21" t="s">
+        <v>424</v>
+      </c>
+      <c r="V21" t="s">
         <v>98</v>
-      </c>
-      <c r="R21" t="s">
-        <v>348</v>
-      </c>
-      <c r="S21" t="s">
-        <v>427</v>
-      </c>
-      <c r="V21" t="s">
-        <v>100</v>
       </c>
       <c r="W21" t="s">
         <v>13</v>
@@ -3671,55 +3703,55 @@
     </row>
     <row r="22" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B22" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C22" t="s">
+        <v>99</v>
+      </c>
+      <c r="E22" t="s">
+        <v>420</v>
+      </c>
+      <c r="F22" t="s">
+        <v>406</v>
+      </c>
+      <c r="G22" t="s">
+        <v>392</v>
+      </c>
+      <c r="H22" t="s">
+        <v>482</v>
+      </c>
+      <c r="I22" t="s">
+        <v>422</v>
+      </c>
+      <c r="J22" t="s">
+        <v>348</v>
+      </c>
+      <c r="L22" t="s">
+        <v>345</v>
+      </c>
+      <c r="M22" t="s">
         <v>101</v>
-      </c>
-      <c r="E22" t="s">
-        <v>423</v>
-      </c>
-      <c r="F22" t="s">
-        <v>409</v>
-      </c>
-      <c r="G22" t="s">
-        <v>395</v>
-      </c>
-      <c r="H22" t="s">
-        <v>485</v>
-      </c>
-      <c r="I22" t="s">
-        <v>425</v>
-      </c>
-      <c r="J22" t="s">
-        <v>350</v>
-      </c>
-      <c r="L22" t="s">
-        <v>347</v>
-      </c>
-      <c r="M22" t="s">
-        <v>103</v>
       </c>
       <c r="O22">
         <v>950</v>
       </c>
       <c r="P22" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>49</v>
+      </c>
+      <c r="R22" t="s">
+        <v>346</v>
+      </c>
+      <c r="S22" t="s">
+        <v>424</v>
+      </c>
+      <c r="V22" t="s">
         <v>102</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>51</v>
-      </c>
-      <c r="R22" t="s">
-        <v>348</v>
-      </c>
-      <c r="S22" t="s">
-        <v>427</v>
-      </c>
-      <c r="V22" t="s">
-        <v>104</v>
       </c>
       <c r="W22" t="s">
         <v>13</v>
@@ -3736,55 +3768,55 @@
     </row>
     <row r="23" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B23" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C23" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E23" t="s">
+        <v>420</v>
+      </c>
+      <c r="F23" t="s">
+        <v>406</v>
+      </c>
+      <c r="G23" t="s">
+        <v>392</v>
+      </c>
+      <c r="H23" t="s">
+        <v>482</v>
+      </c>
+      <c r="I23" t="s">
         <v>423</v>
       </c>
-      <c r="F23" t="s">
-        <v>409</v>
-      </c>
-      <c r="G23" t="s">
-        <v>395</v>
-      </c>
-      <c r="H23" t="s">
-        <v>485</v>
-      </c>
-      <c r="I23" t="s">
-        <v>426</v>
-      </c>
       <c r="J23" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="L23" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="M23" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="O23">
         <v>1777</v>
       </c>
       <c r="P23" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="Q23" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R23" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="S23" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="V23" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="W23" t="s">
         <v>13</v>
@@ -3801,64 +3833,64 @@
     </row>
     <row r="24" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B24" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C24" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="D24" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E24" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="F24" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="G24" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="H24" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="I24" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="J24" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="L24" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="M24" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="N24" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="O24">
         <v>63</v>
       </c>
       <c r="P24" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="Q24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="R24" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="S24" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="V24" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="W24" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="X24">
         <v>70</v>
@@ -3872,58 +3904,58 @@
     </row>
     <row r="25" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B25" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C25" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="E25" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="F25" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="G25" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="H25" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="I25" t="s">
+        <v>370</v>
+      </c>
+      <c r="J25" t="s">
         <v>372</v>
       </c>
-      <c r="J25" t="s">
-        <v>374</v>
-      </c>
       <c r="K25" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="L25" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="M25" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="O25">
         <v>1000</v>
       </c>
       <c r="P25" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="Q25" t="s">
+        <v>115</v>
+      </c>
+      <c r="R25" t="s">
+        <v>346</v>
+      </c>
+      <c r="S25" t="s">
+        <v>424</v>
+      </c>
+      <c r="V25" t="s">
         <v>117</v>
-      </c>
-      <c r="R25" t="s">
-        <v>348</v>
-      </c>
-      <c r="S25" t="s">
-        <v>427</v>
-      </c>
-      <c r="V25" t="s">
-        <v>119</v>
       </c>
       <c r="W25" t="s">
         <v>13</v>
@@ -3940,58 +3972,58 @@
     </row>
     <row r="26" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B26" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C26" t="s">
+        <v>119</v>
+      </c>
+      <c r="E26" t="s">
+        <v>440</v>
+      </c>
+      <c r="F26" t="s">
+        <v>350</v>
+      </c>
+      <c r="G26" t="s">
+        <v>441</v>
+      </c>
+      <c r="H26" t="s">
+        <v>471</v>
+      </c>
+      <c r="I26" t="s">
+        <v>442</v>
+      </c>
+      <c r="J26" t="s">
+        <v>348</v>
+      </c>
+      <c r="K26" t="s">
+        <v>352</v>
+      </c>
+      <c r="L26" s="4" t="s">
+        <v>498</v>
+      </c>
+      <c r="M26" t="s">
         <v>121</v>
-      </c>
-      <c r="E26" t="s">
-        <v>443</v>
-      </c>
-      <c r="F26" t="s">
-        <v>352</v>
-      </c>
-      <c r="G26" t="s">
-        <v>444</v>
-      </c>
-      <c r="H26" t="s">
-        <v>474</v>
-      </c>
-      <c r="I26" t="s">
-        <v>445</v>
-      </c>
-      <c r="J26" t="s">
-        <v>350</v>
-      </c>
-      <c r="K26" t="s">
-        <v>354</v>
-      </c>
-      <c r="L26" s="4" t="s">
-        <v>501</v>
-      </c>
-      <c r="M26" t="s">
-        <v>123</v>
       </c>
       <c r="O26">
         <v>370</v>
       </c>
       <c r="P26" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="Q26" t="s">
         <v>17</v>
       </c>
       <c r="R26" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="S26" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="V26" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="W26" t="s">
         <v>13</v>
@@ -4008,58 +4040,58 @@
     </row>
     <row r="27" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B27" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C27" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E27" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F27" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="G27" t="s">
+        <v>441</v>
+      </c>
+      <c r="H27" t="s">
+        <v>471</v>
+      </c>
+      <c r="I27" t="s">
         <v>444</v>
       </c>
-      <c r="H27" t="s">
-        <v>474</v>
-      </c>
-      <c r="I27" t="s">
-        <v>447</v>
-      </c>
       <c r="J27" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="K27" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="L27" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="M27" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="O27">
         <v>90</v>
       </c>
       <c r="P27" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="Q27" t="s">
         <v>17</v>
       </c>
       <c r="R27" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="S27" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="V27" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="X27">
         <v>30</v>
@@ -4073,58 +4105,58 @@
     </row>
     <row r="28" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B28" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C28" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D28" t="s">
+        <v>127</v>
+      </c>
+      <c r="E28" t="s">
+        <v>420</v>
+      </c>
+      <c r="F28" t="s">
+        <v>406</v>
+      </c>
+      <c r="G28" t="s">
+        <v>392</v>
+      </c>
+      <c r="H28" t="s">
+        <v>482</v>
+      </c>
+      <c r="I28" t="s">
+        <v>359</v>
+      </c>
+      <c r="J28" t="s">
+        <v>348</v>
+      </c>
+      <c r="L28" t="s">
+        <v>345</v>
+      </c>
+      <c r="M28" t="s">
         <v>129</v>
-      </c>
-      <c r="E28" t="s">
-        <v>423</v>
-      </c>
-      <c r="F28" t="s">
-        <v>409</v>
-      </c>
-      <c r="G28" t="s">
-        <v>395</v>
-      </c>
-      <c r="H28" t="s">
-        <v>485</v>
-      </c>
-      <c r="I28" t="s">
-        <v>361</v>
-      </c>
-      <c r="J28" t="s">
-        <v>350</v>
-      </c>
-      <c r="L28" t="s">
-        <v>347</v>
-      </c>
-      <c r="M28" t="s">
-        <v>131</v>
       </c>
       <c r="O28">
         <v>1700</v>
       </c>
       <c r="P28" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>36</v>
+      </c>
+      <c r="R28" t="s">
+        <v>346</v>
+      </c>
+      <c r="S28" t="s">
+        <v>424</v>
+      </c>
+      <c r="V28" t="s">
         <v>130</v>
-      </c>
-      <c r="Q28" t="s">
-        <v>38</v>
-      </c>
-      <c r="R28" t="s">
-        <v>348</v>
-      </c>
-      <c r="S28" t="s">
-        <v>427</v>
-      </c>
-      <c r="V28" t="s">
-        <v>132</v>
       </c>
       <c r="W28" t="s">
         <v>13</v>
@@ -4141,58 +4173,58 @@
     </row>
     <row r="29" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B29" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C29" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E29" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="F29" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="G29" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="H29" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="I29" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="J29" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="L29" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="M29" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="O29">
         <v>225</v>
       </c>
       <c r="P29" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="Q29" t="s">
+        <v>133</v>
+      </c>
+      <c r="R29" t="s">
+        <v>346</v>
+      </c>
+      <c r="S29" t="s">
+        <v>424</v>
+      </c>
+      <c r="V29" t="s">
         <v>135</v>
       </c>
-      <c r="R29" t="s">
-        <v>348</v>
-      </c>
-      <c r="S29" t="s">
-        <v>427</v>
-      </c>
-      <c r="V29" t="s">
-        <v>137</v>
-      </c>
       <c r="W29" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="X29">
         <v>50</v>
@@ -4206,55 +4238,55 @@
     </row>
     <row r="30" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B30" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C30" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="E30" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="F30" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="G30" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="H30" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="I30" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="J30" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="L30" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="M30" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="O30">
         <v>160</v>
       </c>
       <c r="P30" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="Q30" t="s">
         <v>21</v>
       </c>
       <c r="R30" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="S30" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="V30" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="W30" t="s">
         <v>13</v>
@@ -4271,55 +4303,55 @@
     </row>
     <row r="31" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B31" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C31" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E31" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="F31" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="G31" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="H31" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="J31" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="K31" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="L31" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="M31" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="O31">
         <v>125</v>
       </c>
       <c r="P31" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="Q31" t="s">
         <v>17</v>
       </c>
       <c r="R31" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="S31" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="V31" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="X31">
         <v>70</v>
@@ -4333,58 +4365,58 @@
     </row>
     <row r="32" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B32" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C32" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E32" t="s">
+        <v>394</v>
+      </c>
+      <c r="F32" t="s">
+        <v>350</v>
+      </c>
+      <c r="G32" t="s">
+        <v>395</v>
+      </c>
+      <c r="H32" t="s">
+        <v>396</v>
+      </c>
+      <c r="I32" t="s">
         <v>397</v>
       </c>
-      <c r="F32" t="s">
-        <v>352</v>
-      </c>
-      <c r="G32" t="s">
-        <v>398</v>
-      </c>
-      <c r="H32" t="s">
-        <v>399</v>
-      </c>
-      <c r="I32" t="s">
-        <v>400</v>
-      </c>
       <c r="J32" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="K32" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="L32" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="M32" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="O32">
         <v>24</v>
       </c>
       <c r="P32" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="Q32" t="s">
         <v>17</v>
       </c>
       <c r="R32" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="S32" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="V32" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="X32">
         <v>15</v>
@@ -4398,58 +4430,58 @@
     </row>
     <row r="33" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B33" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C33" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E33" t="s">
+        <v>367</v>
+      </c>
+      <c r="F33" t="s">
         <v>369</v>
       </c>
-      <c r="F33" t="s">
-        <v>371</v>
-      </c>
       <c r="G33" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="H33" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="J33" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="K33" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="L33" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="M33" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="O33">
         <v>115</v>
       </c>
       <c r="P33" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="Q33" t="s">
         <v>17</v>
       </c>
       <c r="R33" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="S33" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="V33" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="W33" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="X33">
         <v>25</v>
@@ -4463,58 +4495,58 @@
     </row>
     <row r="34" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B34" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C34" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E34" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F34" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="G34" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="H34" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="I34" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="J34" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="K34" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="L34" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="M34" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="O34">
         <v>4120</v>
       </c>
       <c r="P34" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="Q34" t="s">
         <v>17</v>
       </c>
       <c r="R34" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="S34" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="V34" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="W34" t="s">
         <v>13</v>
@@ -4531,55 +4563,55 @@
     </row>
     <row r="35" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B35" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C35" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="E35" t="s">
+        <v>453</v>
+      </c>
+      <c r="F35" t="s">
+        <v>454</v>
+      </c>
+      <c r="G35" t="s">
+        <v>399</v>
+      </c>
+      <c r="H35" t="s">
+        <v>455</v>
+      </c>
+      <c r="I35" t="s">
         <v>456</v>
       </c>
-      <c r="F35" t="s">
-        <v>457</v>
-      </c>
-      <c r="G35" t="s">
-        <v>402</v>
-      </c>
-      <c r="H35" t="s">
-        <v>458</v>
-      </c>
-      <c r="I35" t="s">
-        <v>459</v>
-      </c>
       <c r="K35" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="L35" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="M35" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="O35">
         <v>565</v>
       </c>
       <c r="P35" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="Q35" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="R35" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="S35" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="V35" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="W35" t="s">
         <v>13</v>
@@ -4596,58 +4628,58 @@
     </row>
     <row r="36" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B36" t="s">
+        <v>151</v>
+      </c>
+      <c r="C36" t="s">
+        <v>425</v>
+      </c>
+      <c r="E36" t="s">
+        <v>457</v>
+      </c>
+      <c r="F36" t="s">
+        <v>385</v>
+      </c>
+      <c r="G36" t="s">
+        <v>399</v>
+      </c>
+      <c r="H36" t="s">
+        <v>496</v>
+      </c>
+      <c r="I36" t="s">
+        <v>359</v>
+      </c>
+      <c r="J36" t="s">
+        <v>360</v>
+      </c>
+      <c r="K36" t="s">
+        <v>468</v>
+      </c>
+      <c r="L36" t="s">
+        <v>345</v>
+      </c>
+      <c r="M36" t="s">
         <v>153</v>
-      </c>
-      <c r="C36" t="s">
-        <v>428</v>
-      </c>
-      <c r="E36" t="s">
-        <v>460</v>
-      </c>
-      <c r="F36" t="s">
-        <v>387</v>
-      </c>
-      <c r="G36" t="s">
-        <v>402</v>
-      </c>
-      <c r="H36" t="s">
-        <v>499</v>
-      </c>
-      <c r="I36" t="s">
-        <v>361</v>
-      </c>
-      <c r="J36" t="s">
-        <v>362</v>
-      </c>
-      <c r="K36" t="s">
-        <v>471</v>
-      </c>
-      <c r="L36" t="s">
-        <v>347</v>
-      </c>
-      <c r="M36" t="s">
-        <v>155</v>
       </c>
       <c r="O36">
         <v>5400</v>
       </c>
       <c r="P36" t="s">
+        <v>152</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>86</v>
+      </c>
+      <c r="R36" t="s">
+        <v>346</v>
+      </c>
+      <c r="S36" t="s">
+        <v>424</v>
+      </c>
+      <c r="V36" t="s">
         <v>154</v>
-      </c>
-      <c r="Q36" t="s">
-        <v>88</v>
-      </c>
-      <c r="R36" t="s">
-        <v>348</v>
-      </c>
-      <c r="S36" t="s">
-        <v>427</v>
-      </c>
-      <c r="V36" t="s">
-        <v>156</v>
       </c>
       <c r="W36" t="s">
         <v>13</v>
@@ -4664,52 +4696,52 @@
     </row>
     <row r="37" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B37" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C37" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E37" t="s">
+        <v>367</v>
+      </c>
+      <c r="F37" t="s">
         <v>369</v>
       </c>
-      <c r="F37" t="s">
-        <v>371</v>
-      </c>
       <c r="G37" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="H37" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="K37" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="L37" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="M37" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="O37">
         <v>2064</v>
       </c>
       <c r="P37" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="Q37" t="s">
         <v>21</v>
       </c>
       <c r="R37" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="S37" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="V37" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="W37" t="s">
         <v>13</v>
@@ -4726,52 +4758,52 @@
     </row>
     <row r="38" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B38" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C38" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E38" t="s">
+        <v>367</v>
+      </c>
+      <c r="F38" t="s">
         <v>369</v>
       </c>
-      <c r="F38" t="s">
-        <v>371</v>
-      </c>
       <c r="G38" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="H38" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="K38" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="L38" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="M38" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="O38">
         <v>109</v>
       </c>
       <c r="P38" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="Q38" t="s">
         <v>21</v>
       </c>
       <c r="R38" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="S38" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="V38" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="X38">
         <v>15</v>
@@ -4785,52 +4817,52 @@
     </row>
     <row r="39" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B39" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C39" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E39" t="s">
+        <v>367</v>
+      </c>
+      <c r="F39" t="s">
         <v>369</v>
       </c>
-      <c r="F39" t="s">
-        <v>371</v>
-      </c>
       <c r="G39" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="H39" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="K39" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="L39" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="M39" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="O39">
         <v>300</v>
       </c>
       <c r="P39" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="Q39" t="s">
         <v>21</v>
       </c>
       <c r="R39" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="S39" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="V39" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="X39">
         <v>25</v>
@@ -4844,52 +4876,52 @@
     </row>
     <row r="40" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B40" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C40" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E40" t="s">
+        <v>367</v>
+      </c>
+      <c r="F40" t="s">
         <v>369</v>
       </c>
-      <c r="F40" t="s">
-        <v>371</v>
-      </c>
       <c r="G40" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="H40" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="K40" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="L40" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="M40" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="O40">
         <v>115</v>
       </c>
       <c r="P40" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="Q40" t="s">
         <v>21</v>
       </c>
       <c r="R40" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="S40" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="V40" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="X40">
         <v>15</v>
@@ -4903,55 +4935,55 @@
     </row>
     <row r="41" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B41" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C41" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="E41" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="F41" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="G41" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="H41" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="I41" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="K41" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="L41" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="M41" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="O41">
         <v>819</v>
       </c>
       <c r="P41" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="Q41" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="R41" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="S41" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="V41" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="W41" t="s">
         <v>13</v>
@@ -4968,55 +5000,55 @@
     </row>
     <row r="42" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B42" t="s">
+        <v>167</v>
+      </c>
+      <c r="C42" t="s">
+        <v>425</v>
+      </c>
+      <c r="E42" t="s">
+        <v>461</v>
+      </c>
+      <c r="F42" t="s">
+        <v>385</v>
+      </c>
+      <c r="G42" t="s">
+        <v>438</v>
+      </c>
+      <c r="H42" t="s">
+        <v>462</v>
+      </c>
+      <c r="I42" t="s">
+        <v>463</v>
+      </c>
+      <c r="J42" t="s">
+        <v>348</v>
+      </c>
+      <c r="K42" t="s">
+        <v>381</v>
+      </c>
+      <c r="L42" t="s">
+        <v>345</v>
+      </c>
+      <c r="M42" t="s">
         <v>169</v>
-      </c>
-      <c r="C42" t="s">
-        <v>428</v>
-      </c>
-      <c r="E42" t="s">
-        <v>464</v>
-      </c>
-      <c r="F42" t="s">
-        <v>387</v>
-      </c>
-      <c r="G42" t="s">
-        <v>441</v>
-      </c>
-      <c r="H42" t="s">
-        <v>465</v>
-      </c>
-      <c r="I42" t="s">
-        <v>466</v>
-      </c>
-      <c r="J42" t="s">
-        <v>350</v>
-      </c>
-      <c r="K42" t="s">
-        <v>383</v>
-      </c>
-      <c r="L42" t="s">
-        <v>347</v>
-      </c>
-      <c r="M42" t="s">
-        <v>171</v>
       </c>
       <c r="O42">
         <v>700</v>
       </c>
       <c r="P42" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="Q42" t="s">
         <v>17</v>
       </c>
       <c r="R42" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="S42" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="T42" s="1">
         <v>45199</v>
@@ -5025,10 +5057,10 @@
         <v>50</v>
       </c>
       <c r="V42" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="W42" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="X42">
         <v>150</v>
@@ -5042,52 +5074,52 @@
     </row>
     <row r="43" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B43" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C43" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="E43" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="F43" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="G43" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="H43" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="I43" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="K43" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="L43" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="M43" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="O43">
         <v>450</v>
       </c>
       <c r="P43" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="Q43" t="s">
         <v>17</v>
       </c>
       <c r="R43" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="S43" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="T43" s="1">
         <v>45199</v>
@@ -5096,10 +5128,10 @@
         <v>50</v>
       </c>
       <c r="V43" t="s">
-        <v>538</v>
+        <v>559</v>
       </c>
       <c r="W43" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="X43">
         <v>120</v>
@@ -5113,58 +5145,58 @@
     </row>
     <row r="44" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B44" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C44" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="E44" t="s">
+        <v>394</v>
+      </c>
+      <c r="F44" t="s">
+        <v>350</v>
+      </c>
+      <c r="G44" t="s">
+        <v>395</v>
+      </c>
+      <c r="H44" t="s">
+        <v>396</v>
+      </c>
+      <c r="I44" t="s">
         <v>397</v>
       </c>
-      <c r="F44" t="s">
-        <v>352</v>
-      </c>
-      <c r="G44" t="s">
-        <v>398</v>
-      </c>
-      <c r="H44" t="s">
-        <v>399</v>
-      </c>
-      <c r="I44" t="s">
-        <v>400</v>
-      </c>
       <c r="J44" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="K44" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="L44" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="M44" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="N44" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="O44">
         <v>1100</v>
       </c>
       <c r="P44" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="Q44" t="s">
         <v>17</v>
       </c>
       <c r="R44" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="S44" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="T44" s="1">
         <v>45199</v>
@@ -5173,10 +5205,10 @@
         <v>50</v>
       </c>
       <c r="V44" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="W44" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="X44">
         <v>200</v>
@@ -5190,55 +5222,55 @@
     </row>
     <row r="45" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B45" t="s">
+        <v>176</v>
+      </c>
+      <c r="C45" t="s">
+        <v>425</v>
+      </c>
+      <c r="D45" t="s">
+        <v>68</v>
+      </c>
+      <c r="E45" t="s">
+        <v>464</v>
+      </c>
+      <c r="F45" t="s">
+        <v>406</v>
+      </c>
+      <c r="G45" t="s">
+        <v>388</v>
+      </c>
+      <c r="H45" t="s">
+        <v>465</v>
+      </c>
+      <c r="I45" t="s">
+        <v>466</v>
+      </c>
+      <c r="K45" t="s">
+        <v>381</v>
+      </c>
+      <c r="L45" t="s">
+        <v>345</v>
+      </c>
+      <c r="M45" t="s">
         <v>178</v>
-      </c>
-      <c r="C45" t="s">
-        <v>428</v>
-      </c>
-      <c r="D45" t="s">
-        <v>70</v>
-      </c>
-      <c r="E45" t="s">
-        <v>467</v>
-      </c>
-      <c r="F45" t="s">
-        <v>409</v>
-      </c>
-      <c r="G45" t="s">
-        <v>390</v>
-      </c>
-      <c r="H45" t="s">
-        <v>468</v>
-      </c>
-      <c r="I45" t="s">
-        <v>469</v>
-      </c>
-      <c r="K45" t="s">
-        <v>383</v>
-      </c>
-      <c r="L45" t="s">
-        <v>347</v>
-      </c>
-      <c r="M45" t="s">
-        <v>180</v>
       </c>
       <c r="O45">
         <v>260</v>
       </c>
       <c r="P45" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="Q45" t="s">
         <v>17</v>
       </c>
       <c r="R45" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="S45" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="T45" s="1">
         <v>45213</v>
@@ -5247,10 +5279,10 @@
         <v>40</v>
       </c>
       <c r="V45" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="W45" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="X45">
         <v>50</v>
@@ -5264,55 +5296,55 @@
     </row>
     <row r="46" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B46" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C46" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="E46" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="F46" t="s">
+        <v>385</v>
+      </c>
+      <c r="G46" t="s">
+        <v>388</v>
+      </c>
+      <c r="H46" t="s">
         <v>387</v>
       </c>
-      <c r="G46" t="s">
-        <v>390</v>
-      </c>
-      <c r="H46" t="s">
-        <v>389</v>
-      </c>
       <c r="I46" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="J46" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="K46" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="L46" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="M46" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="O46">
         <v>110</v>
       </c>
       <c r="P46" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="Q46" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="R46" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="S46" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="T46" s="1">
         <v>45215</v>
@@ -5321,10 +5353,10 @@
         <v>65</v>
       </c>
       <c r="V46" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="W46" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="X46">
         <v>95</v>
@@ -5338,49 +5370,49 @@
     </row>
     <row r="47" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B47" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C47" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E47" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="F47" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="G47" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="H47" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="K47" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="L47" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="M47" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="O47">
         <v>100</v>
       </c>
       <c r="P47" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="Q47" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="R47" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="S47" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="T47" s="1">
         <v>45233</v>
@@ -5389,10 +5421,10 @@
         <v>60</v>
       </c>
       <c r="V47" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="W47" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="X47">
         <v>85</v>
@@ -5406,46 +5438,46 @@
     </row>
     <row r="48" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B48" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C48" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="E48" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="F48" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="G48" t="s">
+        <v>399</v>
+      </c>
+      <c r="H48" t="s">
         <v>402</v>
       </c>
-      <c r="H48" t="s">
-        <v>405</v>
-      </c>
       <c r="L48" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="M48" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="O48">
         <v>123</v>
       </c>
       <c r="P48" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="Q48" t="s">
         <v>17</v>
       </c>
       <c r="R48" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="S48" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="T48" s="1">
         <v>45233</v>
@@ -5454,10 +5486,10 @@
         <v>20</v>
       </c>
       <c r="V48" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="W48" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="X48">
         <v>30</v>
@@ -5471,55 +5503,55 @@
     </row>
     <row r="49" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B49" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C49" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E49" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="F49" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="G49" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="H49" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="I49" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="J49" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="K49" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="L49" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="M49" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="N49" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="O49">
         <v>155</v>
       </c>
       <c r="P49" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="R49" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="S49" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="T49" s="1">
         <v>45236</v>
@@ -5528,10 +5560,10 @@
         <v>55</v>
       </c>
       <c r="V49" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="W49" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="X49">
         <v>65</v>
@@ -5545,52 +5577,52 @@
     </row>
     <row r="50" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B50" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C50" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E50" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F50" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="G50" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="H50" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="I50" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="J50" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="L50" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="M50" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="O50">
         <v>790</v>
       </c>
       <c r="P50" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="Q50" t="s">
         <v>17</v>
       </c>
       <c r="R50" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="S50" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="T50" s="1">
         <v>45247</v>
@@ -5599,10 +5631,10 @@
         <v>50</v>
       </c>
       <c r="V50" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="W50" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="X50">
         <v>140</v>
@@ -5616,58 +5648,58 @@
     </row>
     <row r="51" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B51" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C51" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="E51" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="F51" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="G51" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="H51" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="I51" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="J51" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="L51" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="M51" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="O51">
         <v>3900</v>
       </c>
       <c r="P51" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="Q51" t="s">
+        <v>201</v>
+      </c>
+      <c r="R51" t="s">
+        <v>346</v>
+      </c>
+      <c r="S51" t="s">
+        <v>424</v>
+      </c>
+      <c r="V51" t="s">
         <v>203</v>
       </c>
-      <c r="R51" t="s">
-        <v>348</v>
-      </c>
-      <c r="S51" t="s">
-        <v>427</v>
-      </c>
-      <c r="V51" t="s">
-        <v>205</v>
-      </c>
       <c r="W51" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="X51">
         <v>85</v>
@@ -5681,61 +5713,61 @@
     </row>
     <row r="52" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B52" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C52" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E52" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="F52" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="G52" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="H52" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="I52" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="J52" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="K52" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="L52" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="M52" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="O52">
         <v>1850</v>
       </c>
       <c r="P52" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="Q52" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="R52" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="S52" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="V52" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="W52" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="X52">
         <v>130</v>
@@ -5749,58 +5781,58 @@
     </row>
     <row r="53" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B53" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C53" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="E53" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="F53" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="G53" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="H53" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="I53" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="J53" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="L53" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="M53" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="O53">
         <v>350</v>
       </c>
       <c r="P53" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="Q53" t="s">
         <v>21</v>
       </c>
       <c r="R53" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="S53" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="V53" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="W53" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="X53">
         <v>35</v>
@@ -5814,58 +5846,58 @@
     </row>
     <row r="54" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B54" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C54" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E54" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="F54" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="G54" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="H54" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="I54" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="J54" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="L54" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="M54" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="O54">
         <v>269</v>
       </c>
       <c r="P54" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="Q54" t="s">
         <v>21</v>
       </c>
       <c r="R54" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="S54" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="V54" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="W54" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="X54">
         <v>20</v>
@@ -5879,58 +5911,58 @@
     </row>
     <row r="55" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B55" t="s">
+        <v>215</v>
+      </c>
+      <c r="C55" t="s">
+        <v>216</v>
+      </c>
+      <c r="D55" t="s">
+        <v>84</v>
+      </c>
+      <c r="E55" t="s">
+        <v>479</v>
+      </c>
+      <c r="F55" t="s">
+        <v>391</v>
+      </c>
+      <c r="G55" t="s">
+        <v>399</v>
+      </c>
+      <c r="H55" t="s">
+        <v>480</v>
+      </c>
+      <c r="I55" t="s">
+        <v>362</v>
+      </c>
+      <c r="J55" t="s">
+        <v>363</v>
+      </c>
+      <c r="L55" t="s">
+        <v>345</v>
+      </c>
+      <c r="M55" t="s">
         <v>217</v>
       </c>
-      <c r="C55" t="s">
+      <c r="N55" t="s">
         <v>218</v>
-      </c>
-      <c r="D55" t="s">
-        <v>86</v>
-      </c>
-      <c r="E55" t="s">
-        <v>482</v>
-      </c>
-      <c r="F55" t="s">
-        <v>394</v>
-      </c>
-      <c r="G55" t="s">
-        <v>402</v>
-      </c>
-      <c r="H55" t="s">
-        <v>483</v>
-      </c>
-      <c r="I55" t="s">
-        <v>364</v>
-      </c>
-      <c r="J55" t="s">
-        <v>365</v>
-      </c>
-      <c r="L55" t="s">
-        <v>347</v>
-      </c>
-      <c r="M55" t="s">
-        <v>219</v>
-      </c>
-      <c r="N55" t="s">
-        <v>220</v>
       </c>
       <c r="O55">
         <v>200</v>
       </c>
       <c r="P55" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="Q55" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="R55" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="S55" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="T55" s="1">
         <v>45267</v>
@@ -5939,10 +5971,10 @@
         <v>40</v>
       </c>
       <c r="V55" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="W55" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="X55">
         <v>120</v>
@@ -5956,55 +5988,55 @@
     </row>
     <row r="56" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B56" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C56" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="E56" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="F56" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="G56" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="H56" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="I56" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="J56" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="K56" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="L56" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="M56" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="O56">
         <v>375</v>
       </c>
       <c r="P56" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="Q56" t="s">
         <v>21</v>
       </c>
       <c r="R56" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="S56" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="T56" s="1">
         <v>45267</v>
@@ -6013,10 +6045,10 @@
         <v>25</v>
       </c>
       <c r="V56" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="W56" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="X56">
         <v>65</v>
@@ -6030,52 +6062,52 @@
     </row>
     <row r="57" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B57" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C57" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E57" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="F57" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="G57" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="H57" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="I57" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J57" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="L57" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="M57" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="O57">
         <v>510</v>
       </c>
       <c r="P57" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="Q57" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R57" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="S57" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="T57" s="1">
         <v>45267</v>
@@ -6084,10 +6116,10 @@
         <v>15</v>
       </c>
       <c r="V57" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="W57" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="X57">
         <v>45</v>
@@ -6101,55 +6133,55 @@
     </row>
     <row r="58" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B58" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C58" t="s">
+        <v>224</v>
+      </c>
+      <c r="E58" t="s">
+        <v>420</v>
+      </c>
+      <c r="F58" t="s">
+        <v>406</v>
+      </c>
+      <c r="G58" t="s">
+        <v>392</v>
+      </c>
+      <c r="H58" t="s">
+        <v>482</v>
+      </c>
+      <c r="I58" t="s">
+        <v>485</v>
+      </c>
+      <c r="J58" t="s">
+        <v>348</v>
+      </c>
+      <c r="K58" t="s">
+        <v>381</v>
+      </c>
+      <c r="L58" t="s">
+        <v>345</v>
+      </c>
+      <c r="M58" t="s">
         <v>226</v>
-      </c>
-      <c r="E58" t="s">
-        <v>423</v>
-      </c>
-      <c r="F58" t="s">
-        <v>409</v>
-      </c>
-      <c r="G58" t="s">
-        <v>395</v>
-      </c>
-      <c r="H58" t="s">
-        <v>485</v>
-      </c>
-      <c r="I58" t="s">
-        <v>488</v>
-      </c>
-      <c r="J58" t="s">
-        <v>350</v>
-      </c>
-      <c r="K58" t="s">
-        <v>383</v>
-      </c>
-      <c r="L58" t="s">
-        <v>347</v>
-      </c>
-      <c r="M58" t="s">
-        <v>228</v>
       </c>
       <c r="O58">
         <v>215</v>
       </c>
       <c r="P58" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="Q58" t="s">
         <v>21</v>
       </c>
       <c r="R58" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="S58" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="T58" s="1">
         <v>45269</v>
@@ -6158,10 +6190,10 @@
         <v>35</v>
       </c>
       <c r="V58" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="W58" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="X58">
         <v>60</v>
@@ -6175,58 +6207,58 @@
     </row>
     <row r="59" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B59" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="C59" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="D59" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E59" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="F59" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="G59" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="H59" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="I59" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="J59" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="K59" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="L59" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="M59" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="O59">
         <v>92</v>
       </c>
       <c r="P59" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="Q59" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="R59" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="S59" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="T59" s="1">
         <v>45571</v>
@@ -6235,10 +6267,10 @@
         <v>60</v>
       </c>
       <c r="V59" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="W59" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="X59">
         <v>70</v>
@@ -6252,52 +6284,52 @@
     </row>
     <row r="60" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B60" t="s">
+        <v>233</v>
+      </c>
+      <c r="C60" t="s">
+        <v>425</v>
+      </c>
+      <c r="D60" t="s">
+        <v>56</v>
+      </c>
+      <c r="E60" t="s">
+        <v>493</v>
+      </c>
+      <c r="F60" t="s">
+        <v>385</v>
+      </c>
+      <c r="G60" t="s">
+        <v>399</v>
+      </c>
+      <c r="H60" t="s">
+        <v>487</v>
+      </c>
+      <c r="I60" t="s">
+        <v>373</v>
+      </c>
+      <c r="L60" t="s">
+        <v>345</v>
+      </c>
+      <c r="M60" t="s">
         <v>235</v>
-      </c>
-      <c r="C60" t="s">
-        <v>428</v>
-      </c>
-      <c r="D60" t="s">
-        <v>58</v>
-      </c>
-      <c r="E60" t="s">
-        <v>496</v>
-      </c>
-      <c r="F60" t="s">
-        <v>387</v>
-      </c>
-      <c r="G60" t="s">
-        <v>402</v>
-      </c>
-      <c r="H60" t="s">
-        <v>490</v>
-      </c>
-      <c r="I60" t="s">
-        <v>375</v>
-      </c>
-      <c r="L60" t="s">
-        <v>347</v>
-      </c>
-      <c r="M60" t="s">
-        <v>237</v>
       </c>
       <c r="O60">
         <v>250</v>
       </c>
       <c r="P60" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="Q60" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="R60" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="S60" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="T60" s="1">
         <v>45591</v>
@@ -6306,10 +6338,10 @@
         <v>35</v>
       </c>
       <c r="V60" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="W60" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="X60">
         <v>90</v>
@@ -6323,55 +6355,55 @@
     </row>
     <row r="61" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B61" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C61" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="E61" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="F61" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="G61" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="H61" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="I61" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="J61" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="L61" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="M61" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="N61" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="O61">
         <v>200</v>
       </c>
       <c r="P61" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="Q61" t="s">
         <v>21</v>
       </c>
       <c r="R61" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="S61" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="T61" s="1">
         <v>45635</v>
@@ -6380,10 +6412,10 @@
         <v>36</v>
       </c>
       <c r="V61" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="W61" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="X61">
         <v>100</v>
@@ -6392,57 +6424,57 @@
         <v>46031</v>
       </c>
       <c r="Z61" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="62" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B62" t="s">
+        <v>243</v>
+      </c>
+      <c r="C62" t="s">
+        <v>425</v>
+      </c>
+      <c r="D62" t="s">
+        <v>65</v>
+      </c>
+      <c r="E62" t="s">
+        <v>428</v>
+      </c>
+      <c r="F62" t="s">
+        <v>454</v>
+      </c>
+      <c r="G62" t="s">
+        <v>399</v>
+      </c>
+      <c r="H62" t="s">
+        <v>488</v>
+      </c>
+      <c r="I62" t="s">
+        <v>180</v>
+      </c>
+      <c r="L62" t="s">
+        <v>345</v>
+      </c>
+      <c r="M62" t="s">
         <v>245</v>
-      </c>
-      <c r="C62" t="s">
-        <v>428</v>
-      </c>
-      <c r="D62" t="s">
-        <v>67</v>
-      </c>
-      <c r="E62" t="s">
-        <v>431</v>
-      </c>
-      <c r="F62" t="s">
-        <v>457</v>
-      </c>
-      <c r="G62" t="s">
-        <v>402</v>
-      </c>
-      <c r="H62" t="s">
-        <v>491</v>
-      </c>
-      <c r="I62" t="s">
-        <v>182</v>
-      </c>
-      <c r="L62" t="s">
-        <v>347</v>
-      </c>
-      <c r="M62" t="s">
-        <v>247</v>
       </c>
       <c r="O62">
         <v>370</v>
       </c>
       <c r="P62" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="Q62" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R62" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="S62" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="T62" s="1">
         <v>45646</v>
@@ -6451,10 +6483,10 @@
         <v>50</v>
       </c>
       <c r="V62" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="W62" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="X62">
         <v>110</v>
@@ -6468,58 +6500,58 @@
     </row>
     <row r="63" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B63" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C63" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="D63" t="s">
+        <v>248</v>
+      </c>
+      <c r="E63" t="s">
+        <v>420</v>
+      </c>
+      <c r="F63" t="s">
+        <v>406</v>
+      </c>
+      <c r="G63" t="s">
+        <v>392</v>
+      </c>
+      <c r="H63" t="s">
+        <v>482</v>
+      </c>
+      <c r="I63" t="s">
+        <v>247</v>
+      </c>
+      <c r="J63" t="s">
+        <v>348</v>
+      </c>
+      <c r="K63" t="s">
+        <v>468</v>
+      </c>
+      <c r="L63" t="s">
+        <v>345</v>
+      </c>
+      <c r="M63" t="s">
         <v>250</v>
       </c>
-      <c r="E63" t="s">
-        <v>423</v>
-      </c>
-      <c r="F63" t="s">
-        <v>409</v>
-      </c>
-      <c r="G63" t="s">
-        <v>395</v>
-      </c>
-      <c r="H63" t="s">
-        <v>485</v>
-      </c>
-      <c r="I63" t="s">
-        <v>249</v>
-      </c>
-      <c r="J63" t="s">
-        <v>350</v>
-      </c>
-      <c r="K63" t="s">
-        <v>471</v>
-      </c>
-      <c r="L63" t="s">
-        <v>347</v>
-      </c>
-      <c r="M63" t="s">
-        <v>252</v>
-      </c>
       <c r="N63" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="O63">
         <v>3500</v>
       </c>
       <c r="P63" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="R63" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="S63" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="T63" s="1">
         <v>45839</v>
@@ -6528,10 +6560,10 @@
         <v>160</v>
       </c>
       <c r="V63" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="W63" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="X63">
         <v>300</v>
@@ -6545,55 +6577,55 @@
     </row>
     <row r="64" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B64" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C64" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="E64" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="F64" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="G64" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="H64" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="I64" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="J64" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="L64" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="M64" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="N64" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="O64">
         <v>225</v>
       </c>
       <c r="P64" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="Q64" t="s">
         <v>21</v>
       </c>
       <c r="R64" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="S64" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="T64" s="1">
         <v>45996</v>
@@ -6602,10 +6634,10 @@
         <v>75</v>
       </c>
       <c r="V64" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="W64" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="X64">
         <v>120</v>
@@ -6619,58 +6651,58 @@
     </row>
     <row r="65" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B65" t="s">
+        <v>259</v>
+      </c>
+      <c r="C65" t="s">
+        <v>425</v>
+      </c>
+      <c r="D65" t="s">
+        <v>31</v>
+      </c>
+      <c r="E65" t="s">
+        <v>429</v>
+      </c>
+      <c r="F65" t="s">
+        <v>350</v>
+      </c>
+      <c r="G65" t="s">
+        <v>395</v>
+      </c>
+      <c r="H65" t="s">
+        <v>489</v>
+      </c>
+      <c r="I65" t="s">
+        <v>353</v>
+      </c>
+      <c r="J65" t="s">
+        <v>354</v>
+      </c>
+      <c r="K65" t="s">
+        <v>381</v>
+      </c>
+      <c r="L65" t="s">
+        <v>345</v>
+      </c>
+      <c r="M65" t="s">
         <v>261</v>
-      </c>
-      <c r="C65" t="s">
-        <v>428</v>
-      </c>
-      <c r="D65" t="s">
-        <v>33</v>
-      </c>
-      <c r="E65" t="s">
-        <v>432</v>
-      </c>
-      <c r="F65" t="s">
-        <v>352</v>
-      </c>
-      <c r="G65" t="s">
-        <v>398</v>
-      </c>
-      <c r="H65" t="s">
-        <v>492</v>
-      </c>
-      <c r="I65" t="s">
-        <v>355</v>
-      </c>
-      <c r="J65" t="s">
-        <v>356</v>
-      </c>
-      <c r="K65" t="s">
-        <v>383</v>
-      </c>
-      <c r="L65" t="s">
-        <v>347</v>
-      </c>
-      <c r="M65" t="s">
-        <v>263</v>
       </c>
       <c r="O65">
         <v>105</v>
       </c>
       <c r="P65" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="Q65" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="R65" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="S65" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="T65" s="1">
         <v>46013</v>
@@ -6679,10 +6711,10 @@
         <v>30</v>
       </c>
       <c r="V65" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="W65" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="X65">
         <v>150</v>
@@ -6696,52 +6728,52 @@
     </row>
     <row r="66" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="B66" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C66" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="E66" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="F66" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="G66" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="H66" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="I66" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="K66" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="L66" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="M66" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="O66">
         <v>86</v>
       </c>
       <c r="P66" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="Q66" t="s">
         <v>17</v>
       </c>
       <c r="R66" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="S66" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="T66" s="6">
         <v>46041</v>
@@ -6750,10 +6782,10 @@
         <v>0</v>
       </c>
       <c r="V66" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="W66" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="X66">
         <v>15</v>
@@ -6767,55 +6799,55 @@
     </row>
     <row r="67" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="B67" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C67" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="E67" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="F67" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="G67" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="H67" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="I67" t="s">
+        <v>511</v>
+      </c>
+      <c r="J67" t="s">
+        <v>512</v>
+      </c>
+      <c r="K67" t="s">
+        <v>513</v>
+      </c>
+      <c r="L67" t="s">
+        <v>345</v>
+      </c>
+      <c r="M67" t="s">
         <v>514</v>
-      </c>
-      <c r="J67" t="s">
-        <v>515</v>
-      </c>
-      <c r="K67" t="s">
-        <v>516</v>
-      </c>
-      <c r="L67" t="s">
-        <v>347</v>
-      </c>
-      <c r="M67" t="s">
-        <v>517</v>
       </c>
       <c r="O67">
         <v>28</v>
       </c>
       <c r="P67" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="Q67" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="R67" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="S67" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="T67" s="6">
         <v>46041</v>
@@ -6824,10 +6856,10 @@
         <v>25</v>
       </c>
       <c r="V67" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="W67" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="X67">
         <v>60</v>
@@ -6841,55 +6873,55 @@
     </row>
     <row r="68" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="B68" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C68" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E68" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="F68" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="G68" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="H68" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="I68" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="J68" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="K68" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="L68" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="M68" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="O68">
         <v>92</v>
       </c>
       <c r="P68" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="Q68" t="s">
         <v>10</v>
       </c>
       <c r="R68" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="S68" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="T68" s="6">
         <v>46041</v>
@@ -6898,10 +6930,10 @@
         <v>30</v>
       </c>
       <c r="V68" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="W68" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="X68">
         <v>85</v>
@@ -6915,55 +6947,55 @@
     </row>
     <row r="69" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="B69" t="s">
+        <v>520</v>
+      </c>
+      <c r="C69" t="s">
+        <v>425</v>
+      </c>
+      <c r="E69" t="s">
+        <v>521</v>
+      </c>
+      <c r="F69" t="s">
+        <v>385</v>
+      </c>
+      <c r="G69" t="s">
+        <v>416</v>
+      </c>
+      <c r="H69" t="s">
+        <v>522</v>
+      </c>
+      <c r="I69" t="s">
         <v>523</v>
       </c>
-      <c r="C69" t="s">
-        <v>428</v>
-      </c>
-      <c r="E69" t="s">
+      <c r="J69" t="s">
+        <v>357</v>
+      </c>
+      <c r="K69" t="s">
         <v>524</v>
       </c>
-      <c r="F69" t="s">
-        <v>387</v>
-      </c>
-      <c r="G69" t="s">
-        <v>419</v>
-      </c>
-      <c r="H69" t="s">
+      <c r="L69" t="s">
+        <v>345</v>
+      </c>
+      <c r="M69" t="s">
         <v>525</v>
-      </c>
-      <c r="I69" t="s">
-        <v>526</v>
-      </c>
-      <c r="J69" t="s">
-        <v>359</v>
-      </c>
-      <c r="K69" t="s">
-        <v>527</v>
-      </c>
-      <c r="L69" t="s">
-        <v>347</v>
-      </c>
-      <c r="M69" t="s">
-        <v>528</v>
       </c>
       <c r="O69">
         <v>160</v>
       </c>
       <c r="P69" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="Q69" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="R69" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="S69" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="T69" s="6">
         <v>46041</v>
@@ -6972,10 +7004,10 @@
         <v>60</v>
       </c>
       <c r="V69" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="W69" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="X69">
         <v>150</v>
@@ -6989,58 +7021,58 @@
     </row>
     <row r="70" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="B70" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C70" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="D70" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="E70" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="F70" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="G70" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="H70" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="I70" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="J70" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="K70" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="L70" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="M70" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="O70">
         <v>97</v>
       </c>
       <c r="P70" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="Q70" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="R70" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="S70" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="T70" s="1">
         <v>46071</v>
@@ -7049,10 +7081,10 @@
         <v>155</v>
       </c>
       <c r="V70" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="W70" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="X70">
         <v>200</v>
@@ -7066,58 +7098,58 @@
     </row>
     <row r="71" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="B71" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C71" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D71" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E71" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F71" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="G71" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="H71" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="I71" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="J71" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="K71" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="L71" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="M71" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="O71">
         <v>318</v>
       </c>
       <c r="P71" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="Q71" t="s">
         <v>17</v>
       </c>
       <c r="R71" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="S71" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="T71" s="1">
         <v>46071</v>
@@ -7126,10 +7158,10 @@
         <v>60</v>
       </c>
       <c r="V71" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="W71" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="X71">
         <v>100</v>
@@ -7143,58 +7175,58 @@
     </row>
     <row r="72" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="B72" t="s">
+        <v>545</v>
+      </c>
+      <c r="C72" t="s">
         <v>546</v>
       </c>
-      <c r="B72" t="s">
-        <v>549</v>
-      </c>
-      <c r="C72" t="s">
-        <v>550</v>
-      </c>
       <c r="D72" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E72" t="s">
+        <v>552</v>
+      </c>
+      <c r="F72" t="s">
+        <v>350</v>
+      </c>
+      <c r="G72" t="s">
+        <v>395</v>
+      </c>
+      <c r="H72" t="s">
+        <v>553</v>
+      </c>
+      <c r="I72" t="s">
+        <v>554</v>
+      </c>
+      <c r="J72" t="s">
+        <v>555</v>
+      </c>
+      <c r="K72" t="s">
         <v>556</v>
       </c>
-      <c r="F72" t="s">
-        <v>352</v>
-      </c>
-      <c r="G72" t="s">
-        <v>398</v>
-      </c>
-      <c r="H72" t="s">
-        <v>557</v>
-      </c>
-      <c r="I72" t="s">
-        <v>558</v>
-      </c>
-      <c r="J72" t="s">
-        <v>559</v>
-      </c>
-      <c r="K72" t="s">
-        <v>560</v>
-      </c>
       <c r="L72" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="M72" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="O72">
         <v>47</v>
       </c>
       <c r="P72" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="Q72" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="R72" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="S72" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="T72" s="1">
         <v>46071</v>
@@ -7203,10 +7235,10 @@
         <v>60</v>
       </c>
       <c r="V72" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="W72" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="X72">
         <v>90</v>

--- a/Coleccion de minerales.xlsx
+++ b/Coleccion de minerales.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Colección Minerales\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Mi Colección de Minerales\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC158D4D-FA1D-4474-8493-4B189F9C45D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C5C977D-9FD8-452F-A55E-4761129B7E70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1330" uniqueCount="565">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1334" uniqueCount="570">
   <si>
     <t>Mineral</t>
   </si>
@@ -61,13 +61,6 @@
     <t>48.5x94x44.7</t>
   </si>
   <si>
-    <t>Cavidad bien definida con crecimiento cristalino visible
-Buen contraste cromático (verde-amarillo vs. matriz roja)</t>
-  </si>
-  <si>
-    <t>Adquirido en tienda "La Tierra" Málaga</t>
-  </si>
-  <si>
     <t>ChatGPT</t>
   </si>
   <si>
@@ -83,12 +76,6 @@
     <t>41.5x45x40</t>
   </si>
   <si>
-    <t>Cristales tabulares y pseudohexagonales, muy típicos de La Vacariza.
-Color lila–violáceo pálido, con zonaciones blanquecinas internas.
-Agregado compacto, con cristales entrecruzados y buen volumen.
-Algunas exfoliaciones y microfracturas visibles</t>
-  </si>
-  <si>
     <t>Mibladen mining district, Midelt Province, Drâa-Tafilalet Region.</t>
   </si>
   <si>
@@ -98,15 +85,6 @@
     <t>55.6x59.5x42</t>
   </si>
   <si>
-    <t>Cristales pseudohexagonales bien definidos, típicos de Mibladen.
-Crecimiento en agregados densos, con ese aspecto “empedrado” tan característico.
-Color marrón miel a caramelo, con zonas más claras hacia la parte superior.
-Se aprecia matriz clara (calcita / dolomía) en la zona alta, lo que le da contraste y profundidad visual.</t>
-  </si>
-  <si>
-    <t>Piña</t>
-  </si>
-  <si>
     <t>Pirolusita</t>
   </si>
   <si>
@@ -116,16 +94,9 @@
     <t>Dendrítica</t>
   </si>
   <si>
-    <t>Matacabras, Linares, Jaén, Andalucía.</t>
-  </si>
-  <si>
     <t>75.9x94.5x6.8</t>
   </si>
   <si>
-    <t>Placa de roca sedimentaria clara con dendritas de pirolusita muy bien desarrolladas, formando patrones ramificados de aspecto vegetal (“paisaje”).
-Contraste excelente entre el fondo beige y las dendritas negras, con distribución equilibrada y buena definición de las ramificaciones.</t>
-  </si>
-  <si>
     <t>Pirita</t>
   </si>
   <si>
@@ -138,20 +109,12 @@
     <t>41x47x41</t>
   </si>
   <si>
-    <t>Conjunto de cubos de pirita bien desarrollados, con crecimiento escalonado y ligera interpenetración / macla entre los individuos.
-Caras mayoritariamente planas, con brillo metálico dorado correcto y aristas bien definidas. El conjunto tiene volumen, equilibrio y lectura tridimensional, no es el típico cubo aislado.</t>
-  </si>
-  <si>
     <t>Perú</t>
   </si>
   <si>
     <t>51.4x77.2x67.9</t>
   </si>
   <si>
-    <t>Conjunto masivo de cristales cúbicos de pirita muy estriados, con crecimientos interpenetrados y caras profundamente marcadas por estriaciones paralelas.
-Color dorado oscuro a latón, con brillo metálico fuerte en varias caras y zonas más mate en otras, típico de muchas piritas peruanas de sistemas hidrotermales.</t>
-  </si>
-  <si>
     <t>Marcasita</t>
   </si>
   <si>
@@ -164,18 +127,9 @@
     <t>Agregado discoidal de marcasita con crecimiento radial muy bien definido desde un núcleo central, formando un “sol” casi completo. Presenta textura fibrosa y radiada claramente visible, con color gris latón a bronce apagado y buen contraste de las líneas de crecimiento. Contorno regular y dibujo radial limpio y legible.</t>
   </si>
   <si>
-    <t>Olivino</t>
-  </si>
-  <si>
-    <t>Tenerife</t>
-  </si>
-  <si>
     <t>47x66x43</t>
   </si>
   <si>
-    <t>Agregado masivo de cristales de olivino de color verde oliva a verde amarillento, con brillo vítreo notable en las caras frescas. Cristales anhedrales a subhedrales embebidos en matriz volcánica, con buena dispersión y contraste cromático. Se aprecian zonas más translúcidas que aportan viveza al conjunto.</t>
-  </si>
-  <si>
     <t>Moscovita</t>
   </si>
   <si>
@@ -212,10 +166,6 @@
     <t>82.5x89.5x69</t>
   </si>
   <si>
-    <t>Ejemplar masivo de malaquita con desarrollo botrioidal y reniforme dominante, mostrando una amplia gama de tonos verdes, desde verdes claros empolvados hasta verdes más profundos.
-La parte posterior de la pieza se encuentra profusamente recubierta por microcristales de color verde intenso, con brillo vítreo y textura granular-acicular, atribuibles a brochantita, formando una asociación secundaria muy estética y contrastada sobre la matriz.</t>
-  </si>
-  <si>
     <t>Ferruginosa</t>
   </si>
   <si>
@@ -237,10 +187,6 @@
     <t>54x73x63</t>
   </si>
   <si>
-    <t>Ejemplar formado por agregados cristalinos de rodocrosita de tonalidad rosa pálido a rosada-crema, desarrollados en formas botrioidales y granulares, recubriendo parcialmente una matriz de cuarzo cristalino.
-La rodocrosita presenta cristales pequeños, bien definidos, con brillo vítreo a nacarado, formando masas compactas y relieves suaves. Se observan pequeños huecos y cavidades tapizadas por cristales más definidos, aportando profundidad y textura al conjunto.</t>
-  </si>
-  <si>
     <t>Limonita</t>
   </si>
   <si>
@@ -250,11 +196,6 @@
     <t>300x230x90</t>
   </si>
   <si>
-    <t>Morfología escultórica muy marcada
-Buen contraste ocre–marrón oscuro
-Yacimiento clásico español</t>
-  </si>
-  <si>
     <t>Vanadinita</t>
   </si>
   <si>
@@ -267,12 +208,6 @@
     <t>13.6</t>
   </si>
   <si>
-    <t>Cristales bien formados, hábito hexagonal corto, caras limpias
-Color rojo-marrón intenso con brillo resinoso muy atractivo
-Agregado compacto y equilibrado, sin sensación de “trozo roto”
-Matriz clara que realza el color (probable barita/carbonato)</t>
-  </si>
-  <si>
     <t>Cobre</t>
   </si>
   <si>
@@ -297,21 +232,12 @@
     <t>Estilbita</t>
   </si>
   <si>
-    <t>Aurangabad, Maharashtra.</t>
-  </si>
-  <si>
     <t>India</t>
   </si>
   <si>
     <t>115x80x45</t>
   </si>
   <si>
-    <t>Cristales prismáticos cortos de apofilita, bien formados, asociados a agregados laminares y en abanico de estilbita.
-Asociación típica de cavidades en basaltos (ambiente volcánico).
-Buena, cristalización visible, color agradable pero no intenso
-Sin daños evidentes, cristales íntegros</t>
-  </si>
-  <si>
     <t>Adquirido en tienda "Taller de Minerales" Málaga 2023</t>
   </si>
   <si>
@@ -327,12 +253,6 @@
     <t>200x140x60</t>
   </si>
   <si>
-    <t>Yeso. Cristales prismáticos sobre matriz de alabastro
-Tamaño grande y bien equilibrado
-Cristales bien visibles, repartidos por toda la superficie
-Buen contraste cristal/matriz</t>
-  </si>
-  <si>
     <t>Morión</t>
   </si>
   <si>
@@ -342,10 +262,6 @@
     <t>105x133x36</t>
   </si>
   <si>
-    <t>Grupo cristalino de cuarzo morión formado por numerosos cristales prismáticos bien desarrollados, de color negro intenso a pardo muy oscuro, con elevada transparencia en aristas y zonas internas.
-El conjunto presenta un crecimiento compacto y escalonado, con cristales entrelazados y terminaciones mayoritariamente completas, mostrando buen brillo vítreo y caras definidas. El cristal principal destaca claramente por tamaño y verticalidad, aportando jerarquía visual al conjunto.</t>
-  </si>
-  <si>
     <t>Amatista</t>
   </si>
   <si>
@@ -355,20 +271,12 @@
     <t>74x180x63</t>
   </si>
   <si>
-    <t>Gran drusa de amatista formada por numerosos cristales bien desarrollados, con terminaciones agudas y caras definidas. El color es violeta medio a intenso, con variaciones tonales y zonaciones internas visibles en varios cristales, aportando profundidad y riqueza cromática al conjunto.
-Se observan intercrecimientos de cristales y zonas con microcristales de cuarzo incoloro, así como matriz residual en una de las caras, que refuerza el carácter natural del ejemplar.</t>
-  </si>
-  <si>
     <t>Citrino</t>
   </si>
   <si>
     <t>131.5x180x80</t>
   </si>
   <si>
-    <t>Gran grupo cristalino de cuarzo citrino compuesto por numerosos cristales prismáticos de tamaño medio a grande, con terminaciones bien definidas y caras limpias. El color varía entre amarillo dorado, miel y tonos ámbar intensos, con excelente transparencia interna y zonaciones visibles en varios cristales.
-El crecimiento es denso y compacto, con cristales intercrecidos que forman una masa robusta y muy estética. La matriz clara queda parcialmente visible en la base, aportando estabilidad visual y carácter natural al conjunto.</t>
-  </si>
-  <si>
     <t>Hematites</t>
   </si>
   <si>
@@ -382,10 +290,6 @@
   </si>
   <si>
     <t>40</t>
-  </si>
-  <si>
-    <t>Grupo estético formado por cristales prismáticos de cuarzo lechoso dispuestos en crecimiento radial, emergiendo desde una roseta central de hematites laminar de color negro a pardo oscuro, con brillo metálico a submetálico.
-Los cristales de cuarzo presentan caras bien definidas, ligeras estriaciones de crecimiento y terminaciones agudas, contrastando fuertemente con la textura oscura y compacta de la hematites. La disposición en estrella aporta dinamismo y una excelente lectura tridimensional de la pieza.</t>
   </si>
   <si>
     <t>Adquirido en Feria Navidad Málaga</t>
@@ -476,24 +380,12 @@
     <t>108.5x47.5x30</t>
   </si>
   <si>
-    <t>Grupo de cristales de cuarzo hialino bien formados, con notable transparencia y brillo vítreo. Destaca un posible cristal biterminado de aproximadamente 81 mm, claramente visible y con terminaciones definidas en ambos extremos. Acompañando al principal, se observa otro cristal mayor de unos 50 mm, junto con varios cristales secundarios intercrecidos que refuerzan el carácter estético del conjunto.
-Los cristales muestran caras limpias, con ligeras inclusiones internas y pequeñas marcas de crecimiento, típicas de cuarzos alpinos o de filón. La matriz es escasa y discreta, permitiendo una lectura muy clara de la morfología cristalina.</t>
-  </si>
-  <si>
     <t>17.5x17.5x17.5</t>
   </si>
   <si>
-    <t>Cubo de pirita prácticamente isométrico, con aristas bien definidas y caras planas. Presenta el típico aspecto metálico de Navajún, con brillo satinado-mate debido a microestriaciones de crecimiento visibles en las caras. La geometría es muy limpia, sin maclas ni distorsiones apreciables.
-Se observan ligeras variaciones de tono y pequeñas marcas superficiales, normales en ejemplares de este tamaño y procedencia, que no restan legibilidad cristalográfica.</t>
-  </si>
-  <si>
     <t>46.5x70x46</t>
   </si>
   <si>
-    <t>Grupo de yeso blanco-translúcido, con un cristal principal bien desarrollado de hábito tabular–laminar, tipo “espada”, emergiendo de una matriz masiva de yeso microcristalino. El cristal muestra buena definición de caras, con transparencia media y brillo sedoso-vítreo.
-La matriz presenta cavidades y texturas típicas de la concesión Joan, aportando volumen y contraste al conjunto. El cristal dominante está bien posicionado y resulta claramente legible desde varios ángulos.</t>
-  </si>
-  <si>
     <t>Matriz de Alabastro</t>
   </si>
   <si>
@@ -510,10 +402,6 @@
   </si>
   <si>
     <t>108x89x37</t>
-  </si>
-  <si>
-    <t>Ejemplar de okenita formando varios agregados esferoidales bien definidos, compuestos por finísimas fibras radiales de aspecto algodonoso y sedoso. Los “pompones” muestran buena simetría, volumen y una textura muy característica, con tonos blanco-crema y ligeros matices beige.
-Las okenitas se asientan sobre una matriz volcánica clara, probablemente zeolítica, que proporciona contraste y estabilidad visual al conjunto. Destaca la disposición equilibrada de los agregados, repartidos de forma natural por la superficie.</t>
   </si>
   <si>
     <t>Natrolita</t>
@@ -550,31 +438,15 @@
     <t>63.5x115.5x71.5</t>
   </si>
   <si>
-    <t>Conjunto de múltiples rosetas bien definidas, con buena lectura volumétrica.
-Ligera abrasión superficial típica del material, sin roturas destacables.
-Buen equilibrio entre tamaño, estética y estabilidad.</t>
-  </si>
-  <si>
     <t>84.5x68.5x45</t>
   </si>
   <si>
-    <t>Ejemplar ligero pero bien formado, con láminas relativamente finas.
-Buena estabilidad y presentación
-Aspecto limpio, sin fracturas relevantes; desgaste superficial normal en bordes.</t>
-  </si>
-  <si>
     <t>Prehnita</t>
   </si>
   <si>
     <t>96x125x75</t>
   </si>
   <si>
-    <t>Geoda abierta con tapizado completo de prehnita botroidal, muy homogénea.
-Buen contraste entre la matriz oscura y el interior verde claro.
-Cristalización típica india (Maharashtra/Deccan Traps, aunque no se puede asegurar).
-Pieza estable, sin roturas visibles</t>
-  </si>
-  <si>
     <t>Barita</t>
   </si>
   <si>
@@ -584,11 +456,6 @@
     <t>180x110x60</t>
   </si>
   <si>
-    <t>Conjunto muy estético de barita tabular azulada, bien representativa de El Telegrama (Almería).
-Excelente contraste cromático entre la barita azul y la matriz ferruginosa.
-Cristales abundantes, bien definidos y con buen brillo general.</t>
-  </si>
-  <si>
     <t>Adquirido en Feria de Minerales de Cártama 2023</t>
   </si>
   <si>
@@ -601,12 +468,6 @@
     <t>24.5</t>
   </si>
   <si>
-    <t>Conjunto de cinco cristales cúbicos bien desarrollados,
-uno de ellos alcanzando 24,5 mm de arista,
-acompañados de cristales secundarios.
-Sobre matriz.</t>
-  </si>
-  <si>
     <t>Dolomita</t>
   </si>
   <si>
@@ -616,11 +477,6 @@
     <t>75x98.5x67.5</t>
   </si>
   <si>
-    <t>Ejemplar muy representativo de la Mina Trinidad, con dolomita bien cristalizada sobre limonita.
-Buen contraste estético entre los cristales claros y la matriz oscura ferruginosa.
-Cristales visibles, bien definidos, con crecimiento limpio en varias zonas.</t>
-  </si>
-  <si>
     <t>Azul</t>
   </si>
   <si>
@@ -631,10 +487,6 @@
   </si>
   <si>
     <t>65x85x60</t>
-  </si>
-  <si>
-    <t>Procedencia: Polonia (prob. distrito de Lubin–Głogów)
-Ejemplar muy atractivo y poco común por el color azul verdoso intenso, con cristales aciculares finos y densos, formando agregados radiales bien desarrollados. El brillo es satinado a vítreo y el contraste con la matriz terrosa realza mucho la estética.</t>
   </si>
   <si>
     <t>Adquirido en tienda "Rahasya Minerales" Málaga 2023</t>
@@ -690,25 +542,12 @@
     <t>110x110x50</t>
   </si>
   <si>
-    <t>Cristales cúbicos bien definidos, superpuestos en tapiz denso.
-Color amarillo intenso a miel, con zonas más oscuras internas (zonación natural).
-Buen brillo vítreo, caras mayoritariamente limpias, con ligeras picaduras típicas del yacimiento.
-Tamaño grande para este tipo de agregados.</t>
-  </si>
-  <si>
     <t>Túnez</t>
   </si>
   <si>
     <t>170x170x130</t>
   </si>
   <si>
-    <t>Geoda equilibrada en dos mitades
-Cristales de calcita romboédrica–escalenoédrica, de tamaño medio.
-Color blanco translúcido a crema, con buen brillo en caras frescas.
-Interior tapizado por microcristales brillantes que aportan profundidad.
-Corte limpio y equilibrado: las dos mitades dialogan bien visualmente</t>
-  </si>
-  <si>
     <t>Geoda completa</t>
   </si>
   <si>
@@ -718,33 +557,18 @@
     <t>150x140x140</t>
   </si>
   <si>
-    <t>Interior tapizado por calcedonia botroidal, textura mamelonar muy bien desarrollada.
-Color azul-gris lechoso, homogéneo y muy atractivo.
-Superficies suaves, con brillo ceroso típico, muy “orgánico”.
-Presencia de estructuras estalactíticas cortas en una de las mitades, algo que siempre suma.
-Corte limpio y mitades bien equilibradas.</t>
-  </si>
-  <si>
     <t>Geoda partida (dos mitades)</t>
   </si>
   <si>
     <t>78x88.5x47</t>
   </si>
   <si>
-    <t>Interior con cristales de calcita bien definidos, translúcidos, de tono crema–miel.
-Brillo vítreo.</t>
-  </si>
-  <si>
     <t>Geoda abierta</t>
   </si>
   <si>
     <t>50x101x85</t>
   </si>
   <si>
-    <t>Geoda abierta parcialmente, tapizada internamente por microcristales de cuarzo bien desarrollados, de brillo vítreo y color blanco a ligeramente translúcido. Los cristales presentan un hábito drusiforme, recubriendo las paredes internas de la cavidad de manera bastante homogénea.
-La matriz externa es compacta, de aspecto silíceo-carbonatado, con tonos ocres por alteración superficial, típica de geodas marroquíes formadas en cavidades sedimentarias o volcánico-sedimentarias.</t>
-  </si>
-  <si>
     <t>Microcristales en Geoda</t>
   </si>
   <si>
@@ -766,17 +590,9 @@
     <t>59x89.5x48.5</t>
   </si>
   <si>
-    <t>Hábito botroidal muy marcado y bien definido, con superficies redondeadas y compactas.
-Brillo metálico excepcional</t>
-  </si>
-  <si>
     <t>110x60x92.5</t>
   </si>
   <si>
-    <t>Agregado de cristales prismáticos cortos.
-Color violeta natural y homogéneo.</t>
-  </si>
-  <si>
     <t>Hematoideo</t>
   </si>
   <si>
@@ -786,10 +602,6 @@
     <t>57x65x47</t>
   </si>
   <si>
-    <t>Color rojo teja a rojo ladrillo.
-Cristales romboédricos cortos, agregados compactos.</t>
-  </si>
-  <si>
     <t>Adquirido en Feria Navidad Málaga 2023</t>
   </si>
   <si>
@@ -814,12 +626,6 @@
     <t>81x91x56</t>
   </si>
   <si>
-    <t>Contraste cromático azul–verde muy atractivo
-Textura botroidal bien desarrollada
-Cavidades con microcristales que aportan brillo
-Volumen compacto</t>
-  </si>
-  <si>
     <t>Adquirido en tienda "PIETRA" Granada en 2024</t>
   </si>
   <si>
@@ -829,12 +635,6 @@
     <t>51x39.5x30</t>
   </si>
   <si>
-    <t>Cristales escalenoédricos bien definidos (“dientes de perro” robustos)
-Color amarillo miel homogéneo
-Brillo vítreo–sedoso, típico de calcitas marroquíes
-Crecimiento limpio y aislado, no apelmazado</t>
-  </si>
-  <si>
     <t>Adquirido en Feria Navidad Málaga 2024</t>
   </si>
   <si>
@@ -850,34 +650,18 @@
     <t>150x170x32</t>
   </si>
   <si>
-    <t>Color azul bien marcado, con zonación natural
-Cristales visibles, relativamente largos y bien definidos
-Buen contraste entre la cianita azul y la matriz clara</t>
-  </si>
-  <si>
     <t>Ahumado</t>
   </si>
   <si>
     <t>Calcita Blanca</t>
   </si>
   <si>
-    <t>Procedencia no documentada. Morfología y asociación mineral compatibles con yacimientos alpinos europeos.</t>
-  </si>
-  <si>
     <t>250x150x110</t>
   </si>
   <si>
     <t>86x37x39.5</t>
   </si>
   <si>
-    <t>Cuarzos bien formados, prismáticos, con caras limpias.
-Color ahumado uniforme y profundo (no gris apagado).
-Tamaño excepcional del cristal principal (casi 9 cm).
-Asociación con calcita que rompe masa y aporta contraste.
-Pieza muy escultórica, tridimensional.
-No se aprecian roturas recientes.</t>
-  </si>
-  <si>
     <t>Adquirido en tienda "PIETRA" Granada en 2025</t>
   </si>
   <si>
@@ -890,10 +674,6 @@
     <t>50</t>
   </si>
   <si>
-    <t>Color rojo oscuro homogéneo
-Buen equilibrio entre cristal principal y secundarios</t>
-  </si>
-  <si>
     <t>Adquirido en Feria Navidad Málaga 2025</t>
   </si>
   <si>
@@ -906,11 +686,6 @@
     <t>67.5x41x21</t>
   </si>
   <si>
-    <t>Mineral principal: Galena (cristales cúbicos, gris plomo, alto brillo metálico)
-Asociación: Pirita bien cristalizada (micro a pequeños cubos dorados)
-Presentación: pieza “escultural”, vertical</t>
-  </si>
-  <si>
     <t>M-001</t>
   </si>
   <si>
@@ -1316,15 +1091,9 @@
     <t>Dorado</t>
   </si>
   <si>
-    <t>(Mg,Fe)2SiO4</t>
-  </si>
-  <si>
     <t>Silicatos</t>
   </si>
   <si>
-    <t>Ortorrómbico, piramidal</t>
-  </si>
-  <si>
     <t>Verde oliva a verde amarillento</t>
   </si>
   <si>
@@ -1620,15 +1389,6 @@
   </si>
   <si>
     <t>Fluorescencia UVA</t>
-  </si>
-  <si>
-    <t>Hábito cristalino: Agregados en roseta de cristales escalenoédricos
-Color: Marrón a marrón cognac (impurezas de Fe)
-Brillo: Vítreo a mate
-Transparencia: Translúcida a opaca.
-Ejemplar de calcita ferruginosa con hábito en rosetas tridimensionales,
-morfología y coloración muy compatibles con material clásico de San Antonio Mine, México.
-La procedencia exacta no está documentada, por lo que se indica como probable.</t>
   </si>
   <si>
     <t>M-065</t>
@@ -1754,9 +1514,6 @@
     <t>Tounfite, Midelt, Draa-Tafilalet</t>
   </si>
   <si>
-    <t>Hidroxiapofilita-(K) (atribución probable). Apofilitas bien cristalizadas, hábito cúbico limpio. Buen contraste cromático: blanco lechoso + estilbita crema. Brillo satinado agradable, sin aspecto apagado. Composición estética y compacta.</t>
-  </si>
-  <si>
     <t>Cantera Torre de las Palomas, La Araña, Málaga, Andalucía.</t>
   </si>
   <si>
@@ -1856,12 +1613,265 @@
   <si>
     <t>Sierra Minera de Cartagena-La Unión, Murcia</t>
   </si>
+  <si>
+    <t>Adamantino a resinoso</t>
+  </si>
+  <si>
+    <t>Rombododecaédrico</t>
+  </si>
+  <si>
+    <t>Andradita</t>
+  </si>
+  <si>
+    <t>Demantoide</t>
+  </si>
+  <si>
+    <r>
+      <t>Ca</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Lucida Sans Unicode"/>
+        <family val="2"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Lucida Sans Unicode"/>
+        <family val="2"/>
+      </rPr>
+      <t>Fe</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="9.1"/>
+        <color rgb="FF000000"/>
+        <rFont val="Lucida Sans Unicode"/>
+        <family val="2"/>
+      </rPr>
+      <t>3+</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Lucida Sans Unicode"/>
+        <family val="2"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Lucida Sans Unicode"/>
+        <family val="2"/>
+      </rPr>
+      <t>(SiO</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Lucida Sans Unicode"/>
+        <family val="2"/>
+      </rPr>
+      <t>4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Lucida Sans Unicode"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Lucida Sans Unicode"/>
+        <family val="2"/>
+      </rPr>
+      <t>3</t>
+    </r>
+  </si>
+  <si>
+    <t>Comprado entre 1980 - 1985 (Colección antigua). Tienda "La Tierra" (Málaga, España)</t>
+  </si>
+  <si>
+    <t>Las Vigas de Ramírez, Estado de Veracruz</t>
+  </si>
+  <si>
+    <t>Abundantes cristales de andradita variedad demantoide, de tonalidad verde oliva a verde amarillento. Los cristales presentan hábito predominantemente dodecaédrico, algunos parcialmente embebidos en la matriz y otros con desarrollo más libre, mostrando caras bien definidas y brillo vítreo intenso.</t>
+  </si>
+  <si>
+    <t>Illinois</t>
+  </si>
+  <si>
+    <t>Probable: Solnhofen (Baviera)</t>
+  </si>
+  <si>
+    <t>Alemania</t>
+  </si>
+  <si>
+    <t>Comprado entre 1980 - 1985 (Colección antigua). Tienda "La Tierra" (Málaga, España) por 6500 pesetas</t>
+  </si>
+  <si>
+    <t>Comprado entre 1980 - 1985 (Colección antigua). Tienda "La Tierra" (Málaga, España) por 6800 pesetas</t>
+  </si>
+  <si>
+    <t>Comprado entre 1980 - 1985 (Colección antigua). Tienda "La Tierra" (Málaga, España) por 1600 pesetas.</t>
+  </si>
+  <si>
+    <t>Ejemplar de cuarzo ahumado de dimensiones excepcionales, caracterizado por su robustez y desarrollo cristalino completo. El espécimen presenta una estructura prismática de gran volumen, terminada en una pirámide hexagonal bien preservada. La pieza destaca por su imponente verticalidad y la pureza de su coloración, que oscila entre un marrón tabaco translúcido y tonos más densos en el núcleo del cristal.</t>
+  </si>
+  <si>
+    <t>Minas Gerais</t>
+  </si>
+  <si>
+    <t>Matriz de limonita recubierta por cristales de adamita prismáticos cortos que tapizan las cavidades de la matriz de hierro. Con luz ultravioleta (onda corta), la adamita brilla con un verde neón espectacular debido a la presencia de pequeñas cantidades de uranio.</t>
+  </si>
+  <si>
+    <t>Cristales tabulares y pseudohexagonales, muy típicos de La Vacariza. Color lila–violáceo pálido, con zonaciones blanquecinas internas. Agregado compacto, con cristales entrecruzados y buen volumen. Algunas exfoliaciones y microfracturas visibles.</t>
+  </si>
+  <si>
+    <t>Cristales pseudohexagonales bien definidos, típicos de Mibladen. Crecimiento en agregados densos, con ese aspecto “empedrado” tan característico. Color marrón miel a caramelo, con zonas más claras hacia la parte superior. Se aprecia matriz clara (calcita / dolomía) en la zona alta, lo que le da contraste y profundidad visual.</t>
+  </si>
+  <si>
+    <t>Placa de roca sedimentaria clara con dendritas de pirolusita muy bien desarrolladas, formando patrones ramificados de aspecto vegetal (“paisaje”). Contraste excelente entre el fondo beige y las dendritas negras, con distribución equilibrada y buena definición de las ramificaciones.</t>
+  </si>
+  <si>
+    <t>Conjunto de cubos de pirita bien desarrollados, con crecimiento escalonado y ligera interpenetración / macla entre los individuos. Caras mayoritariamente planas, con brillo metálico dorado correcto y aristas bien definidas. El conjunto tiene volumen, equilibrio y lectura tridimensional, no es el típico cubo aislado.</t>
+  </si>
+  <si>
+    <t>Conjunto masivo de cristales cúbicos de pirita muy estriados, con crecimientos interpenetrados y caras profundamente marcadas por estriaciones paralelas. Color dorado oscuro a latón, con brillo metálico fuerte en varias caras y zonas más mate en otras, típico de muchas piritas peruanas de sistemas hidrotermales.</t>
+  </si>
+  <si>
+    <t>Ejemplar masivo de malaquita con desarrollo botrioidal y reniforme dominante, mostrando una amplia gama de tonos verdes, desde verdes claros empolvados hasta verdes más profundos. La parte posterior de la pieza se encuentra profusamente recubierta por microcristales de color verde intenso, con brillo vítreo y textura granular-acicular, atribuibles a brochantita, formando una asociación secundaria muy estética y contrastada sobre la matriz.</t>
+  </si>
+  <si>
+    <t>Ejemplar de calcita ferruginosa con hábito en rosetas tridimensionales. Morfología y coloración muy compatibles con material clásico de San Antonio Mine, México. La procedencia exacta no está documentada, por lo que se indica como probable.</t>
+  </si>
+  <si>
+    <t>Ejemplar formado por agregados cristalinos de rodocrosita de tonalidad rosa pálido a rosada-crema, desarrollados en formas botrioidales y granulares, recubriendo parcialmente una matriz de cuarzo cristalino. La rodocrosita presenta cristales pequeños, bien definidos, con brillo vítreo a nacarado, formando masas compactas y relieves suaves. Se observan pequeños huecos y cavidades tapizadas por cristales más definidos, aportando profundidad y textura al conjunto.</t>
+  </si>
+  <si>
+    <t>Morfología escultórica muy marcada, Buen contraste ocre–marrón oscuro. Yacimiento clásico español</t>
+  </si>
+  <si>
+    <t>Cristales bien formados, hábito hexagonal corto, caras limpias. Color rojo-marrón intenso con brillo resinoso muy atractivo. Agregado compacto y equilibrado, sin sensación de “trozo roto”. Matriz clara que realza el color (probable barita/carbonato).</t>
+  </si>
+  <si>
+    <t>Cristales prismáticos cortos de apofilita, bien formados, asociados a agregados laminares y en abanico de estilbita. Asociación típica de cavidades en basaltos (ambiente volcánico). Buena, cristalización visible, color agradable pero no intenso. Sin daños evidentes, cristales íntegros.</t>
+  </si>
+  <si>
+    <t>Yeso. Cristales prismáticos sobre matriz de alabastro. Tamaño grande y bien equilibrado. Cristales bien visibles, repartidos por toda la superficie. Buen contraste cristal/matriz.</t>
+  </si>
+  <si>
+    <t>Grupo cristalino de cuarzo morión formado por numerosos cristales prismáticos bien desarrollados, de color negro intenso a pardo muy oscuro, con elevada transparencia en aristas y zonas internas. El conjunto presenta un crecimiento compacto y escalonado, con cristales entrelazados y terminaciones mayoritariamente completas, mostrando buen brillo vítreo y caras definidas. El cristal principal destaca claramente por tamaño y verticalidad, aportando jerarquía visual al conjunto.</t>
+  </si>
+  <si>
+    <t>Gran grupo cristalino de cuarzo citrino compuesto por numerosos cristales prismáticos de tamaño medio a grande, con terminaciones bien definidas y caras limpias. El color varía entre amarillo dorado, miel y tonos ámbar intensos, con excelente transparencia interna y zonaciones visibles en varios cristales. El crecimiento es denso y compacto, con cristales intercrecidos que forman una masa robusta y muy estética. La matriz clara queda parcialmente visible en la base, aportando estabilidad visual y carácter natural al conjunto.</t>
+  </si>
+  <si>
+    <t>Gran drusa de amatista formada por numerosos cristales bien desarrollados, con terminaciones agudas y caras definidas. El color es violeta medio a intenso, con variaciones tonales y zonaciones internas visibles en varios cristales, aportando profundidad y riqueza cromática al conjunto. Se observan intercrecimientos de cristales y zonas con microcristales de cuarzo incoloro, así como matriz residual en una de las caras, que refuerza el carácter natural del ejemplar.</t>
+  </si>
+  <si>
+    <t>Grupo estético formado por cristales prismáticos de cuarzo lechoso dispuestos en crecimiento radial, emergiendo desde una roseta central de hematites laminar de color negro a pardo oscuro, con brillo metálico a submetálico. Los cristales de cuarzo presentan caras bien definidas, ligeras estriaciones de crecimiento y terminaciones agudas, contrastando fuertemente con la textura oscura y compacta de la hematites. La disposición en estrella aporta dinamismo y una excelente lectura tridimensional de la pieza.</t>
+  </si>
+  <si>
+    <t>Grupo de cristales de cuarzo hialino bien formados, con notable transparencia y brillo vítreo. Destaca un posible cristal biterminado de aproximadamente 81 mm, claramente visible y con terminaciones definidas en ambos extremos. Acompañando al principal, se observa otro cristal mayor de unos 50 mm, junto con varios cristales secundarios intercrecidos que refuerzan el carácter estético del conjunto. Los cristales muestran caras limpias, con ligeras inclusiones internas y pequeñas marcas de crecimiento, típicas de cuarzos alpinos o de filón. La matriz es escasa y discreta, permitiendo una lectura muy clara de la morfología cristalina.</t>
+  </si>
+  <si>
+    <t>Cubo de pirita prácticamente isométrico, con aristas bien definidas y caras planas. Presenta el típico aspecto metálico de Navajún, con brillo satinado-mate debido a microestriaciones de crecimiento visibles en las caras. La geometría es muy limpia, sin maclas ni distorsiones apreciables. Se observan ligeras variaciones de tono y pequeñas marcas superficiales, normales en ejemplares de este tamaño y procedencia, que no restan legibilidad cristalográfica.</t>
+  </si>
+  <si>
+    <t>Grupo de yeso blanco-translúcido, con un cristal principal bien desarrollado de hábito tabular–laminar, tipo “espada”, emergiendo de una matriz masiva de yeso microcristalino. El cristal muestra buena definición de caras, con transparencia media y brillo sedoso-vítreo. La matriz presenta cavidades y texturas típicas de la concesión Joan, aportando volumen y contraste al conjunto. El cristal dominante está bien posicionado y resulta claramente legible desde varios ángulos.</t>
+  </si>
+  <si>
+    <t>Ejemplar de okenita formando varios agregados esferoidales bien definidos, compuestos por finísimas fibras radiales de aspecto algodonoso y sedoso. Los “pompones” muestran buena simetría, volumen y una textura muy característica, con tonos blanco-crema y ligeros matices beige. Las okenitas se asientan sobre una matriz volcánica clara, probablemente zeolítica, que proporciona contraste y estabilidad visual al conjunto. Destaca la disposición equilibrada de los agregados, repartidos de forma natural por la superficie.</t>
+  </si>
+  <si>
+    <t>Conjunto de múltiples rosetas bien definidas, con buena lectura volumétrica. Ligera abrasión superficial típica del material, sin roturas destacables. Buen equilibrio entre tamaño, estética y estabilidad.</t>
+  </si>
+  <si>
+    <t>Ejemplar ligero pero bien formado, con láminas relativamente finas. Buena estabilidad y presentación. Aspecto limpio, sin fracturas relevantes; desgaste superficial normal en bordes.</t>
+  </si>
+  <si>
+    <t>Geoda abierta con tapizado completo de prehnita botroidal, muy homogénea. Buen contraste entre la matriz oscura y el interior verde claro. Cristalización típica india (Maharashtra/Deccan Traps, aunque no se puede asegurar). Pieza estable, sin roturas visibles.</t>
+  </si>
+  <si>
+    <t>Conjunto muy estético de barita tabular azulada, bien representativa de El Telegrama (Almería). Excelente contraste cromático entre la barita azul y la matriz ferruginosa. Cristales abundantes, bien definidos y con buen brillo general.</t>
+  </si>
+  <si>
+    <t>Conjunto de cinco cristales cúbicos bien desarrollados, Uno de ellos alcanzando 24,5 mm de arista, acompañados de cristales secundarios. Sobre matriz.</t>
+  </si>
+  <si>
+    <t>Ejemplar muy representativo de la Mina Trinidad, con dolomita bien cristalizada sobre limonita. Buen contraste estético entre los cristales claros y la matriz oscura ferruginosa. Cristales visibles, bien definidos, con crecimiento limpio en varias zonas.</t>
+  </si>
+  <si>
+    <t>Procedencia: Polonia (prob. distrito de Lubin–Głogów). Ejemplar muy atractivo y poco común por el color azul verdoso intenso, con cristales aciculares finos y densos, formando agregados radiales bien desarrollados. El brillo es satinado a vítreo y el contraste con la matriz terrosa realza mucho la estética.</t>
+  </si>
+  <si>
+    <t>Cristales cúbicos bien definidos, superpuestos en tapiz denso. Color amarillo intenso a miel, con zonas más oscuras internas (zonación natural). Buen brillo vítreo, caras mayoritariamente limpias, con ligeras picaduras típicas del yacimiento. Tamaño grande para este tipo de agregados.</t>
+  </si>
+  <si>
+    <t>Geoda equilibrada en dos mitades. Cristales de calcita romboédrica–escalenoédrica, de tamaño medio. Color blanco translúcido a crema, con buen brillo en caras frescas. Interior tapizado por microcristales brillantes que aportan profundidad. Corte limpio y equilibrado: las dos mitades dialogan bien visualmente.</t>
+  </si>
+  <si>
+    <t>Interior tapizado por calcedonia botroidal, textura mamelonar muy bien desarrollada. Color azul-gris lechoso, homogéneo y muy atractivo. Superficies suaves, con brillo ceroso típico, muy “orgánico”. Presencia de estructuras estalactíticas cortas en una de las mitades, algo que siempre suma. Corte limpio y mitades bien equilibradas.</t>
+  </si>
+  <si>
+    <t>Interior con cristales de calcita bien definidos, translúcidos, de tono crema–miel. Brillo vítreo.</t>
+  </si>
+  <si>
+    <t>Geoda abierta parcialmente, tapizada internamente por microcristales de cuarzo bien desarrollados, de brillo vítreo y color blanco a ligeramente translúcido. Los cristales presentan un hábito drusiforme, recubriendo las paredes internas de la cavidad de manera bastante homogénea. La matriz externa es compacta, de aspecto silíceo-carbonatado, con tonos ocres por alteración superficial, típica de geodas marroquíes formadas en cavidades sedimentarias o volcánico-sedimentarias.</t>
+  </si>
+  <si>
+    <t>Hidroxiapofilita-(K) (atribución probable). Apofilitas bien cristalizadas, hábito cúbico limpio. Buen contraste cromático: blanco lechoso + estilbita crema. Brillo satinado agradable, sin aspecto apagado. Composición estética y compacta (no “desparramada”)</t>
+  </si>
+  <si>
+    <t>Hábito botroidal muy marcado y bien definido, con superficies redondeadas y compactas. Brillo metálico excepcional.</t>
+  </si>
+  <si>
+    <t>Agregado de cristales prismáticos cortos. Color violeta natural y homogéneo.</t>
+  </si>
+  <si>
+    <t>Color rojo teja a rojo ladrillo. Cristales romboédricos cortos, agregados compactos.</t>
+  </si>
+  <si>
+    <t>Contraste cromático azul–verde muy atractivo. Textura botroidal bien desarrollada. Cavidades con microcristales que aportan brillo. Volumen compacto.</t>
+  </si>
+  <si>
+    <t>Cristales escalenoédricos bien definidos (“dientes de perro” robustos). Color amarillo miel homogéneo. Brillo vítreo–sedoso, típico de calcitas marroquíes. Crecimiento limpio y aislado, no apelmazado.</t>
+  </si>
+  <si>
+    <t>Color azul bien marcado, con zonación natural. Cristales visibles, relativamente largos y bien definidos. Buen contraste entre la cianita azul y la matriz clara.</t>
+  </si>
+  <si>
+    <t>Color rojo oscuro homogéneo. Buen equilibrio entre cristal principal y secundarios.</t>
+  </si>
+  <si>
+    <t>Mineral principal: Galena (cristales cúbicos, gris plomo, alto brillo metálico). Asociación: Pirita bien cristalizada (micro a pequeños cubos dorados). Presentación: pieza “escultural”, vertical.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1908,6 +1918,26 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Lucida Sans Unicode"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <vertAlign val="subscript"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Lucida Sans Unicode"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <vertAlign val="superscript"/>
+      <sz val="9.1"/>
+      <color rgb="FF000000"/>
+      <name val="Lucida Sans Unicode"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -2317,7 +2347,7 @@
   <sheetData>
     <row r="1" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>330</v>
+        <v>281</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>0</v>
@@ -2329,37 +2359,37 @@
         <v>2</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>333</v>
+        <v>284</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>334</v>
+        <v>285</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>335</v>
+        <v>286</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>336</v>
+        <v>287</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>337</v>
+        <v>288</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>338</v>
+        <v>289</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>339</v>
+        <v>290</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>499</v>
+        <v>448</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>434</v>
+        <v>383</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>435</v>
+        <v>384</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>433</v>
+        <v>382</v>
       </c>
       <c r="P1" s="3" t="s">
         <v>3</v>
@@ -2368,16 +2398,16 @@
         <v>4</v>
       </c>
       <c r="R1" s="3" t="s">
-        <v>340</v>
+        <v>291</v>
       </c>
       <c r="S1" s="3" t="s">
-        <v>341</v>
+        <v>292</v>
       </c>
       <c r="T1" s="3" t="s">
-        <v>331</v>
+        <v>282</v>
       </c>
       <c r="U1" s="3" t="s">
-        <v>328</v>
+        <v>279</v>
       </c>
       <c r="V1" s="3" t="s">
         <v>5</v>
@@ -2386,10 +2416,10 @@
         <v>6</v>
       </c>
       <c r="X1" s="3" t="s">
-        <v>342</v>
+        <v>293</v>
       </c>
       <c r="Y1" s="3" t="s">
-        <v>329</v>
+        <v>280</v>
       </c>
       <c r="Z1" s="3" t="s">
         <v>7</v>
@@ -2397,34 +2427,34 @@
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>263</v>
+        <v>214</v>
       </c>
       <c r="B2" t="s">
         <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>425</v>
+        <v>374</v>
       </c>
       <c r="E2" t="s">
-        <v>426</v>
+        <v>375</v>
       </c>
       <c r="F2" t="s">
-        <v>385</v>
+        <v>336</v>
       </c>
       <c r="G2" t="s">
-        <v>384</v>
+        <v>335</v>
       </c>
       <c r="H2" t="s">
-        <v>386</v>
+        <v>337</v>
       </c>
       <c r="I2" t="s">
-        <v>358</v>
+        <v>309</v>
       </c>
       <c r="J2" t="s">
-        <v>348</v>
+        <v>299</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>498</v>
+        <v>447</v>
       </c>
       <c r="M2" t="s">
         <v>11</v>
@@ -2439,16 +2469,16 @@
         <v>10</v>
       </c>
       <c r="R2" t="s">
-        <v>349</v>
+        <v>300</v>
       </c>
       <c r="S2" t="s">
-        <v>424</v>
+        <v>373</v>
       </c>
       <c r="V2" t="s">
-        <v>12</v>
+        <v>528</v>
       </c>
       <c r="W2" t="s">
-        <v>13</v>
+        <v>517</v>
       </c>
       <c r="X2">
         <v>120</v>
@@ -2457,60 +2487,63 @@
         <v>46031</v>
       </c>
       <c r="Z2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>264</v>
+        <v>215</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>425</v>
+        <v>374</v>
       </c>
       <c r="E3" t="s">
-        <v>377</v>
+        <v>328</v>
       </c>
       <c r="F3" t="s">
-        <v>385</v>
+        <v>336</v>
       </c>
       <c r="G3" t="s">
-        <v>388</v>
+        <v>339</v>
       </c>
       <c r="H3" t="s">
-        <v>387</v>
+        <v>338</v>
       </c>
       <c r="I3" t="s">
-        <v>389</v>
+        <v>340</v>
       </c>
       <c r="J3" t="s">
-        <v>366</v>
+        <v>317</v>
       </c>
       <c r="L3" t="s">
-        <v>345</v>
+        <v>296</v>
       </c>
       <c r="M3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O3">
         <v>130</v>
       </c>
       <c r="P3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="Q3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="R3" t="s">
-        <v>346</v>
+        <v>297</v>
       </c>
       <c r="S3" t="s">
-        <v>424</v>
+        <v>373</v>
       </c>
       <c r="V3" t="s">
-        <v>19</v>
+        <v>529</v>
+      </c>
+      <c r="W3" t="s">
+        <v>517</v>
       </c>
       <c r="X3">
         <v>65</v>
@@ -2519,63 +2552,60 @@
         <v>46032</v>
       </c>
       <c r="Z3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>265</v>
+        <v>216</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>425</v>
+        <v>374</v>
       </c>
       <c r="E4" t="s">
-        <v>377</v>
+        <v>328</v>
       </c>
       <c r="F4" t="s">
-        <v>385</v>
+        <v>336</v>
       </c>
       <c r="G4" t="s">
-        <v>388</v>
+        <v>339</v>
       </c>
       <c r="H4" t="s">
-        <v>387</v>
+        <v>338</v>
       </c>
       <c r="I4" t="s">
-        <v>390</v>
+        <v>341</v>
       </c>
       <c r="K4" t="s">
-        <v>381</v>
+        <v>332</v>
       </c>
       <c r="L4" t="s">
-        <v>345</v>
+        <v>296</v>
       </c>
       <c r="M4" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="O4">
         <v>160</v>
       </c>
       <c r="P4" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="Q4" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="R4" t="s">
-        <v>346</v>
+        <v>297</v>
       </c>
       <c r="S4" t="s">
-        <v>424</v>
+        <v>373</v>
       </c>
       <c r="V4" t="s">
-        <v>23</v>
-      </c>
-      <c r="W4" t="s">
-        <v>24</v>
+        <v>530</v>
       </c>
       <c r="X4">
         <v>60</v>
@@ -2584,69 +2614,69 @@
         <v>46032</v>
       </c>
       <c r="Z4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>266</v>
+        <v>217</v>
       </c>
       <c r="B5" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="C5" t="s">
-        <v>425</v>
+        <v>374</v>
       </c>
       <c r="D5" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="E5" t="s">
-        <v>377</v>
+        <v>328</v>
       </c>
       <c r="F5" t="s">
-        <v>406</v>
+        <v>355</v>
       </c>
       <c r="G5" t="s">
-        <v>388</v>
+        <v>339</v>
       </c>
       <c r="H5" t="s">
-        <v>560</v>
+        <v>507</v>
       </c>
       <c r="I5" t="s">
-        <v>561</v>
+        <v>508</v>
       </c>
       <c r="J5" t="s">
-        <v>562</v>
+        <v>509</v>
       </c>
       <c r="K5" t="s">
-        <v>381</v>
+        <v>332</v>
       </c>
       <c r="L5" t="s">
-        <v>345</v>
+        <v>296</v>
       </c>
       <c r="M5" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O5">
         <v>410</v>
       </c>
       <c r="P5" t="s">
-        <v>564</v>
+        <v>511</v>
       </c>
       <c r="Q5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="R5" t="s">
-        <v>346</v>
+        <v>297</v>
       </c>
       <c r="S5" t="s">
-        <v>424</v>
+        <v>373</v>
       </c>
       <c r="V5" t="s">
-        <v>563</v>
+        <v>510</v>
       </c>
       <c r="W5" t="s">
-        <v>13</v>
+        <v>517</v>
       </c>
       <c r="X5">
         <v>90</v>
@@ -2655,57 +2685,57 @@
         <v>46032</v>
       </c>
       <c r="Z5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>267</v>
+        <v>218</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="E6" t="s">
-        <v>427</v>
+        <v>376</v>
       </c>
       <c r="F6" t="s">
-        <v>391</v>
+        <v>342</v>
       </c>
       <c r="G6" t="s">
-        <v>392</v>
+        <v>343</v>
       </c>
       <c r="H6" t="s">
-        <v>393</v>
+        <v>344</v>
       </c>
       <c r="K6" t="s">
-        <v>381</v>
+        <v>332</v>
       </c>
       <c r="L6" t="s">
-        <v>345</v>
+        <v>296</v>
       </c>
       <c r="M6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="O6">
         <v>120</v>
       </c>
       <c r="P6" t="s">
-        <v>28</v>
+        <v>521</v>
       </c>
       <c r="Q6" t="s">
-        <v>17</v>
+        <v>522</v>
       </c>
       <c r="R6" t="s">
-        <v>346</v>
+        <v>297</v>
       </c>
       <c r="S6" t="s">
-        <v>424</v>
+        <v>373</v>
       </c>
       <c r="V6" t="s">
-        <v>30</v>
+        <v>531</v>
       </c>
       <c r="X6">
         <v>60</v>
@@ -2714,66 +2744,66 @@
         <v>46032</v>
       </c>
       <c r="Z6" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>268</v>
+        <v>219</v>
       </c>
       <c r="B7" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="E7" t="s">
-        <v>394</v>
+        <v>345</v>
       </c>
       <c r="F7" t="s">
-        <v>350</v>
+        <v>301</v>
       </c>
       <c r="G7" t="s">
-        <v>395</v>
+        <v>346</v>
       </c>
       <c r="H7" t="s">
-        <v>396</v>
+        <v>347</v>
       </c>
       <c r="I7" t="s">
-        <v>397</v>
+        <v>348</v>
       </c>
       <c r="J7" t="s">
-        <v>354</v>
+        <v>305</v>
       </c>
       <c r="K7" t="s">
-        <v>381</v>
+        <v>332</v>
       </c>
       <c r="L7" t="s">
-        <v>345</v>
+        <v>296</v>
       </c>
       <c r="M7" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="O7">
         <v>118</v>
       </c>
       <c r="P7" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="Q7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="R7" t="s">
-        <v>346</v>
+        <v>297</v>
       </c>
       <c r="S7" t="s">
-        <v>424</v>
+        <v>373</v>
       </c>
       <c r="V7" t="s">
-        <v>35</v>
+        <v>532</v>
       </c>
       <c r="W7" t="s">
-        <v>13</v>
+        <v>517</v>
       </c>
       <c r="X7">
         <v>180</v>
@@ -2782,66 +2812,66 @@
         <v>46032</v>
       </c>
       <c r="Z7" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>269</v>
+        <v>220</v>
       </c>
       <c r="B8" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C8" t="s">
-        <v>425</v>
+        <v>374</v>
       </c>
       <c r="E8" t="s">
-        <v>394</v>
+        <v>345</v>
       </c>
       <c r="F8" t="s">
-        <v>350</v>
+        <v>301</v>
       </c>
       <c r="G8" t="s">
-        <v>395</v>
+        <v>346</v>
       </c>
       <c r="H8" t="s">
-        <v>396</v>
+        <v>347</v>
       </c>
       <c r="I8" t="s">
-        <v>397</v>
+        <v>348</v>
       </c>
       <c r="J8" t="s">
-        <v>354</v>
+        <v>305</v>
       </c>
       <c r="K8" t="s">
-        <v>381</v>
+        <v>332</v>
       </c>
       <c r="L8" t="s">
-        <v>345</v>
+        <v>296</v>
       </c>
       <c r="M8" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="O8">
         <v>572</v>
       </c>
       <c r="P8" t="s">
-        <v>327</v>
+        <v>278</v>
       </c>
       <c r="Q8" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="R8" t="s">
-        <v>346</v>
+        <v>297</v>
       </c>
       <c r="S8" t="s">
-        <v>424</v>
+        <v>373</v>
       </c>
       <c r="V8" t="s">
-        <v>38</v>
+        <v>533</v>
       </c>
       <c r="W8" t="s">
-        <v>13</v>
+        <v>517</v>
       </c>
       <c r="X8">
         <v>140</v>
@@ -2850,66 +2880,66 @@
         <v>46032</v>
       </c>
       <c r="Z8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>270</v>
+        <v>221</v>
       </c>
       <c r="B9" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>425</v>
+        <v>374</v>
       </c>
       <c r="E9" t="s">
-        <v>394</v>
+        <v>345</v>
       </c>
       <c r="F9" t="s">
-        <v>350</v>
+        <v>301</v>
       </c>
       <c r="G9" t="s">
-        <v>395</v>
+        <v>346</v>
       </c>
       <c r="H9" t="s">
-        <v>483</v>
+        <v>432</v>
       </c>
       <c r="I9" t="s">
-        <v>397</v>
+        <v>348</v>
       </c>
       <c r="J9" t="s">
-        <v>354</v>
+        <v>305</v>
       </c>
       <c r="K9" t="s">
-        <v>381</v>
+        <v>332</v>
       </c>
       <c r="L9" t="s">
-        <v>345</v>
+        <v>296</v>
       </c>
       <c r="M9" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="O9">
         <v>81</v>
       </c>
       <c r="P9" t="s">
-        <v>327</v>
+        <v>520</v>
       </c>
       <c r="Q9" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="R9" t="s">
-        <v>346</v>
+        <v>297</v>
       </c>
       <c r="S9" t="s">
-        <v>424</v>
+        <v>373</v>
       </c>
       <c r="V9" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="W9" t="s">
-        <v>13</v>
+        <v>517</v>
       </c>
       <c r="X9">
         <v>45</v>
@@ -2918,119 +2948,125 @@
         <v>46032</v>
       </c>
       <c r="Z9" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:26" ht="18.75" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
-        <v>271</v>
+        <v>222</v>
       </c>
       <c r="B10" t="s">
-        <v>43</v>
+        <v>514</v>
       </c>
       <c r="C10" t="s">
-        <v>425</v>
+        <v>515</v>
       </c>
       <c r="E10" t="s">
-        <v>398</v>
+        <v>516</v>
       </c>
       <c r="F10" t="s">
-        <v>400</v>
+        <v>301</v>
       </c>
       <c r="G10" t="s">
-        <v>399</v>
+        <v>349</v>
+      </c>
+      <c r="H10" t="s">
+        <v>513</v>
       </c>
       <c r="I10" t="s">
-        <v>401</v>
+        <v>350</v>
       </c>
       <c r="J10" t="s">
-        <v>348</v>
+        <v>512</v>
       </c>
       <c r="L10" t="s">
-        <v>345</v>
+        <v>296</v>
       </c>
       <c r="M10" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="O10">
         <v>171</v>
       </c>
       <c r="P10" t="s">
-        <v>44</v>
+        <v>518</v>
       </c>
       <c r="Q10" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="R10" t="s">
-        <v>346</v>
+        <v>297</v>
       </c>
       <c r="S10" t="s">
-        <v>424</v>
+        <v>373</v>
       </c>
       <c r="V10" t="s">
-        <v>46</v>
+        <v>519</v>
+      </c>
+      <c r="W10" t="s">
+        <v>517</v>
       </c>
       <c r="X10">
-        <v>40</v>
+        <v>150</v>
       </c>
       <c r="Y10" s="1">
-        <v>46032</v>
+        <v>46073</v>
       </c>
       <c r="Z10" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>272</v>
+        <v>223</v>
       </c>
       <c r="B11" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="C11" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="E11" t="s">
-        <v>495</v>
+        <v>444</v>
       </c>
       <c r="G11" t="s">
-        <v>399</v>
+        <v>349</v>
       </c>
       <c r="H11" t="s">
-        <v>484</v>
+        <v>433</v>
       </c>
       <c r="I11" t="s">
-        <v>403</v>
+        <v>352</v>
       </c>
       <c r="J11" t="s">
-        <v>404</v>
+        <v>353</v>
       </c>
       <c r="L11" t="s">
-        <v>345</v>
+        <v>296</v>
       </c>
       <c r="M11" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="O11">
         <v>204</v>
       </c>
       <c r="P11" t="s">
-        <v>327</v>
+        <v>278</v>
       </c>
       <c r="Q11" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="R11" t="s">
-        <v>346</v>
+        <v>297</v>
       </c>
       <c r="S11" t="s">
-        <v>424</v>
+        <v>373</v>
       </c>
       <c r="V11" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="W11" t="s">
-        <v>13</v>
+        <v>517</v>
       </c>
       <c r="X11">
         <v>30</v>
@@ -3039,66 +3075,66 @@
         <v>46032</v>
       </c>
       <c r="Z11" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>273</v>
+        <v>224</v>
       </c>
       <c r="B12" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="C12" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="E12" t="s">
-        <v>377</v>
+        <v>328</v>
       </c>
       <c r="F12" t="s">
-        <v>406</v>
+        <v>355</v>
       </c>
       <c r="G12" t="s">
-        <v>388</v>
+        <v>339</v>
       </c>
       <c r="H12" t="s">
-        <v>405</v>
+        <v>354</v>
       </c>
       <c r="I12" t="s">
-        <v>379</v>
+        <v>330</v>
       </c>
       <c r="J12" t="s">
-        <v>380</v>
+        <v>331</v>
       </c>
       <c r="K12" t="s">
-        <v>381</v>
+        <v>332</v>
       </c>
       <c r="L12" s="4" t="s">
-        <v>498</v>
+        <v>447</v>
       </c>
       <c r="M12" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="O12">
         <v>500</v>
       </c>
       <c r="P12" t="s">
-        <v>327</v>
+        <v>278</v>
       </c>
       <c r="Q12" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="R12" t="s">
-        <v>346</v>
+        <v>297</v>
       </c>
       <c r="S12" t="s">
-        <v>424</v>
+        <v>373</v>
       </c>
       <c r="V12" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="W12" t="s">
-        <v>13</v>
+        <v>517</v>
       </c>
       <c r="X12">
         <v>120</v>
@@ -3107,63 +3143,63 @@
         <v>46039</v>
       </c>
       <c r="Z12" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>274</v>
+        <v>225</v>
       </c>
       <c r="B13" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="C13" t="s">
-        <v>425</v>
+        <v>374</v>
       </c>
       <c r="D13" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="E13" t="s">
-        <v>430</v>
+        <v>379</v>
       </c>
       <c r="F13" t="s">
-        <v>369</v>
+        <v>320</v>
       </c>
       <c r="G13" t="s">
-        <v>388</v>
+        <v>339</v>
       </c>
       <c r="H13" t="s">
-        <v>407</v>
+        <v>356</v>
       </c>
       <c r="I13" t="s">
-        <v>408</v>
+        <v>357</v>
       </c>
       <c r="L13" t="s">
-        <v>345</v>
+        <v>296</v>
       </c>
       <c r="M13" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="O13">
         <v>550</v>
       </c>
       <c r="P13" t="s">
-        <v>327</v>
+        <v>278</v>
       </c>
       <c r="Q13" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="R13" t="s">
-        <v>346</v>
+        <v>297</v>
       </c>
       <c r="S13" t="s">
-        <v>424</v>
+        <v>373</v>
       </c>
       <c r="V13" t="s">
-        <v>59</v>
+        <v>534</v>
       </c>
       <c r="W13" t="s">
-        <v>13</v>
+        <v>517</v>
       </c>
       <c r="X13">
         <v>90</v>
@@ -3172,66 +3208,66 @@
         <v>46032</v>
       </c>
       <c r="Z13" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>275</v>
+        <v>226</v>
       </c>
       <c r="B14" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="C14" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="E14" t="s">
-        <v>377</v>
+        <v>328</v>
       </c>
       <c r="F14" t="s">
-        <v>406</v>
+        <v>355</v>
       </c>
       <c r="G14" t="s">
-        <v>388</v>
+        <v>339</v>
       </c>
       <c r="H14" t="s">
-        <v>405</v>
+        <v>354</v>
       </c>
       <c r="I14" t="s">
-        <v>375</v>
+        <v>326</v>
       </c>
       <c r="J14" t="s">
-        <v>376</v>
+        <v>327</v>
       </c>
       <c r="K14" t="s">
-        <v>378</v>
+        <v>329</v>
       </c>
       <c r="L14" t="s">
-        <v>345</v>
+        <v>296</v>
       </c>
       <c r="M14" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="O14">
         <v>450</v>
       </c>
       <c r="P14" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="Q14" t="s">
         <v>10</v>
       </c>
       <c r="R14" t="s">
-        <v>346</v>
+        <v>297</v>
       </c>
       <c r="S14" t="s">
-        <v>424</v>
+        <v>373</v>
       </c>
       <c r="V14" s="5" t="s">
-        <v>500</v>
+        <v>535</v>
       </c>
       <c r="W14" t="s">
-        <v>13</v>
+        <v>517</v>
       </c>
       <c r="X14">
         <v>120</v>
@@ -3240,66 +3276,66 @@
         <v>46032</v>
       </c>
       <c r="Z14" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>276</v>
+        <v>227</v>
       </c>
       <c r="B15" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="C15" t="s">
-        <v>425</v>
+        <v>374</v>
       </c>
       <c r="D15" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="E15" t="s">
-        <v>431</v>
+        <v>380</v>
       </c>
       <c r="F15" t="s">
-        <v>406</v>
+        <v>355</v>
       </c>
       <c r="G15" t="s">
-        <v>388</v>
+        <v>339</v>
       </c>
       <c r="H15" t="s">
-        <v>409</v>
+        <v>358</v>
       </c>
       <c r="I15" t="s">
-        <v>410</v>
+        <v>359</v>
       </c>
       <c r="J15" t="s">
-        <v>411</v>
+        <v>360</v>
       </c>
       <c r="L15" t="s">
-        <v>345</v>
+        <v>296</v>
       </c>
       <c r="M15" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="O15">
         <v>207</v>
       </c>
       <c r="P15" t="s">
-        <v>327</v>
+        <v>278</v>
       </c>
       <c r="Q15" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="R15" t="s">
-        <v>346</v>
+        <v>297</v>
       </c>
       <c r="S15" t="s">
-        <v>424</v>
+        <v>373</v>
       </c>
       <c r="V15" t="s">
-        <v>67</v>
+        <v>536</v>
       </c>
       <c r="W15" t="s">
-        <v>13</v>
+        <v>517</v>
       </c>
       <c r="X15">
         <v>75</v>
@@ -3308,60 +3344,60 @@
         <v>46032</v>
       </c>
       <c r="Z15" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:26" ht="18.75" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
-        <v>277</v>
+        <v>228</v>
       </c>
       <c r="B16" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="C16" t="s">
-        <v>425</v>
+        <v>374</v>
       </c>
       <c r="E16" t="s">
-        <v>533</v>
+        <v>481</v>
       </c>
       <c r="F16" t="s">
-        <v>412</v>
+        <v>361</v>
       </c>
       <c r="G16" t="s">
-        <v>392</v>
+        <v>343</v>
       </c>
       <c r="I16" t="s">
-        <v>413</v>
+        <v>362</v>
       </c>
       <c r="K16" t="s">
-        <v>381</v>
+        <v>332</v>
       </c>
       <c r="L16" t="s">
-        <v>345</v>
+        <v>296</v>
       </c>
       <c r="M16" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="O16">
         <v>2900</v>
       </c>
       <c r="P16" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="Q16" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="R16" t="s">
-        <v>346</v>
+        <v>297</v>
       </c>
       <c r="S16" t="s">
-        <v>424</v>
+        <v>373</v>
       </c>
       <c r="V16" t="s">
-        <v>71</v>
+        <v>537</v>
       </c>
       <c r="W16" t="s">
-        <v>13</v>
+        <v>517</v>
       </c>
       <c r="X16">
         <v>200</v>
@@ -3370,66 +3406,66 @@
         <v>46031</v>
       </c>
       <c r="Z16" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>278</v>
+        <v>229</v>
       </c>
       <c r="B17" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="C17" t="s">
-        <v>425</v>
+        <v>374</v>
       </c>
       <c r="E17" t="s">
-        <v>432</v>
+        <v>381</v>
       </c>
       <c r="F17" t="s">
-        <v>414</v>
+        <v>363</v>
       </c>
       <c r="G17" t="s">
-        <v>384</v>
+        <v>335</v>
       </c>
       <c r="H17" t="s">
-        <v>364</v>
+        <v>315</v>
       </c>
       <c r="I17" t="s">
-        <v>356</v>
+        <v>307</v>
       </c>
       <c r="J17" t="s">
-        <v>357</v>
+        <v>308</v>
       </c>
       <c r="L17" t="s">
-        <v>345</v>
+        <v>296</v>
       </c>
       <c r="M17" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="N17" t="s">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="O17">
         <v>75</v>
       </c>
       <c r="P17" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="Q17" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="R17" t="s">
-        <v>346</v>
+        <v>297</v>
       </c>
       <c r="S17" t="s">
-        <v>344</v>
+        <v>295</v>
       </c>
       <c r="V17" t="s">
-        <v>76</v>
+        <v>538</v>
       </c>
       <c r="W17" t="s">
-        <v>13</v>
+        <v>517</v>
       </c>
       <c r="X17">
         <v>200</v>
@@ -3438,63 +3474,63 @@
         <v>46031</v>
       </c>
       <c r="Z17" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>279</v>
+        <v>230</v>
       </c>
       <c r="B18" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="C18" t="s">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="E18" t="s">
-        <v>415</v>
+        <v>364</v>
       </c>
       <c r="F18" t="s">
-        <v>350</v>
+        <v>301</v>
       </c>
       <c r="G18" t="s">
-        <v>416</v>
+        <v>365</v>
       </c>
       <c r="H18" t="s">
-        <v>417</v>
+        <v>366</v>
       </c>
       <c r="I18" t="s">
-        <v>418</v>
+        <v>367</v>
       </c>
       <c r="J18" t="s">
-        <v>354</v>
+        <v>305</v>
       </c>
       <c r="L18" t="s">
-        <v>345</v>
+        <v>296</v>
       </c>
       <c r="M18" t="s">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="O18">
         <v>156</v>
       </c>
       <c r="P18" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="Q18" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="R18" t="s">
-        <v>346</v>
+        <v>297</v>
       </c>
       <c r="S18" t="s">
-        <v>424</v>
+        <v>373</v>
       </c>
       <c r="V18" t="s">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="W18" t="s">
-        <v>13</v>
+        <v>525</v>
       </c>
       <c r="X18">
         <v>90</v>
@@ -3503,66 +3539,66 @@
         <v>46039</v>
       </c>
       <c r="Z18" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>280</v>
+        <v>231</v>
       </c>
       <c r="B19" t="s">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="C19" t="s">
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="D19" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="E19" t="s">
-        <v>479</v>
+        <v>428</v>
       </c>
       <c r="F19" t="s">
-        <v>385</v>
+        <v>336</v>
       </c>
       <c r="G19" t="s">
-        <v>399</v>
+        <v>349</v>
       </c>
       <c r="H19" t="s">
-        <v>419</v>
+        <v>368</v>
       </c>
       <c r="I19" t="s">
-        <v>355</v>
+        <v>306</v>
       </c>
       <c r="J19" t="s">
-        <v>366</v>
+        <v>317</v>
       </c>
       <c r="L19" t="s">
-        <v>345</v>
+        <v>296</v>
       </c>
       <c r="M19" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="O19">
         <v>341</v>
       </c>
       <c r="P19" t="s">
-        <v>85</v>
+        <v>125</v>
       </c>
       <c r="Q19" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="R19" t="s">
-        <v>349</v>
+        <v>300</v>
       </c>
       <c r="S19" t="s">
-        <v>424</v>
+        <v>373</v>
       </c>
       <c r="V19" t="s">
-        <v>88</v>
+        <v>539</v>
       </c>
       <c r="W19" t="s">
-        <v>89</v>
+        <v>524</v>
       </c>
       <c r="X19">
         <v>180</v>
@@ -3571,60 +3607,60 @@
         <v>46031</v>
       </c>
       <c r="Z19" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>281</v>
+        <v>232</v>
       </c>
       <c r="B20" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="C20" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="E20" t="s">
-        <v>367</v>
+        <v>318</v>
       </c>
       <c r="F20" t="s">
-        <v>369</v>
+        <v>320</v>
       </c>
       <c r="G20" t="s">
-        <v>438</v>
+        <v>387</v>
       </c>
       <c r="H20" t="s">
-        <v>368</v>
+        <v>319</v>
       </c>
       <c r="J20" t="s">
-        <v>348</v>
+        <v>299</v>
       </c>
       <c r="L20" t="s">
-        <v>343</v>
+        <v>294</v>
       </c>
       <c r="M20" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="O20">
         <v>1400</v>
       </c>
       <c r="P20" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="Q20" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="R20" t="s">
-        <v>346</v>
+        <v>297</v>
       </c>
       <c r="S20" t="s">
-        <v>344</v>
+        <v>295</v>
       </c>
       <c r="V20" t="s">
-        <v>94</v>
+        <v>540</v>
       </c>
       <c r="W20" t="s">
-        <v>13</v>
+        <v>517</v>
       </c>
       <c r="X20">
         <v>100</v>
@@ -3633,63 +3669,63 @@
         <v>46031</v>
       </c>
       <c r="Z20" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="21" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>282</v>
+        <v>233</v>
       </c>
       <c r="B21" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="C21" t="s">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="E21" t="s">
-        <v>420</v>
+        <v>369</v>
       </c>
       <c r="F21" t="s">
-        <v>406</v>
+        <v>355</v>
       </c>
       <c r="G21" t="s">
-        <v>392</v>
+        <v>343</v>
       </c>
       <c r="H21" t="s">
-        <v>482</v>
+        <v>431</v>
       </c>
       <c r="I21" t="s">
-        <v>421</v>
+        <v>370</v>
       </c>
       <c r="J21" t="s">
-        <v>348</v>
+        <v>299</v>
       </c>
       <c r="L21" t="s">
-        <v>345</v>
+        <v>296</v>
       </c>
       <c r="M21" t="s">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="O21">
         <v>414</v>
       </c>
       <c r="P21" t="s">
-        <v>327</v>
+        <v>278</v>
       </c>
       <c r="Q21" t="s">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="R21" t="s">
-        <v>346</v>
+        <v>297</v>
       </c>
       <c r="S21" t="s">
-        <v>424</v>
+        <v>373</v>
       </c>
       <c r="V21" t="s">
-        <v>98</v>
+        <v>541</v>
       </c>
       <c r="W21" t="s">
-        <v>13</v>
+        <v>517</v>
       </c>
       <c r="X21">
         <v>150</v>
@@ -3698,63 +3734,63 @@
         <v>46032</v>
       </c>
       <c r="Z21" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="22" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>283</v>
+        <v>234</v>
       </c>
       <c r="B22" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="C22" t="s">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="E22" t="s">
-        <v>420</v>
+        <v>369</v>
       </c>
       <c r="F22" t="s">
-        <v>406</v>
+        <v>355</v>
       </c>
       <c r="G22" t="s">
-        <v>392</v>
+        <v>343</v>
       </c>
       <c r="H22" t="s">
-        <v>482</v>
+        <v>431</v>
       </c>
       <c r="I22" t="s">
-        <v>422</v>
+        <v>371</v>
       </c>
       <c r="J22" t="s">
-        <v>348</v>
+        <v>299</v>
       </c>
       <c r="L22" t="s">
-        <v>345</v>
+        <v>296</v>
       </c>
       <c r="M22" t="s">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="O22">
         <v>950</v>
       </c>
       <c r="P22" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="Q22" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="R22" t="s">
-        <v>346</v>
+        <v>297</v>
       </c>
       <c r="S22" t="s">
-        <v>424</v>
+        <v>373</v>
       </c>
       <c r="V22" t="s">
-        <v>102</v>
+        <v>543</v>
       </c>
       <c r="W22" t="s">
-        <v>13</v>
+        <v>517</v>
       </c>
       <c r="X22">
         <v>150</v>
@@ -3763,63 +3799,63 @@
         <v>46032</v>
       </c>
       <c r="Z22" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="23" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>284</v>
+        <v>235</v>
       </c>
       <c r="B23" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="C23" t="s">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="E23" t="s">
-        <v>420</v>
+        <v>369</v>
       </c>
       <c r="F23" t="s">
-        <v>406</v>
+        <v>355</v>
       </c>
       <c r="G23" t="s">
+        <v>343</v>
+      </c>
+      <c r="H23" t="s">
+        <v>431</v>
+      </c>
+      <c r="I23" t="s">
+        <v>372</v>
+      </c>
+      <c r="J23" t="s">
         <v>392</v>
       </c>
-      <c r="H23" t="s">
-        <v>482</v>
-      </c>
-      <c r="I23" t="s">
-        <v>423</v>
-      </c>
-      <c r="J23" t="s">
-        <v>443</v>
-      </c>
       <c r="L23" t="s">
-        <v>345</v>
+        <v>296</v>
       </c>
       <c r="M23" t="s">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="O23">
         <v>1777</v>
       </c>
       <c r="P23" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="Q23" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="R23" t="s">
-        <v>346</v>
+        <v>297</v>
       </c>
       <c r="S23" t="s">
-        <v>424</v>
+        <v>373</v>
       </c>
       <c r="V23" t="s">
-        <v>105</v>
+        <v>542</v>
       </c>
       <c r="W23" t="s">
-        <v>13</v>
+        <v>517</v>
       </c>
       <c r="X23">
         <v>250</v>
@@ -3828,69 +3864,69 @@
         <v>46032</v>
       </c>
       <c r="Z23" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="24" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>285</v>
+        <v>236</v>
       </c>
       <c r="B24" t="s">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="C24" t="s">
-        <v>425</v>
+        <v>374</v>
       </c>
       <c r="D24" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="E24" t="s">
-        <v>490</v>
+        <v>439</v>
       </c>
       <c r="F24" t="s">
-        <v>406</v>
+        <v>355</v>
       </c>
       <c r="G24" t="s">
-        <v>392</v>
+        <v>343</v>
       </c>
       <c r="H24" t="s">
-        <v>436</v>
+        <v>385</v>
       </c>
       <c r="I24" t="s">
-        <v>437</v>
+        <v>386</v>
       </c>
       <c r="J24" t="s">
-        <v>354</v>
+        <v>305</v>
       </c>
       <c r="L24" t="s">
-        <v>345</v>
+        <v>296</v>
       </c>
       <c r="M24" t="s">
-        <v>109</v>
+        <v>87</v>
       </c>
       <c r="N24" t="s">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="O24">
         <v>63</v>
       </c>
       <c r="P24" t="s">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="Q24" t="s">
-        <v>108</v>
+        <v>86</v>
       </c>
       <c r="R24" t="s">
-        <v>346</v>
+        <v>297</v>
       </c>
       <c r="S24" t="s">
-        <v>424</v>
+        <v>373</v>
       </c>
       <c r="V24" t="s">
-        <v>111</v>
+        <v>544</v>
       </c>
       <c r="W24" t="s">
-        <v>112</v>
+        <v>89</v>
       </c>
       <c r="X24">
         <v>70</v>
@@ -3899,66 +3935,66 @@
         <v>46032</v>
       </c>
       <c r="Z24" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="25" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>286</v>
+        <v>237</v>
       </c>
       <c r="B25" t="s">
-        <v>113</v>
+        <v>90</v>
       </c>
       <c r="C25" t="s">
-        <v>425</v>
+        <v>374</v>
       </c>
       <c r="E25" t="s">
-        <v>494</v>
+        <v>443</v>
       </c>
       <c r="F25" t="s">
-        <v>385</v>
+        <v>336</v>
       </c>
       <c r="G25" t="s">
-        <v>438</v>
+        <v>387</v>
       </c>
       <c r="H25" t="s">
-        <v>439</v>
+        <v>388</v>
       </c>
       <c r="I25" t="s">
-        <v>370</v>
+        <v>321</v>
       </c>
       <c r="J25" t="s">
-        <v>372</v>
+        <v>323</v>
       </c>
       <c r="K25" t="s">
-        <v>371</v>
+        <v>322</v>
       </c>
       <c r="L25" t="s">
-        <v>345</v>
+        <v>296</v>
       </c>
       <c r="M25" t="s">
-        <v>116</v>
+        <v>93</v>
       </c>
       <c r="O25">
         <v>1000</v>
       </c>
       <c r="P25" t="s">
-        <v>114</v>
+        <v>91</v>
       </c>
       <c r="Q25" t="s">
-        <v>115</v>
+        <v>92</v>
       </c>
       <c r="R25" t="s">
-        <v>346</v>
+        <v>297</v>
       </c>
       <c r="S25" t="s">
-        <v>424</v>
+        <v>373</v>
       </c>
       <c r="V25" t="s">
-        <v>117</v>
+        <v>94</v>
       </c>
       <c r="W25" t="s">
-        <v>13</v>
+        <v>517</v>
       </c>
       <c r="X25">
         <v>150</v>
@@ -3967,66 +4003,66 @@
         <v>46031</v>
       </c>
       <c r="Z25" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="26" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>287</v>
+        <v>238</v>
       </c>
       <c r="B26" t="s">
-        <v>118</v>
+        <v>95</v>
       </c>
       <c r="C26" t="s">
-        <v>119</v>
+        <v>96</v>
       </c>
       <c r="E26" t="s">
-        <v>440</v>
+        <v>389</v>
       </c>
       <c r="F26" t="s">
-        <v>350</v>
+        <v>301</v>
       </c>
       <c r="G26" t="s">
-        <v>441</v>
+        <v>390</v>
       </c>
       <c r="H26" t="s">
-        <v>471</v>
+        <v>420</v>
       </c>
       <c r="I26" t="s">
-        <v>442</v>
+        <v>391</v>
       </c>
       <c r="J26" t="s">
-        <v>348</v>
+        <v>299</v>
       </c>
       <c r="K26" t="s">
-        <v>352</v>
+        <v>303</v>
       </c>
       <c r="L26" s="4" t="s">
-        <v>498</v>
+        <v>447</v>
       </c>
       <c r="M26" t="s">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="O26">
         <v>370</v>
       </c>
       <c r="P26" t="s">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="Q26" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="R26" t="s">
-        <v>346</v>
+        <v>297</v>
       </c>
       <c r="S26" t="s">
-        <v>424</v>
+        <v>373</v>
       </c>
       <c r="V26" t="s">
-        <v>122</v>
+        <v>99</v>
       </c>
       <c r="W26" t="s">
-        <v>13</v>
+        <v>517</v>
       </c>
       <c r="X26">
         <v>850</v>
@@ -4035,63 +4071,63 @@
         <v>46030</v>
       </c>
       <c r="Z26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="27" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>288</v>
+        <v>239</v>
       </c>
       <c r="B27" t="s">
-        <v>118</v>
+        <v>95</v>
       </c>
       <c r="C27" t="s">
-        <v>123</v>
+        <v>100</v>
       </c>
       <c r="E27" t="s">
-        <v>440</v>
+        <v>389</v>
       </c>
       <c r="F27" t="s">
-        <v>350</v>
+        <v>301</v>
       </c>
       <c r="G27" t="s">
-        <v>441</v>
+        <v>390</v>
       </c>
       <c r="H27" t="s">
-        <v>471</v>
+        <v>420</v>
       </c>
       <c r="I27" t="s">
-        <v>444</v>
+        <v>393</v>
       </c>
       <c r="J27" t="s">
-        <v>348</v>
+        <v>299</v>
       </c>
       <c r="K27" t="s">
-        <v>445</v>
+        <v>394</v>
       </c>
       <c r="L27" t="s">
-        <v>343</v>
+        <v>294</v>
       </c>
       <c r="M27" t="s">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="O27">
         <v>90</v>
       </c>
       <c r="P27" t="s">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="Q27" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="R27" t="s">
-        <v>346</v>
+        <v>297</v>
       </c>
       <c r="S27" t="s">
-        <v>424</v>
+        <v>373</v>
       </c>
       <c r="V27" t="s">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="X27">
         <v>30</v>
@@ -4100,66 +4136,66 @@
         <v>46032</v>
       </c>
       <c r="Z27" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="28" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>289</v>
+        <v>240</v>
       </c>
       <c r="B28" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="C28" t="s">
-        <v>126</v>
+        <v>103</v>
       </c>
       <c r="D28" t="s">
-        <v>127</v>
+        <v>104</v>
       </c>
       <c r="E28" t="s">
-        <v>420</v>
+        <v>369</v>
       </c>
       <c r="F28" t="s">
-        <v>406</v>
+        <v>355</v>
       </c>
       <c r="G28" t="s">
-        <v>392</v>
+        <v>343</v>
       </c>
       <c r="H28" t="s">
-        <v>482</v>
+        <v>431</v>
       </c>
       <c r="I28" t="s">
-        <v>359</v>
+        <v>310</v>
       </c>
       <c r="J28" t="s">
-        <v>348</v>
+        <v>299</v>
       </c>
       <c r="L28" t="s">
-        <v>345</v>
+        <v>296</v>
       </c>
       <c r="M28" t="s">
-        <v>129</v>
+        <v>106</v>
       </c>
       <c r="O28">
         <v>1700</v>
       </c>
       <c r="P28" t="s">
-        <v>128</v>
+        <v>105</v>
       </c>
       <c r="Q28" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="R28" t="s">
-        <v>346</v>
+        <v>297</v>
       </c>
       <c r="S28" t="s">
-        <v>424</v>
+        <v>373</v>
       </c>
       <c r="V28" t="s">
-        <v>130</v>
+        <v>107</v>
       </c>
       <c r="W28" t="s">
-        <v>13</v>
+        <v>517</v>
       </c>
       <c r="X28">
         <v>200</v>
@@ -4168,63 +4204,63 @@
         <v>46031</v>
       </c>
       <c r="Z28" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="29" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>290</v>
+        <v>241</v>
       </c>
       <c r="B29" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="C29" t="s">
-        <v>131</v>
+        <v>108</v>
       </c>
       <c r="E29" t="s">
-        <v>420</v>
+        <v>369</v>
       </c>
       <c r="F29" t="s">
-        <v>406</v>
+        <v>355</v>
       </c>
       <c r="G29" t="s">
-        <v>392</v>
+        <v>343</v>
       </c>
       <c r="H29" t="s">
-        <v>446</v>
+        <v>395</v>
       </c>
       <c r="I29" t="s">
-        <v>447</v>
+        <v>396</v>
       </c>
       <c r="J29" t="s">
-        <v>348</v>
+        <v>299</v>
       </c>
       <c r="L29" t="s">
-        <v>345</v>
+        <v>296</v>
       </c>
       <c r="M29" t="s">
-        <v>134</v>
+        <v>111</v>
       </c>
       <c r="O29">
         <v>225</v>
       </c>
       <c r="P29" t="s">
-        <v>132</v>
+        <v>109</v>
       </c>
       <c r="Q29" t="s">
-        <v>133</v>
+        <v>110</v>
       </c>
       <c r="R29" t="s">
-        <v>346</v>
+        <v>297</v>
       </c>
       <c r="S29" t="s">
-        <v>424</v>
+        <v>373</v>
       </c>
       <c r="V29" t="s">
-        <v>135</v>
+        <v>112</v>
       </c>
       <c r="W29" t="s">
-        <v>112</v>
+        <v>89</v>
       </c>
       <c r="X29">
         <v>50</v>
@@ -4233,63 +4269,63 @@
         <v>46032</v>
       </c>
       <c r="Z29" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="30" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>291</v>
+        <v>242</v>
       </c>
       <c r="B30" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="C30" t="s">
-        <v>425</v>
+        <v>374</v>
       </c>
       <c r="E30" t="s">
-        <v>492</v>
+        <v>441</v>
       </c>
       <c r="F30" t="s">
-        <v>369</v>
+        <v>320</v>
       </c>
       <c r="G30" t="s">
-        <v>438</v>
+        <v>387</v>
       </c>
       <c r="H30" t="s">
-        <v>448</v>
+        <v>397</v>
       </c>
       <c r="I30" t="s">
-        <v>449</v>
+        <v>398</v>
       </c>
       <c r="J30" t="s">
-        <v>348</v>
+        <v>299</v>
       </c>
       <c r="L30" t="s">
-        <v>345</v>
+        <v>296</v>
       </c>
       <c r="M30" t="s">
-        <v>136</v>
+        <v>113</v>
       </c>
       <c r="O30">
         <v>160</v>
       </c>
       <c r="P30" t="s">
-        <v>327</v>
+        <v>278</v>
       </c>
       <c r="Q30" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="R30" t="s">
-        <v>346</v>
+        <v>297</v>
       </c>
       <c r="S30" t="s">
-        <v>424</v>
+        <v>373</v>
       </c>
       <c r="V30" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="W30" t="s">
-        <v>13</v>
+        <v>517</v>
       </c>
       <c r="X30">
         <v>100</v>
@@ -4298,60 +4334,60 @@
         <v>46032</v>
       </c>
       <c r="Z30" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="31" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>292</v>
+        <v>243</v>
       </c>
       <c r="B31" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="C31" t="s">
-        <v>126</v>
+        <v>103</v>
       </c>
       <c r="E31" t="s">
-        <v>420</v>
+        <v>369</v>
       </c>
       <c r="F31" t="s">
-        <v>406</v>
+        <v>355</v>
       </c>
       <c r="G31" t="s">
-        <v>392</v>
+        <v>343</v>
       </c>
       <c r="H31" t="s">
-        <v>482</v>
+        <v>431</v>
       </c>
       <c r="J31" t="s">
-        <v>348</v>
+        <v>299</v>
       </c>
       <c r="K31" t="s">
-        <v>450</v>
+        <v>399</v>
       </c>
       <c r="L31" t="s">
-        <v>345</v>
+        <v>296</v>
       </c>
       <c r="M31" t="s">
-        <v>138</v>
+        <v>115</v>
       </c>
       <c r="O31">
         <v>125</v>
       </c>
       <c r="P31" t="s">
-        <v>327</v>
+        <v>278</v>
       </c>
       <c r="Q31" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="R31" t="s">
-        <v>346</v>
+        <v>297</v>
       </c>
       <c r="S31" t="s">
-        <v>424</v>
+        <v>373</v>
       </c>
       <c r="V31" t="s">
-        <v>139</v>
+        <v>545</v>
       </c>
       <c r="X31">
         <v>70</v>
@@ -4360,63 +4396,63 @@
         <v>46032</v>
       </c>
       <c r="Z31" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="32" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>293</v>
+        <v>244</v>
       </c>
       <c r="B32" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C32" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="E32" t="s">
-        <v>394</v>
+        <v>345</v>
       </c>
       <c r="F32" t="s">
-        <v>350</v>
+        <v>301</v>
       </c>
       <c r="G32" t="s">
-        <v>395</v>
+        <v>346</v>
       </c>
       <c r="H32" t="s">
-        <v>396</v>
+        <v>347</v>
       </c>
       <c r="I32" t="s">
-        <v>397</v>
+        <v>348</v>
       </c>
       <c r="J32" t="s">
-        <v>354</v>
+        <v>305</v>
       </c>
       <c r="K32" t="s">
-        <v>381</v>
+        <v>332</v>
       </c>
       <c r="L32" t="s">
-        <v>345</v>
+        <v>296</v>
       </c>
       <c r="M32" t="s">
-        <v>140</v>
+        <v>116</v>
       </c>
       <c r="O32">
         <v>24</v>
       </c>
       <c r="P32" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="Q32" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="R32" t="s">
-        <v>346</v>
+        <v>297</v>
       </c>
       <c r="S32" t="s">
-        <v>424</v>
+        <v>373</v>
       </c>
       <c r="V32" t="s">
-        <v>141</v>
+        <v>546</v>
       </c>
       <c r="X32">
         <v>15</v>
@@ -4425,63 +4461,63 @@
         <v>46032</v>
       </c>
       <c r="Z32" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="33" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="B33" t="s">
+        <v>72</v>
+      </c>
+      <c r="C33" t="s">
+        <v>73</v>
+      </c>
+      <c r="E33" t="s">
+        <v>318</v>
+      </c>
+      <c r="F33" t="s">
+        <v>320</v>
+      </c>
+      <c r="G33" t="s">
+        <v>387</v>
+      </c>
+      <c r="H33" t="s">
+        <v>319</v>
+      </c>
+      <c r="J33" t="s">
+        <v>401</v>
+      </c>
+      <c r="K33" t="s">
+        <v>400</v>
+      </c>
+      <c r="L33" t="s">
         <v>294</v>
       </c>
-      <c r="B33" t="s">
-        <v>90</v>
-      </c>
-      <c r="C33" t="s">
-        <v>91</v>
-      </c>
-      <c r="E33" t="s">
-        <v>367</v>
-      </c>
-      <c r="F33" t="s">
-        <v>369</v>
-      </c>
-      <c r="G33" t="s">
-        <v>438</v>
-      </c>
-      <c r="H33" t="s">
-        <v>368</v>
-      </c>
-      <c r="J33" t="s">
-        <v>452</v>
-      </c>
-      <c r="K33" t="s">
-        <v>451</v>
-      </c>
-      <c r="L33" t="s">
-        <v>343</v>
-      </c>
       <c r="M33" t="s">
-        <v>142</v>
+        <v>117</v>
       </c>
       <c r="O33">
         <v>115</v>
       </c>
       <c r="P33" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="Q33" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="R33" t="s">
-        <v>346</v>
+        <v>297</v>
       </c>
       <c r="S33" t="s">
-        <v>424</v>
+        <v>373</v>
       </c>
       <c r="V33" t="s">
-        <v>143</v>
+        <v>547</v>
       </c>
       <c r="W33" t="s">
-        <v>144</v>
+        <v>118</v>
       </c>
       <c r="X33">
         <v>25</v>
@@ -4490,66 +4526,66 @@
         <v>46032</v>
       </c>
       <c r="Z33" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="34" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>295</v>
+        <v>246</v>
       </c>
       <c r="B34" t="s">
-        <v>118</v>
+        <v>95</v>
       </c>
       <c r="C34" t="s">
-        <v>123</v>
+        <v>100</v>
       </c>
       <c r="E34" t="s">
-        <v>440</v>
+        <v>389</v>
       </c>
       <c r="F34" t="s">
-        <v>350</v>
+        <v>301</v>
       </c>
       <c r="G34" t="s">
-        <v>441</v>
+        <v>390</v>
       </c>
       <c r="H34" t="s">
-        <v>471</v>
+        <v>420</v>
       </c>
       <c r="I34" t="s">
-        <v>347</v>
+        <v>298</v>
       </c>
       <c r="J34" t="s">
-        <v>348</v>
+        <v>299</v>
       </c>
       <c r="K34" t="s">
-        <v>351</v>
+        <v>302</v>
       </c>
       <c r="L34" t="s">
-        <v>343</v>
+        <v>294</v>
       </c>
       <c r="M34" t="s">
-        <v>146</v>
+        <v>120</v>
       </c>
       <c r="O34">
         <v>4120</v>
       </c>
       <c r="P34" t="s">
-        <v>145</v>
+        <v>119</v>
       </c>
       <c r="Q34" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="R34" t="s">
-        <v>349</v>
+        <v>300</v>
       </c>
       <c r="S34" t="s">
-        <v>424</v>
+        <v>373</v>
       </c>
       <c r="V34" t="s">
-        <v>147</v>
+        <v>121</v>
       </c>
       <c r="W34" t="s">
-        <v>13</v>
+        <v>517</v>
       </c>
       <c r="X34">
         <v>1200</v>
@@ -4558,63 +4594,63 @@
         <v>46030</v>
       </c>
       <c r="Z34" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="35" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B35" t="s">
+        <v>122</v>
+      </c>
+      <c r="C35" t="s">
+        <v>374</v>
+      </c>
+      <c r="E35" t="s">
+        <v>402</v>
+      </c>
+      <c r="F35" t="s">
+        <v>403</v>
+      </c>
+      <c r="G35" t="s">
+        <v>349</v>
+      </c>
+      <c r="H35" t="s">
+        <v>404</v>
+      </c>
+      <c r="I35" t="s">
+        <v>405</v>
+      </c>
+      <c r="K35" t="s">
+        <v>332</v>
+      </c>
+      <c r="L35" t="s">
         <v>296</v>
       </c>
-      <c r="B35" t="s">
-        <v>148</v>
-      </c>
-      <c r="C35" t="s">
-        <v>425</v>
-      </c>
-      <c r="E35" t="s">
-        <v>453</v>
-      </c>
-      <c r="F35" t="s">
-        <v>454</v>
-      </c>
-      <c r="G35" t="s">
-        <v>399</v>
-      </c>
-      <c r="H35" t="s">
-        <v>455</v>
-      </c>
-      <c r="I35" t="s">
-        <v>456</v>
-      </c>
-      <c r="K35" t="s">
-        <v>381</v>
-      </c>
-      <c r="L35" t="s">
-        <v>345</v>
-      </c>
       <c r="M35" t="s">
-        <v>149</v>
+        <v>123</v>
       </c>
       <c r="O35">
         <v>565</v>
       </c>
       <c r="P35" t="s">
-        <v>327</v>
+        <v>278</v>
       </c>
       <c r="Q35" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="R35" t="s">
-        <v>346</v>
+        <v>297</v>
       </c>
       <c r="S35" t="s">
-        <v>424</v>
+        <v>373</v>
       </c>
       <c r="V35" t="s">
-        <v>150</v>
+        <v>548</v>
       </c>
       <c r="W35" t="s">
-        <v>13</v>
+        <v>517</v>
       </c>
       <c r="X35">
         <v>60</v>
@@ -4623,66 +4659,66 @@
         <v>46032</v>
       </c>
       <c r="Z35" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="36" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>297</v>
+        <v>248</v>
       </c>
       <c r="B36" t="s">
-        <v>151</v>
+        <v>124</v>
       </c>
       <c r="C36" t="s">
-        <v>425</v>
+        <v>374</v>
       </c>
       <c r="E36" t="s">
-        <v>457</v>
+        <v>406</v>
       </c>
       <c r="F36" t="s">
-        <v>385</v>
+        <v>336</v>
       </c>
       <c r="G36" t="s">
-        <v>399</v>
+        <v>349</v>
       </c>
       <c r="H36" t="s">
-        <v>496</v>
+        <v>445</v>
       </c>
       <c r="I36" t="s">
-        <v>359</v>
+        <v>310</v>
       </c>
       <c r="J36" t="s">
-        <v>360</v>
+        <v>311</v>
       </c>
       <c r="K36" t="s">
-        <v>468</v>
+        <v>417</v>
       </c>
       <c r="L36" t="s">
-        <v>345</v>
+        <v>296</v>
       </c>
       <c r="M36" t="s">
-        <v>153</v>
+        <v>126</v>
       </c>
       <c r="O36">
         <v>5400</v>
       </c>
       <c r="P36" t="s">
-        <v>152</v>
+        <v>125</v>
       </c>
       <c r="Q36" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="R36" t="s">
-        <v>346</v>
+        <v>297</v>
       </c>
       <c r="S36" t="s">
-        <v>424</v>
+        <v>373</v>
       </c>
       <c r="V36" t="s">
-        <v>154</v>
+        <v>127</v>
       </c>
       <c r="W36" t="s">
-        <v>13</v>
+        <v>517</v>
       </c>
       <c r="X36">
         <v>700</v>
@@ -4691,60 +4727,60 @@
         <v>46031</v>
       </c>
       <c r="Z36" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="37" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>298</v>
+        <v>249</v>
       </c>
       <c r="B37" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="C37" t="s">
-        <v>155</v>
+        <v>128</v>
       </c>
       <c r="E37" t="s">
-        <v>367</v>
+        <v>318</v>
       </c>
       <c r="F37" t="s">
-        <v>369</v>
+        <v>320</v>
       </c>
       <c r="G37" t="s">
-        <v>438</v>
+        <v>387</v>
       </c>
       <c r="H37" t="s">
-        <v>368</v>
+        <v>319</v>
       </c>
       <c r="K37" t="s">
-        <v>381</v>
+        <v>332</v>
       </c>
       <c r="L37" t="s">
-        <v>345</v>
+        <v>296</v>
       </c>
       <c r="M37" t="s">
-        <v>156</v>
+        <v>129</v>
       </c>
       <c r="O37">
         <v>2064</v>
       </c>
       <c r="P37" t="s">
-        <v>327</v>
+        <v>278</v>
       </c>
       <c r="Q37" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="R37" t="s">
-        <v>346</v>
+        <v>297</v>
       </c>
       <c r="S37" t="s">
-        <v>424</v>
+        <v>373</v>
       </c>
       <c r="V37" t="s">
-        <v>157</v>
+        <v>130</v>
       </c>
       <c r="W37" t="s">
-        <v>13</v>
+        <v>517</v>
       </c>
       <c r="X37">
         <v>100</v>
@@ -4753,57 +4789,57 @@
         <v>46033</v>
       </c>
       <c r="Z37" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="38" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>299</v>
+        <v>250</v>
       </c>
       <c r="B38" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="C38" t="s">
-        <v>155</v>
+        <v>128</v>
       </c>
       <c r="E38" t="s">
-        <v>367</v>
+        <v>318</v>
       </c>
       <c r="F38" t="s">
-        <v>369</v>
+        <v>320</v>
       </c>
       <c r="G38" t="s">
-        <v>438</v>
+        <v>387</v>
       </c>
       <c r="H38" t="s">
-        <v>368</v>
+        <v>319</v>
       </c>
       <c r="K38" t="s">
-        <v>381</v>
+        <v>332</v>
       </c>
       <c r="L38" t="s">
-        <v>345</v>
+        <v>296</v>
       </c>
       <c r="M38" t="s">
-        <v>158</v>
+        <v>131</v>
       </c>
       <c r="O38">
         <v>109</v>
       </c>
       <c r="P38" t="s">
-        <v>327</v>
+        <v>278</v>
       </c>
       <c r="Q38" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="R38" t="s">
-        <v>346</v>
+        <v>297</v>
       </c>
       <c r="S38" t="s">
-        <v>424</v>
+        <v>373</v>
       </c>
       <c r="V38" t="s">
-        <v>159</v>
+        <v>132</v>
       </c>
       <c r="X38">
         <v>15</v>
@@ -4812,57 +4848,57 @@
         <v>46033</v>
       </c>
       <c r="Z38" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="39" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>300</v>
+        <v>251</v>
       </c>
       <c r="B39" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="C39" t="s">
-        <v>155</v>
+        <v>128</v>
       </c>
       <c r="E39" t="s">
-        <v>367</v>
+        <v>318</v>
       </c>
       <c r="F39" t="s">
-        <v>369</v>
+        <v>320</v>
       </c>
       <c r="G39" t="s">
-        <v>438</v>
+        <v>387</v>
       </c>
       <c r="H39" t="s">
-        <v>368</v>
+        <v>319</v>
       </c>
       <c r="K39" t="s">
-        <v>381</v>
+        <v>332</v>
       </c>
       <c r="L39" t="s">
-        <v>345</v>
+        <v>296</v>
       </c>
       <c r="M39" t="s">
-        <v>160</v>
+        <v>133</v>
       </c>
       <c r="O39">
         <v>300</v>
       </c>
       <c r="P39" t="s">
-        <v>327</v>
+        <v>278</v>
       </c>
       <c r="Q39" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="R39" t="s">
-        <v>346</v>
+        <v>297</v>
       </c>
       <c r="S39" t="s">
-        <v>424</v>
+        <v>373</v>
       </c>
       <c r="V39" t="s">
-        <v>161</v>
+        <v>549</v>
       </c>
       <c r="X39">
         <v>25</v>
@@ -4871,57 +4907,57 @@
         <v>46033</v>
       </c>
       <c r="Z39" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="40" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>301</v>
+        <v>252</v>
       </c>
       <c r="B40" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="C40" t="s">
-        <v>155</v>
+        <v>128</v>
       </c>
       <c r="E40" t="s">
-        <v>367</v>
+        <v>318</v>
       </c>
       <c r="F40" t="s">
-        <v>369</v>
+        <v>320</v>
       </c>
       <c r="G40" t="s">
-        <v>438</v>
+        <v>387</v>
       </c>
       <c r="H40" t="s">
-        <v>368</v>
+        <v>319</v>
       </c>
       <c r="K40" t="s">
-        <v>381</v>
+        <v>332</v>
       </c>
       <c r="L40" t="s">
-        <v>345</v>
+        <v>296</v>
       </c>
       <c r="M40" t="s">
-        <v>162</v>
+        <v>134</v>
       </c>
       <c r="O40">
         <v>115</v>
       </c>
       <c r="P40" t="s">
-        <v>327</v>
+        <v>278</v>
       </c>
       <c r="Q40" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="R40" t="s">
-        <v>346</v>
+        <v>297</v>
       </c>
       <c r="S40" t="s">
-        <v>424</v>
+        <v>373</v>
       </c>
       <c r="V40" t="s">
-        <v>163</v>
+        <v>550</v>
       </c>
       <c r="X40">
         <v>15</v>
@@ -4930,125 +4966,125 @@
         <v>46033</v>
       </c>
       <c r="Z40" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="41" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>302</v>
+        <v>253</v>
       </c>
       <c r="B41" t="s">
-        <v>164</v>
+        <v>135</v>
       </c>
       <c r="C41" t="s">
-        <v>425</v>
+        <v>374</v>
       </c>
       <c r="E41" t="s">
-        <v>458</v>
+        <v>407</v>
       </c>
       <c r="F41" t="s">
-        <v>385</v>
+        <v>336</v>
       </c>
       <c r="G41" t="s">
-        <v>399</v>
+        <v>349</v>
       </c>
       <c r="H41" t="s">
-        <v>459</v>
+        <v>408</v>
       </c>
       <c r="I41" t="s">
-        <v>460</v>
+        <v>409</v>
       </c>
       <c r="K41" t="s">
-        <v>381</v>
+        <v>332</v>
       </c>
       <c r="L41" t="s">
-        <v>345</v>
+        <v>296</v>
       </c>
       <c r="M41" t="s">
-        <v>165</v>
+        <v>136</v>
       </c>
       <c r="O41">
         <v>819</v>
       </c>
       <c r="P41" t="s">
-        <v>327</v>
+        <v>278</v>
       </c>
       <c r="Q41" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="R41" t="s">
-        <v>346</v>
+        <v>297</v>
       </c>
       <c r="S41" t="s">
-        <v>424</v>
+        <v>373</v>
       </c>
       <c r="V41" t="s">
-        <v>166</v>
+        <v>551</v>
       </c>
       <c r="W41" t="s">
-        <v>13</v>
+        <v>523</v>
       </c>
       <c r="X41">
-        <v>60</v>
+        <v>175</v>
       </c>
       <c r="Y41" s="1">
         <v>46033</v>
       </c>
       <c r="Z41" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="42" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>303</v>
+        <v>254</v>
       </c>
       <c r="B42" t="s">
-        <v>167</v>
+        <v>137</v>
       </c>
       <c r="C42" t="s">
-        <v>425</v>
+        <v>374</v>
       </c>
       <c r="E42" t="s">
-        <v>461</v>
+        <v>410</v>
       </c>
       <c r="F42" t="s">
-        <v>385</v>
+        <v>336</v>
       </c>
       <c r="G42" t="s">
-        <v>438</v>
+        <v>387</v>
       </c>
       <c r="H42" t="s">
-        <v>462</v>
+        <v>411</v>
       </c>
       <c r="I42" t="s">
-        <v>463</v>
+        <v>412</v>
       </c>
       <c r="J42" t="s">
-        <v>348</v>
+        <v>299</v>
       </c>
       <c r="K42" t="s">
-        <v>381</v>
+        <v>332</v>
       </c>
       <c r="L42" t="s">
-        <v>345</v>
+        <v>296</v>
       </c>
       <c r="M42" t="s">
-        <v>169</v>
+        <v>139</v>
       </c>
       <c r="O42">
         <v>700</v>
       </c>
       <c r="P42" t="s">
-        <v>168</v>
+        <v>138</v>
       </c>
       <c r="Q42" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="R42" t="s">
-        <v>346</v>
+        <v>297</v>
       </c>
       <c r="S42" t="s">
-        <v>424</v>
+        <v>373</v>
       </c>
       <c r="T42" s="1">
         <v>45199</v>
@@ -5057,10 +5093,10 @@
         <v>50</v>
       </c>
       <c r="V42" t="s">
-        <v>170</v>
+        <v>552</v>
       </c>
       <c r="W42" t="s">
-        <v>171</v>
+        <v>140</v>
       </c>
       <c r="X42">
         <v>150</v>
@@ -5069,57 +5105,57 @@
         <v>46033</v>
       </c>
       <c r="Z42" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="43" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>304</v>
+        <v>255</v>
       </c>
       <c r="B43" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="C43" t="s">
-        <v>425</v>
+        <v>374</v>
       </c>
       <c r="E43" t="s">
-        <v>377</v>
+        <v>328</v>
       </c>
       <c r="F43" t="s">
-        <v>406</v>
+        <v>355</v>
       </c>
       <c r="G43" t="s">
-        <v>388</v>
+        <v>339</v>
       </c>
       <c r="H43" t="s">
-        <v>405</v>
+        <v>354</v>
       </c>
       <c r="I43" t="s">
-        <v>374</v>
+        <v>325</v>
       </c>
       <c r="K43" t="s">
-        <v>381</v>
+        <v>332</v>
       </c>
       <c r="L43" t="s">
-        <v>345</v>
+        <v>296</v>
       </c>
       <c r="M43" t="s">
-        <v>172</v>
+        <v>141</v>
       </c>
       <c r="O43">
         <v>450</v>
       </c>
       <c r="P43" t="s">
-        <v>536</v>
+        <v>483</v>
       </c>
       <c r="Q43" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="R43" t="s">
-        <v>346</v>
+        <v>297</v>
       </c>
       <c r="S43" t="s">
-        <v>424</v>
+        <v>373</v>
       </c>
       <c r="T43" s="1">
         <v>45199</v>
@@ -5128,10 +5164,10 @@
         <v>50</v>
       </c>
       <c r="V43" t="s">
-        <v>559</v>
+        <v>506</v>
       </c>
       <c r="W43" t="s">
-        <v>171</v>
+        <v>140</v>
       </c>
       <c r="X43">
         <v>120</v>
@@ -5140,63 +5176,63 @@
         <v>46031</v>
       </c>
       <c r="Z43" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="44" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="B44" t="s">
+        <v>24</v>
+      </c>
+      <c r="C44" t="s">
+        <v>374</v>
+      </c>
+      <c r="E44" t="s">
+        <v>345</v>
+      </c>
+      <c r="F44" t="s">
+        <v>301</v>
+      </c>
+      <c r="G44" t="s">
+        <v>346</v>
+      </c>
+      <c r="H44" t="s">
+        <v>347</v>
+      </c>
+      <c r="I44" t="s">
+        <v>348</v>
+      </c>
+      <c r="J44" t="s">
         <v>305</v>
       </c>
-      <c r="B44" t="s">
-        <v>31</v>
-      </c>
-      <c r="C44" t="s">
-        <v>425</v>
-      </c>
-      <c r="E44" t="s">
-        <v>394</v>
-      </c>
-      <c r="F44" t="s">
-        <v>350</v>
-      </c>
-      <c r="G44" t="s">
-        <v>395</v>
-      </c>
-      <c r="H44" t="s">
-        <v>396</v>
-      </c>
-      <c r="I44" t="s">
-        <v>397</v>
-      </c>
-      <c r="J44" t="s">
-        <v>354</v>
-      </c>
       <c r="K44" t="s">
-        <v>381</v>
+        <v>332</v>
       </c>
       <c r="L44" t="s">
-        <v>345</v>
+        <v>296</v>
       </c>
       <c r="M44" t="s">
-        <v>173</v>
+        <v>142</v>
       </c>
       <c r="N44" t="s">
-        <v>174</v>
+        <v>143</v>
       </c>
       <c r="O44">
         <v>1100</v>
       </c>
       <c r="P44" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="Q44" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="R44" t="s">
-        <v>346</v>
+        <v>297</v>
       </c>
       <c r="S44" t="s">
-        <v>424</v>
+        <v>373</v>
       </c>
       <c r="T44" s="1">
         <v>45199</v>
@@ -5205,10 +5241,10 @@
         <v>50</v>
       </c>
       <c r="V44" t="s">
-        <v>175</v>
+        <v>553</v>
       </c>
       <c r="W44" t="s">
-        <v>171</v>
+        <v>140</v>
       </c>
       <c r="X44">
         <v>200</v>
@@ -5217,60 +5253,60 @@
         <v>46031</v>
       </c>
       <c r="Z44" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="45" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>306</v>
+        <v>257</v>
       </c>
       <c r="B45" t="s">
-        <v>176</v>
+        <v>144</v>
       </c>
       <c r="C45" t="s">
-        <v>425</v>
+        <v>374</v>
       </c>
       <c r="D45" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="E45" t="s">
-        <v>464</v>
+        <v>413</v>
       </c>
       <c r="F45" t="s">
-        <v>406</v>
+        <v>355</v>
       </c>
       <c r="G45" t="s">
-        <v>388</v>
+        <v>339</v>
       </c>
       <c r="H45" t="s">
-        <v>465</v>
+        <v>414</v>
       </c>
       <c r="I45" t="s">
-        <v>466</v>
+        <v>415</v>
       </c>
       <c r="K45" t="s">
-        <v>381</v>
+        <v>332</v>
       </c>
       <c r="L45" t="s">
-        <v>345</v>
+        <v>296</v>
       </c>
       <c r="M45" t="s">
-        <v>178</v>
+        <v>146</v>
       </c>
       <c r="O45">
         <v>260</v>
       </c>
       <c r="P45" t="s">
-        <v>177</v>
+        <v>145</v>
       </c>
       <c r="Q45" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="R45" t="s">
-        <v>346</v>
+        <v>297</v>
       </c>
       <c r="S45" t="s">
-        <v>424</v>
+        <v>373</v>
       </c>
       <c r="T45" s="1">
         <v>45213</v>
@@ -5279,10 +5315,10 @@
         <v>40</v>
       </c>
       <c r="V45" t="s">
-        <v>179</v>
+        <v>554</v>
       </c>
       <c r="W45" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="X45">
         <v>50</v>
@@ -5291,60 +5327,60 @@
         <v>46033</v>
       </c>
       <c r="Z45" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="46" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>307</v>
+        <v>258</v>
       </c>
       <c r="B46" t="s">
+        <v>283</v>
+      </c>
+      <c r="C46" t="s">
+        <v>374</v>
+      </c>
+      <c r="E46" t="s">
+        <v>328</v>
+      </c>
+      <c r="F46" t="s">
+        <v>336</v>
+      </c>
+      <c r="G46" t="s">
+        <v>339</v>
+      </c>
+      <c r="H46" t="s">
+        <v>338</v>
+      </c>
+      <c r="I46" t="s">
+        <v>416</v>
+      </c>
+      <c r="J46" t="s">
+        <v>314</v>
+      </c>
+      <c r="K46" t="s">
         <v>332</v>
       </c>
-      <c r="C46" t="s">
-        <v>425</v>
-      </c>
-      <c r="E46" t="s">
-        <v>377</v>
-      </c>
-      <c r="F46" t="s">
-        <v>385</v>
-      </c>
-      <c r="G46" t="s">
-        <v>388</v>
-      </c>
-      <c r="H46" t="s">
-        <v>387</v>
-      </c>
-      <c r="I46" t="s">
-        <v>467</v>
-      </c>
-      <c r="J46" t="s">
-        <v>363</v>
-      </c>
-      <c r="K46" t="s">
-        <v>381</v>
-      </c>
       <c r="L46" t="s">
-        <v>345</v>
+        <v>296</v>
       </c>
       <c r="M46" t="s">
-        <v>183</v>
+        <v>150</v>
       </c>
       <c r="O46">
         <v>110</v>
       </c>
       <c r="P46" t="s">
-        <v>181</v>
+        <v>148</v>
       </c>
       <c r="Q46" t="s">
-        <v>182</v>
+        <v>149</v>
       </c>
       <c r="R46" t="s">
-        <v>346</v>
+        <v>297</v>
       </c>
       <c r="S46" t="s">
-        <v>424</v>
+        <v>373</v>
       </c>
       <c r="T46" s="1">
         <v>45215</v>
@@ -5353,10 +5389,10 @@
         <v>65</v>
       </c>
       <c r="V46" t="s">
-        <v>184</v>
+        <v>555</v>
       </c>
       <c r="W46" t="s">
-        <v>185</v>
+        <v>151</v>
       </c>
       <c r="X46">
         <v>95</v>
@@ -5365,54 +5401,54 @@
         <v>46033</v>
       </c>
       <c r="Z46" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="47" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>308</v>
+        <v>259</v>
       </c>
       <c r="B47" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="C47" t="s">
-        <v>126</v>
+        <v>103</v>
       </c>
       <c r="E47" t="s">
-        <v>420</v>
+        <v>369</v>
       </c>
       <c r="F47" t="s">
-        <v>406</v>
+        <v>355</v>
       </c>
       <c r="G47" t="s">
-        <v>392</v>
+        <v>343</v>
       </c>
       <c r="H47" t="s">
-        <v>482</v>
+        <v>431</v>
       </c>
       <c r="K47" t="s">
-        <v>468</v>
+        <v>417</v>
       </c>
       <c r="L47" t="s">
-        <v>345</v>
+        <v>296</v>
       </c>
       <c r="M47" t="s">
-        <v>188</v>
+        <v>154</v>
       </c>
       <c r="O47">
         <v>100</v>
       </c>
       <c r="P47" t="s">
-        <v>186</v>
+        <v>152</v>
       </c>
       <c r="Q47" t="s">
-        <v>187</v>
+        <v>153</v>
       </c>
       <c r="R47" t="s">
-        <v>346</v>
+        <v>297</v>
       </c>
       <c r="S47" t="s">
-        <v>424</v>
+        <v>373</v>
       </c>
       <c r="T47" s="1">
         <v>45233</v>
@@ -5421,10 +5457,10 @@
         <v>60</v>
       </c>
       <c r="V47" t="s">
-        <v>189</v>
+        <v>155</v>
       </c>
       <c r="W47" t="s">
-        <v>190</v>
+        <v>156</v>
       </c>
       <c r="X47">
         <v>85</v>
@@ -5433,51 +5469,51 @@
         <v>46033</v>
       </c>
       <c r="Z47" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="48" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>309</v>
+        <v>260</v>
       </c>
       <c r="B48" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="C48" t="s">
-        <v>425</v>
+        <v>374</v>
       </c>
       <c r="E48" t="s">
-        <v>495</v>
+        <v>444</v>
       </c>
       <c r="F48" t="s">
-        <v>369</v>
+        <v>320</v>
       </c>
       <c r="G48" t="s">
-        <v>399</v>
+        <v>349</v>
       </c>
       <c r="H48" t="s">
-        <v>402</v>
+        <v>351</v>
       </c>
       <c r="L48" t="s">
-        <v>345</v>
+        <v>296</v>
       </c>
       <c r="M48" t="s">
-        <v>192</v>
+        <v>158</v>
       </c>
       <c r="O48">
         <v>123</v>
       </c>
       <c r="P48" t="s">
-        <v>191</v>
+        <v>157</v>
       </c>
       <c r="Q48" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="R48" t="s">
-        <v>346</v>
+        <v>297</v>
       </c>
       <c r="S48" t="s">
-        <v>424</v>
+        <v>373</v>
       </c>
       <c r="T48" s="1">
         <v>45233</v>
@@ -5486,10 +5522,10 @@
         <v>20</v>
       </c>
       <c r="V48" t="s">
-        <v>193</v>
+        <v>159</v>
       </c>
       <c r="W48" t="s">
-        <v>190</v>
+        <v>156</v>
       </c>
       <c r="X48">
         <v>30</v>
@@ -5498,60 +5534,63 @@
         <v>46033</v>
       </c>
       <c r="Z48" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="49" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>310</v>
+        <v>261</v>
       </c>
       <c r="B49" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="C49" t="s">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="E49" t="s">
-        <v>420</v>
+        <v>369</v>
       </c>
       <c r="F49" t="s">
-        <v>406</v>
+        <v>355</v>
       </c>
       <c r="G49" t="s">
-        <v>392</v>
+        <v>343</v>
       </c>
       <c r="H49" t="s">
-        <v>470</v>
+        <v>419</v>
       </c>
       <c r="I49" t="s">
-        <v>469</v>
+        <v>418</v>
       </c>
       <c r="J49" t="s">
-        <v>348</v>
+        <v>299</v>
       </c>
       <c r="K49" t="s">
-        <v>381</v>
+        <v>332</v>
       </c>
       <c r="L49" t="s">
-        <v>345</v>
+        <v>296</v>
       </c>
       <c r="M49" t="s">
-        <v>195</v>
+        <v>161</v>
       </c>
       <c r="N49" t="s">
-        <v>196</v>
+        <v>162</v>
       </c>
       <c r="O49">
         <v>155</v>
       </c>
       <c r="P49" t="s">
-        <v>194</v>
+        <v>160</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>37</v>
       </c>
       <c r="R49" t="s">
-        <v>346</v>
+        <v>297</v>
       </c>
       <c r="S49" t="s">
-        <v>424</v>
+        <v>373</v>
       </c>
       <c r="T49" s="1">
         <v>45236</v>
@@ -5560,10 +5599,10 @@
         <v>55</v>
       </c>
       <c r="V49" t="s">
-        <v>197</v>
+        <v>163</v>
       </c>
       <c r="W49" t="s">
-        <v>190</v>
+        <v>156</v>
       </c>
       <c r="X49">
         <v>65</v>
@@ -5572,57 +5611,57 @@
         <v>46033</v>
       </c>
       <c r="Z49" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="50" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>311</v>
+        <v>262</v>
       </c>
       <c r="B50" t="s">
-        <v>118</v>
+        <v>95</v>
       </c>
       <c r="C50" t="s">
-        <v>123</v>
+        <v>100</v>
       </c>
       <c r="E50" t="s">
-        <v>440</v>
+        <v>389</v>
       </c>
       <c r="F50" t="s">
-        <v>350</v>
+        <v>301</v>
       </c>
       <c r="G50" t="s">
-        <v>441</v>
+        <v>390</v>
       </c>
       <c r="H50" t="s">
-        <v>471</v>
+        <v>420</v>
       </c>
       <c r="I50" t="s">
-        <v>472</v>
+        <v>421</v>
       </c>
       <c r="J50" t="s">
-        <v>348</v>
+        <v>299</v>
       </c>
       <c r="L50" t="s">
-        <v>343</v>
+        <v>294</v>
       </c>
       <c r="M50" t="s">
-        <v>199</v>
+        <v>165</v>
       </c>
       <c r="O50">
         <v>790</v>
       </c>
       <c r="P50" t="s">
-        <v>198</v>
+        <v>164</v>
       </c>
       <c r="Q50" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="R50" t="s">
-        <v>346</v>
+        <v>297</v>
       </c>
       <c r="S50" t="s">
-        <v>424</v>
+        <v>373</v>
       </c>
       <c r="T50" s="1">
         <v>45247</v>
@@ -5631,10 +5670,10 @@
         <v>50</v>
       </c>
       <c r="V50" t="s">
-        <v>200</v>
+        <v>556</v>
       </c>
       <c r="W50" t="s">
-        <v>185</v>
+        <v>151</v>
       </c>
       <c r="X50">
         <v>140</v>
@@ -5643,63 +5682,63 @@
         <v>46033</v>
       </c>
       <c r="Z50" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="51" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>312</v>
+        <v>263</v>
       </c>
       <c r="B51" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="C51" t="s">
-        <v>425</v>
+        <v>374</v>
       </c>
       <c r="E51" t="s">
-        <v>377</v>
+        <v>328</v>
       </c>
       <c r="F51" t="s">
-        <v>406</v>
+        <v>355</v>
       </c>
       <c r="G51" t="s">
-        <v>388</v>
+        <v>339</v>
       </c>
       <c r="H51" t="s">
-        <v>405</v>
+        <v>354</v>
       </c>
       <c r="I51" t="s">
-        <v>473</v>
+        <v>422</v>
       </c>
       <c r="J51" t="s">
-        <v>348</v>
+        <v>299</v>
       </c>
       <c r="L51" t="s">
-        <v>345</v>
+        <v>296</v>
       </c>
       <c r="M51" t="s">
-        <v>202</v>
+        <v>167</v>
       </c>
       <c r="O51">
         <v>3900</v>
       </c>
       <c r="P51" t="s">
-        <v>327</v>
+        <v>278</v>
       </c>
       <c r="Q51" t="s">
-        <v>201</v>
+        <v>166</v>
       </c>
       <c r="R51" t="s">
-        <v>346</v>
+        <v>297</v>
       </c>
       <c r="S51" t="s">
-        <v>424</v>
+        <v>373</v>
       </c>
       <c r="V51" t="s">
-        <v>203</v>
+        <v>557</v>
       </c>
       <c r="W51" t="s">
-        <v>204</v>
+        <v>168</v>
       </c>
       <c r="X51">
         <v>85</v>
@@ -5708,66 +5747,66 @@
         <v>46033</v>
       </c>
       <c r="Z51" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="52" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>313</v>
+        <v>264</v>
       </c>
       <c r="B52" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="C52" t="s">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="E52" t="s">
-        <v>420</v>
+        <v>369</v>
       </c>
       <c r="F52" t="s">
-        <v>406</v>
+        <v>355</v>
       </c>
       <c r="G52" t="s">
-        <v>392</v>
+        <v>343</v>
       </c>
       <c r="H52" t="s">
-        <v>474</v>
+        <v>423</v>
       </c>
       <c r="I52" t="s">
-        <v>475</v>
+        <v>424</v>
       </c>
       <c r="J52" t="s">
-        <v>476</v>
+        <v>425</v>
       </c>
       <c r="K52" t="s">
-        <v>381</v>
+        <v>332</v>
       </c>
       <c r="L52" t="s">
-        <v>345</v>
+        <v>296</v>
       </c>
       <c r="M52" t="s">
-        <v>206</v>
+        <v>170</v>
       </c>
       <c r="O52">
         <v>1850</v>
       </c>
       <c r="P52" t="s">
-        <v>327</v>
+        <v>278</v>
       </c>
       <c r="Q52" t="s">
-        <v>201</v>
+        <v>166</v>
       </c>
       <c r="R52" t="s">
-        <v>346</v>
+        <v>297</v>
       </c>
       <c r="S52" t="s">
-        <v>424</v>
+        <v>373</v>
       </c>
       <c r="V52" t="s">
-        <v>207</v>
+        <v>558</v>
       </c>
       <c r="W52" t="s">
-        <v>208</v>
+        <v>171</v>
       </c>
       <c r="X52">
         <v>130</v>
@@ -5776,63 +5815,63 @@
         <v>46033</v>
       </c>
       <c r="Z52" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="53" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>314</v>
+        <v>265</v>
       </c>
       <c r="B53" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="C53" t="s">
-        <v>425</v>
+        <v>374</v>
       </c>
       <c r="E53" t="s">
-        <v>377</v>
+        <v>328</v>
       </c>
       <c r="F53" t="s">
-        <v>406</v>
+        <v>355</v>
       </c>
       <c r="G53" t="s">
-        <v>388</v>
+        <v>339</v>
       </c>
       <c r="H53" t="s">
-        <v>405</v>
+        <v>354</v>
       </c>
       <c r="I53" t="s">
-        <v>477</v>
+        <v>426</v>
       </c>
       <c r="J53" t="s">
-        <v>348</v>
+        <v>299</v>
       </c>
       <c r="L53" t="s">
-        <v>345</v>
+        <v>296</v>
       </c>
       <c r="M53" t="s">
-        <v>209</v>
+        <v>172</v>
       </c>
       <c r="O53">
         <v>350</v>
       </c>
       <c r="P53" t="s">
-        <v>327</v>
+        <v>278</v>
       </c>
       <c r="Q53" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="R53" t="s">
-        <v>346</v>
+        <v>297</v>
       </c>
       <c r="S53" t="s">
-        <v>424</v>
+        <v>373</v>
       </c>
       <c r="V53" t="s">
-        <v>210</v>
+        <v>559</v>
       </c>
       <c r="W53" t="s">
-        <v>211</v>
+        <v>173</v>
       </c>
       <c r="X53">
         <v>35</v>
@@ -5841,63 +5880,63 @@
         <v>46033</v>
       </c>
       <c r="Z53" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="54" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>315</v>
+        <v>266</v>
       </c>
       <c r="B54" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="C54" t="s">
-        <v>131</v>
+        <v>108</v>
       </c>
       <c r="E54" t="s">
-        <v>420</v>
+        <v>369</v>
       </c>
       <c r="F54" t="s">
-        <v>406</v>
+        <v>355</v>
       </c>
       <c r="G54" t="s">
-        <v>392</v>
+        <v>343</v>
       </c>
       <c r="H54" t="s">
-        <v>497</v>
+        <v>446</v>
       </c>
       <c r="I54" t="s">
-        <v>478</v>
+        <v>427</v>
       </c>
       <c r="J54" t="s">
-        <v>348</v>
+        <v>299</v>
       </c>
       <c r="L54" t="s">
-        <v>345</v>
+        <v>296</v>
       </c>
       <c r="M54" t="s">
-        <v>212</v>
+        <v>174</v>
       </c>
       <c r="O54">
         <v>269</v>
       </c>
       <c r="P54" t="s">
-        <v>327</v>
+        <v>278</v>
       </c>
       <c r="Q54" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="R54" t="s">
-        <v>346</v>
+        <v>297</v>
       </c>
       <c r="S54" t="s">
-        <v>424</v>
+        <v>373</v>
       </c>
       <c r="V54" t="s">
-        <v>213</v>
+        <v>560</v>
       </c>
       <c r="W54" t="s">
-        <v>214</v>
+        <v>175</v>
       </c>
       <c r="X54">
         <v>20</v>
@@ -5906,63 +5945,63 @@
         <v>46033</v>
       </c>
       <c r="Z54" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="55" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>316</v>
+        <v>267</v>
       </c>
       <c r="B55" t="s">
-        <v>215</v>
+        <v>176</v>
       </c>
       <c r="C55" t="s">
-        <v>216</v>
+        <v>177</v>
       </c>
       <c r="D55" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="E55" t="s">
-        <v>479</v>
+        <v>428</v>
       </c>
       <c r="F55" t="s">
-        <v>391</v>
+        <v>342</v>
       </c>
       <c r="G55" t="s">
-        <v>399</v>
+        <v>349</v>
       </c>
       <c r="H55" t="s">
-        <v>480</v>
+        <v>429</v>
       </c>
       <c r="I55" t="s">
-        <v>362</v>
+        <v>313</v>
       </c>
       <c r="J55" t="s">
-        <v>363</v>
+        <v>314</v>
       </c>
       <c r="L55" t="s">
-        <v>345</v>
+        <v>296</v>
       </c>
       <c r="M55" t="s">
-        <v>217</v>
+        <v>178</v>
       </c>
       <c r="N55" t="s">
-        <v>218</v>
+        <v>179</v>
       </c>
       <c r="O55">
         <v>200</v>
       </c>
       <c r="P55" t="s">
-        <v>152</v>
+        <v>125</v>
       </c>
       <c r="Q55" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="R55" t="s">
-        <v>346</v>
+        <v>297</v>
       </c>
       <c r="S55" t="s">
-        <v>424</v>
+        <v>373</v>
       </c>
       <c r="T55" s="1">
         <v>45267</v>
@@ -5971,10 +6010,10 @@
         <v>40</v>
       </c>
       <c r="V55" t="s">
-        <v>535</v>
+        <v>561</v>
       </c>
       <c r="W55" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="X55">
         <v>120</v>
@@ -5983,60 +6022,60 @@
         <v>46031</v>
       </c>
       <c r="Z55" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="56" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>317</v>
+        <v>268</v>
       </c>
       <c r="B56" t="s">
-        <v>219</v>
+        <v>180</v>
       </c>
       <c r="C56" t="s">
-        <v>425</v>
+        <v>374</v>
       </c>
       <c r="E56" t="s">
-        <v>491</v>
+        <v>440</v>
       </c>
       <c r="F56" t="s">
-        <v>385</v>
+        <v>336</v>
       </c>
       <c r="G56" t="s">
-        <v>392</v>
+        <v>343</v>
       </c>
       <c r="H56" t="s">
-        <v>481</v>
+        <v>430</v>
       </c>
       <c r="I56" t="s">
-        <v>437</v>
+        <v>386</v>
       </c>
       <c r="J56" t="s">
-        <v>354</v>
+        <v>305</v>
       </c>
       <c r="K56" t="s">
-        <v>381</v>
+        <v>332</v>
       </c>
       <c r="L56" t="s">
-        <v>345</v>
+        <v>296</v>
       </c>
       <c r="M56" t="s">
-        <v>220</v>
+        <v>181</v>
       </c>
       <c r="O56">
         <v>375</v>
       </c>
       <c r="P56" t="s">
-        <v>532</v>
+        <v>480</v>
       </c>
       <c r="Q56" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="R56" t="s">
-        <v>346</v>
+        <v>297</v>
       </c>
       <c r="S56" t="s">
-        <v>424</v>
+        <v>373</v>
       </c>
       <c r="T56" s="1">
         <v>45267</v>
@@ -6045,10 +6084,10 @@
         <v>25</v>
       </c>
       <c r="V56" t="s">
-        <v>221</v>
+        <v>562</v>
       </c>
       <c r="W56" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="X56">
         <v>65</v>
@@ -6057,57 +6096,57 @@
         <v>46033</v>
       </c>
       <c r="Z56" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="57" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>318</v>
+        <v>269</v>
       </c>
       <c r="B57" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="C57" t="s">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="E57" t="s">
-        <v>420</v>
+        <v>369</v>
       </c>
       <c r="F57" t="s">
-        <v>406</v>
+        <v>355</v>
       </c>
       <c r="G57" t="s">
-        <v>392</v>
+        <v>343</v>
       </c>
       <c r="H57" t="s">
-        <v>482</v>
+        <v>431</v>
       </c>
       <c r="I57" t="s">
-        <v>119</v>
+        <v>96</v>
       </c>
       <c r="J57" t="s">
-        <v>348</v>
+        <v>299</v>
       </c>
       <c r="L57" t="s">
-        <v>345</v>
+        <v>296</v>
       </c>
       <c r="M57" t="s">
-        <v>222</v>
+        <v>182</v>
       </c>
       <c r="O57">
         <v>510</v>
       </c>
       <c r="P57" t="s">
-        <v>327</v>
+        <v>278</v>
       </c>
       <c r="Q57" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="R57" t="s">
-        <v>346</v>
+        <v>297</v>
       </c>
       <c r="S57" t="s">
-        <v>424</v>
+        <v>373</v>
       </c>
       <c r="T57" s="1">
         <v>45267</v>
@@ -6116,10 +6155,10 @@
         <v>15</v>
       </c>
       <c r="V57" t="s">
-        <v>223</v>
+        <v>563</v>
       </c>
       <c r="W57" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="X57">
         <v>45</v>
@@ -6128,60 +6167,60 @@
         <v>46033</v>
       </c>
       <c r="Z57" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="58" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>319</v>
+        <v>270</v>
       </c>
       <c r="B58" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="C58" t="s">
-        <v>224</v>
+        <v>183</v>
       </c>
       <c r="E58" t="s">
-        <v>420</v>
+        <v>369</v>
       </c>
       <c r="F58" t="s">
-        <v>406</v>
+        <v>355</v>
       </c>
       <c r="G58" t="s">
-        <v>392</v>
+        <v>343</v>
       </c>
       <c r="H58" t="s">
-        <v>482</v>
+        <v>431</v>
       </c>
       <c r="I58" t="s">
-        <v>485</v>
+        <v>434</v>
       </c>
       <c r="J58" t="s">
-        <v>348</v>
+        <v>299</v>
       </c>
       <c r="K58" t="s">
-        <v>381</v>
+        <v>332</v>
       </c>
       <c r="L58" t="s">
-        <v>345</v>
+        <v>296</v>
       </c>
       <c r="M58" t="s">
-        <v>226</v>
+        <v>185</v>
       </c>
       <c r="O58">
         <v>215</v>
       </c>
       <c r="P58" t="s">
-        <v>225</v>
+        <v>184</v>
       </c>
       <c r="Q58" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="R58" t="s">
-        <v>346</v>
+        <v>297</v>
       </c>
       <c r="S58" t="s">
-        <v>424</v>
+        <v>373</v>
       </c>
       <c r="T58" s="1">
         <v>45269</v>
@@ -6190,10 +6229,10 @@
         <v>35</v>
       </c>
       <c r="V58" t="s">
-        <v>227</v>
+        <v>564</v>
       </c>
       <c r="W58" t="s">
-        <v>228</v>
+        <v>186</v>
       </c>
       <c r="X58">
         <v>60</v>
@@ -6202,63 +6241,63 @@
         <v>46033</v>
       </c>
       <c r="Z58" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="59" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="B59" t="s">
+        <v>478</v>
+      </c>
+      <c r="C59" t="s">
+        <v>374</v>
+      </c>
+      <c r="D59" t="s">
+        <v>44</v>
+      </c>
+      <c r="E59" t="s">
+        <v>435</v>
+      </c>
+      <c r="F59" t="s">
         <v>320</v>
       </c>
-      <c r="B59" t="s">
-        <v>530</v>
-      </c>
-      <c r="C59" t="s">
-        <v>425</v>
-      </c>
-      <c r="D59" t="s">
-        <v>56</v>
-      </c>
-      <c r="E59" t="s">
-        <v>486</v>
-      </c>
-      <c r="F59" t="s">
-        <v>369</v>
-      </c>
       <c r="G59" t="s">
-        <v>388</v>
+        <v>339</v>
       </c>
       <c r="H59" t="s">
-        <v>407</v>
+        <v>356</v>
       </c>
       <c r="I59" t="s">
-        <v>382</v>
+        <v>333</v>
       </c>
       <c r="J59" t="s">
-        <v>383</v>
+        <v>334</v>
       </c>
       <c r="K59" t="s">
-        <v>381</v>
+        <v>332</v>
       </c>
       <c r="L59" t="s">
-        <v>345</v>
+        <v>296</v>
       </c>
       <c r="M59" t="s">
-        <v>231</v>
+        <v>189</v>
       </c>
       <c r="O59">
         <v>92</v>
       </c>
       <c r="P59" t="s">
-        <v>229</v>
+        <v>187</v>
       </c>
       <c r="Q59" t="s">
-        <v>230</v>
+        <v>188</v>
       </c>
       <c r="R59" t="s">
-        <v>346</v>
+        <v>297</v>
       </c>
       <c r="S59" t="s">
-        <v>424</v>
+        <v>373</v>
       </c>
       <c r="T59" s="1">
         <v>45571</v>
@@ -6267,10 +6306,10 @@
         <v>60</v>
       </c>
       <c r="V59" t="s">
-        <v>531</v>
+        <v>479</v>
       </c>
       <c r="W59" t="s">
-        <v>232</v>
+        <v>190</v>
       </c>
       <c r="X59">
         <v>70</v>
@@ -6279,57 +6318,57 @@
         <v>46032</v>
       </c>
       <c r="Z59" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="60" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>321</v>
+        <v>272</v>
       </c>
       <c r="B60" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="C60" t="s">
-        <v>425</v>
+        <v>374</v>
       </c>
       <c r="D60" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="E60" t="s">
-        <v>493</v>
+        <v>442</v>
       </c>
       <c r="F60" t="s">
-        <v>385</v>
+        <v>336</v>
       </c>
       <c r="G60" t="s">
-        <v>399</v>
+        <v>349</v>
       </c>
       <c r="H60" t="s">
-        <v>487</v>
+        <v>436</v>
       </c>
       <c r="I60" t="s">
-        <v>373</v>
+        <v>324</v>
       </c>
       <c r="L60" t="s">
-        <v>345</v>
+        <v>296</v>
       </c>
       <c r="M60" t="s">
-        <v>235</v>
+        <v>193</v>
       </c>
       <c r="O60">
         <v>250</v>
       </c>
       <c r="P60" t="s">
-        <v>234</v>
+        <v>192</v>
       </c>
       <c r="Q60" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="R60" t="s">
-        <v>346</v>
+        <v>297</v>
       </c>
       <c r="S60" t="s">
-        <v>424</v>
+        <v>373</v>
       </c>
       <c r="T60" s="1">
         <v>45591</v>
@@ -6338,10 +6377,10 @@
         <v>35</v>
       </c>
       <c r="V60" t="s">
-        <v>236</v>
+        <v>565</v>
       </c>
       <c r="W60" t="s">
-        <v>237</v>
+        <v>194</v>
       </c>
       <c r="X60">
         <v>90</v>
@@ -6350,60 +6389,60 @@
         <v>46031</v>
       </c>
       <c r="Z60" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="61" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>322</v>
+        <v>273</v>
       </c>
       <c r="B61" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="C61" t="s">
-        <v>425</v>
+        <v>374</v>
       </c>
       <c r="E61" t="s">
-        <v>377</v>
+        <v>328</v>
       </c>
       <c r="F61" t="s">
-        <v>406</v>
+        <v>355</v>
       </c>
       <c r="G61" t="s">
-        <v>388</v>
+        <v>339</v>
       </c>
       <c r="H61" t="s">
-        <v>405</v>
+        <v>354</v>
       </c>
       <c r="I61" t="s">
-        <v>365</v>
+        <v>316</v>
       </c>
       <c r="J61" t="s">
-        <v>366</v>
+        <v>317</v>
       </c>
       <c r="L61" t="s">
-        <v>345</v>
+        <v>296</v>
       </c>
       <c r="M61" t="s">
-        <v>238</v>
+        <v>195</v>
       </c>
       <c r="N61" t="s">
-        <v>239</v>
+        <v>196</v>
       </c>
       <c r="O61">
         <v>200</v>
       </c>
       <c r="P61" t="s">
-        <v>534</v>
+        <v>482</v>
       </c>
       <c r="Q61" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="R61" t="s">
-        <v>346</v>
+        <v>297</v>
       </c>
       <c r="S61" t="s">
-        <v>424</v>
+        <v>373</v>
       </c>
       <c r="T61" s="1">
         <v>45635</v>
@@ -6412,10 +6451,10 @@
         <v>36</v>
       </c>
       <c r="V61" t="s">
-        <v>240</v>
+        <v>566</v>
       </c>
       <c r="W61" t="s">
-        <v>241</v>
+        <v>197</v>
       </c>
       <c r="X61">
         <v>100</v>
@@ -6424,57 +6463,57 @@
         <v>46031</v>
       </c>
       <c r="Z61" t="s">
-        <v>242</v>
+        <v>198</v>
       </c>
     </row>
     <row r="62" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>323</v>
+        <v>274</v>
       </c>
       <c r="B62" t="s">
-        <v>243</v>
+        <v>199</v>
       </c>
       <c r="C62" t="s">
-        <v>425</v>
+        <v>374</v>
       </c>
       <c r="D62" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="E62" t="s">
-        <v>428</v>
+        <v>377</v>
       </c>
       <c r="F62" t="s">
-        <v>454</v>
+        <v>403</v>
       </c>
       <c r="G62" t="s">
-        <v>399</v>
+        <v>349</v>
       </c>
       <c r="H62" t="s">
-        <v>488</v>
+        <v>437</v>
       </c>
       <c r="I62" t="s">
-        <v>180</v>
+        <v>147</v>
       </c>
       <c r="L62" t="s">
-        <v>345</v>
+        <v>296</v>
       </c>
       <c r="M62" t="s">
-        <v>245</v>
+        <v>201</v>
       </c>
       <c r="O62">
         <v>370</v>
       </c>
       <c r="P62" t="s">
-        <v>244</v>
+        <v>200</v>
       </c>
       <c r="Q62" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="R62" t="s">
-        <v>346</v>
+        <v>297</v>
       </c>
       <c r="S62" t="s">
-        <v>424</v>
+        <v>373</v>
       </c>
       <c r="T62" s="1">
         <v>45646</v>
@@ -6483,10 +6522,10 @@
         <v>50</v>
       </c>
       <c r="V62" t="s">
-        <v>246</v>
+        <v>567</v>
       </c>
       <c r="W62" t="s">
-        <v>237</v>
+        <v>194</v>
       </c>
       <c r="X62">
         <v>110</v>
@@ -6495,63 +6534,66 @@
         <v>46031</v>
       </c>
       <c r="Z62" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="63" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>324</v>
+        <v>275</v>
       </c>
       <c r="B63" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="C63" t="s">
-        <v>247</v>
+        <v>202</v>
       </c>
       <c r="D63" t="s">
-        <v>248</v>
+        <v>203</v>
       </c>
       <c r="E63" t="s">
-        <v>420</v>
+        <v>369</v>
       </c>
       <c r="F63" t="s">
-        <v>406</v>
+        <v>355</v>
       </c>
       <c r="G63" t="s">
-        <v>392</v>
+        <v>343</v>
       </c>
       <c r="H63" t="s">
-        <v>482</v>
+        <v>431</v>
       </c>
       <c r="I63" t="s">
-        <v>247</v>
+        <v>202</v>
       </c>
       <c r="J63" t="s">
-        <v>348</v>
+        <v>299</v>
       </c>
       <c r="K63" t="s">
-        <v>468</v>
+        <v>417</v>
       </c>
       <c r="L63" t="s">
-        <v>345</v>
+        <v>296</v>
       </c>
       <c r="M63" t="s">
-        <v>250</v>
+        <v>204</v>
       </c>
       <c r="N63" t="s">
-        <v>251</v>
+        <v>205</v>
       </c>
       <c r="O63">
         <v>3500</v>
       </c>
       <c r="P63" t="s">
-        <v>249</v>
+        <v>527</v>
+      </c>
+      <c r="Q63" t="s">
+        <v>37</v>
       </c>
       <c r="R63" t="s">
-        <v>346</v>
+        <v>297</v>
       </c>
       <c r="S63" t="s">
-        <v>424</v>
+        <v>373</v>
       </c>
       <c r="T63" s="1">
         <v>45839</v>
@@ -6560,10 +6602,10 @@
         <v>160</v>
       </c>
       <c r="V63" t="s">
-        <v>252</v>
+        <v>526</v>
       </c>
       <c r="W63" t="s">
-        <v>253</v>
+        <v>206</v>
       </c>
       <c r="X63">
         <v>300</v>
@@ -6572,60 +6614,60 @@
         <v>45839</v>
       </c>
       <c r="Z63" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="64" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>325</v>
+        <v>276</v>
       </c>
       <c r="B64" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="C64" t="s">
-        <v>224</v>
+        <v>183</v>
       </c>
       <c r="E64" t="s">
-        <v>420</v>
+        <v>369</v>
       </c>
       <c r="F64" t="s">
-        <v>406</v>
+        <v>355</v>
       </c>
       <c r="G64" t="s">
-        <v>392</v>
+        <v>343</v>
       </c>
       <c r="H64" t="s">
-        <v>482</v>
+        <v>431</v>
       </c>
       <c r="I64" t="s">
-        <v>361</v>
+        <v>312</v>
       </c>
       <c r="J64" t="s">
-        <v>348</v>
+        <v>299</v>
       </c>
       <c r="L64" t="s">
-        <v>345</v>
+        <v>296</v>
       </c>
       <c r="M64" t="s">
-        <v>255</v>
+        <v>208</v>
       </c>
       <c r="N64" t="s">
-        <v>256</v>
+        <v>209</v>
       </c>
       <c r="O64">
         <v>225</v>
       </c>
       <c r="P64" t="s">
-        <v>254</v>
+        <v>207</v>
       </c>
       <c r="Q64" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="R64" t="s">
-        <v>346</v>
+        <v>297</v>
       </c>
       <c r="S64" t="s">
-        <v>424</v>
+        <v>373</v>
       </c>
       <c r="T64" s="1">
         <v>45996</v>
@@ -6634,10 +6676,10 @@
         <v>75</v>
       </c>
       <c r="V64" t="s">
-        <v>257</v>
+        <v>568</v>
       </c>
       <c r="W64" t="s">
-        <v>258</v>
+        <v>210</v>
       </c>
       <c r="X64">
         <v>120</v>
@@ -6646,63 +6688,63 @@
         <v>46031</v>
       </c>
       <c r="Z64" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="65" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>326</v>
+        <v>277</v>
       </c>
       <c r="B65" t="s">
-        <v>259</v>
+        <v>211</v>
       </c>
       <c r="C65" t="s">
-        <v>425</v>
+        <v>374</v>
       </c>
       <c r="D65" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="E65" t="s">
-        <v>429</v>
+        <v>378</v>
       </c>
       <c r="F65" t="s">
-        <v>350</v>
+        <v>301</v>
       </c>
       <c r="G65" t="s">
-        <v>395</v>
+        <v>346</v>
       </c>
       <c r="H65" t="s">
-        <v>489</v>
+        <v>438</v>
       </c>
       <c r="I65" t="s">
-        <v>353</v>
+        <v>304</v>
       </c>
       <c r="J65" t="s">
-        <v>354</v>
+        <v>305</v>
       </c>
       <c r="K65" t="s">
-        <v>381</v>
+        <v>332</v>
       </c>
       <c r="L65" t="s">
-        <v>345</v>
+        <v>296</v>
       </c>
       <c r="M65" t="s">
-        <v>261</v>
+        <v>213</v>
       </c>
       <c r="O65">
         <v>105</v>
       </c>
       <c r="P65" t="s">
-        <v>260</v>
+        <v>212</v>
       </c>
       <c r="Q65" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="R65" t="s">
-        <v>349</v>
+        <v>300</v>
       </c>
       <c r="S65" t="s">
-        <v>424</v>
+        <v>373</v>
       </c>
       <c r="T65" s="1">
         <v>46013</v>
@@ -6711,10 +6753,10 @@
         <v>30</v>
       </c>
       <c r="V65" t="s">
-        <v>262</v>
+        <v>569</v>
       </c>
       <c r="W65" t="s">
-        <v>510</v>
+        <v>458</v>
       </c>
       <c r="X65">
         <v>150</v>
@@ -6723,69 +6765,66 @@
         <v>46031</v>
       </c>
       <c r="Z65" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="66" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>501</v>
+        <v>449</v>
       </c>
       <c r="B66" t="s">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="C66" t="s">
-        <v>425</v>
+        <v>374</v>
       </c>
       <c r="E66" t="s">
-        <v>420</v>
+        <v>369</v>
       </c>
       <c r="F66" t="s">
-        <v>406</v>
+        <v>355</v>
       </c>
       <c r="G66" t="s">
-        <v>392</v>
+        <v>343</v>
       </c>
       <c r="H66" t="s">
-        <v>505</v>
+        <v>453</v>
       </c>
       <c r="I66" t="s">
-        <v>506</v>
+        <v>454</v>
       </c>
       <c r="K66" t="s">
-        <v>381</v>
+        <v>332</v>
       </c>
       <c r="L66" t="s">
-        <v>345</v>
+        <v>296</v>
       </c>
       <c r="M66" t="s">
-        <v>507</v>
+        <v>455</v>
       </c>
       <c r="O66">
         <v>86</v>
       </c>
       <c r="P66" t="s">
-        <v>508</v>
+        <v>456</v>
       </c>
       <c r="Q66" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="R66" t="s">
-        <v>346</v>
+        <v>297</v>
       </c>
       <c r="S66" t="s">
-        <v>424</v>
+        <v>373</v>
       </c>
       <c r="T66" s="6">
         <v>46041</v>
       </c>
-      <c r="U66">
-        <v>0</v>
-      </c>
       <c r="V66" t="s">
-        <v>509</v>
+        <v>457</v>
       </c>
       <c r="W66" t="s">
-        <v>510</v>
+        <v>458</v>
       </c>
       <c r="X66">
         <v>15</v>
@@ -6794,60 +6833,60 @@
         <v>46043</v>
       </c>
       <c r="Z66" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="67" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>502</v>
+        <v>450</v>
       </c>
       <c r="B67" t="s">
-        <v>167</v>
+        <v>137</v>
       </c>
       <c r="C67" t="s">
-        <v>425</v>
+        <v>374</v>
       </c>
       <c r="E67" t="s">
+        <v>410</v>
+      </c>
+      <c r="F67" t="s">
+        <v>336</v>
+      </c>
+      <c r="G67" t="s">
+        <v>387</v>
+      </c>
+      <c r="H67" t="s">
+        <v>411</v>
+      </c>
+      <c r="I67" t="s">
+        <v>459</v>
+      </c>
+      <c r="J67" t="s">
+        <v>460</v>
+      </c>
+      <c r="K67" t="s">
         <v>461</v>
       </c>
-      <c r="F67" t="s">
-        <v>385</v>
-      </c>
-      <c r="G67" t="s">
-        <v>438</v>
-      </c>
-      <c r="H67" t="s">
+      <c r="L67" t="s">
+        <v>296</v>
+      </c>
+      <c r="M67" t="s">
         <v>462</v>
-      </c>
-      <c r="I67" t="s">
-        <v>511</v>
-      </c>
-      <c r="J67" t="s">
-        <v>512</v>
-      </c>
-      <c r="K67" t="s">
-        <v>513</v>
-      </c>
-      <c r="L67" t="s">
-        <v>345</v>
-      </c>
-      <c r="M67" t="s">
-        <v>514</v>
       </c>
       <c r="O67">
         <v>28</v>
       </c>
       <c r="P67" t="s">
-        <v>527</v>
+        <v>475</v>
       </c>
       <c r="Q67" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="R67" t="s">
-        <v>349</v>
+        <v>300</v>
       </c>
       <c r="S67" t="s">
-        <v>424</v>
+        <v>373</v>
       </c>
       <c r="T67" s="6">
         <v>46041</v>
@@ -6856,10 +6895,10 @@
         <v>25</v>
       </c>
       <c r="V67" t="s">
-        <v>515</v>
+        <v>463</v>
       </c>
       <c r="W67" t="s">
-        <v>510</v>
+        <v>458</v>
       </c>
       <c r="X67">
         <v>60</v>
@@ -6868,60 +6907,60 @@
         <v>46043</v>
       </c>
       <c r="Z67" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="68" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>503</v>
+        <v>451</v>
       </c>
       <c r="B68" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="C68" t="s">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="E68" t="s">
-        <v>420</v>
+        <v>369</v>
       </c>
       <c r="F68" t="s">
-        <v>406</v>
+        <v>355</v>
       </c>
       <c r="G68" t="s">
-        <v>392</v>
+        <v>343</v>
       </c>
       <c r="H68" t="s">
-        <v>482</v>
+        <v>431</v>
       </c>
       <c r="I68" t="s">
-        <v>516</v>
+        <v>464</v>
       </c>
       <c r="J68" t="s">
-        <v>348</v>
+        <v>299</v>
       </c>
       <c r="K68" t="s">
-        <v>468</v>
+        <v>417</v>
       </c>
       <c r="L68" t="s">
-        <v>345</v>
+        <v>296</v>
       </c>
       <c r="M68" t="s">
-        <v>517</v>
+        <v>465</v>
       </c>
       <c r="O68">
         <v>92</v>
       </c>
       <c r="P68" t="s">
-        <v>518</v>
+        <v>466</v>
       </c>
       <c r="Q68" t="s">
         <v>10</v>
       </c>
       <c r="R68" t="s">
-        <v>349</v>
+        <v>300</v>
       </c>
       <c r="S68" t="s">
-        <v>424</v>
+        <v>373</v>
       </c>
       <c r="T68" s="6">
         <v>46041</v>
@@ -6930,10 +6969,10 @@
         <v>30</v>
       </c>
       <c r="V68" t="s">
-        <v>519</v>
+        <v>467</v>
       </c>
       <c r="W68" t="s">
-        <v>510</v>
+        <v>458</v>
       </c>
       <c r="X68">
         <v>85</v>
@@ -6942,60 +6981,60 @@
         <v>46043</v>
       </c>
       <c r="Z68" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="69" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>504</v>
+        <v>452</v>
       </c>
       <c r="B69" t="s">
-        <v>520</v>
+        <v>468</v>
       </c>
       <c r="C69" t="s">
-        <v>425</v>
+        <v>374</v>
       </c>
       <c r="E69" t="s">
-        <v>521</v>
+        <v>469</v>
       </c>
       <c r="F69" t="s">
-        <v>385</v>
+        <v>336</v>
       </c>
       <c r="G69" t="s">
-        <v>416</v>
+        <v>365</v>
       </c>
       <c r="H69" t="s">
-        <v>522</v>
+        <v>470</v>
       </c>
       <c r="I69" t="s">
-        <v>523</v>
+        <v>471</v>
       </c>
       <c r="J69" t="s">
-        <v>357</v>
+        <v>308</v>
       </c>
       <c r="K69" t="s">
-        <v>524</v>
+        <v>472</v>
       </c>
       <c r="L69" t="s">
-        <v>345</v>
+        <v>296</v>
       </c>
       <c r="M69" t="s">
-        <v>525</v>
+        <v>473</v>
       </c>
       <c r="O69">
         <v>160</v>
       </c>
       <c r="P69" t="s">
-        <v>526</v>
+        <v>474</v>
       </c>
       <c r="Q69" t="s">
-        <v>528</v>
+        <v>476</v>
       </c>
       <c r="R69" t="s">
-        <v>349</v>
+        <v>300</v>
       </c>
       <c r="S69" t="s">
-        <v>424</v>
+        <v>373</v>
       </c>
       <c r="T69" s="6">
         <v>46041</v>
@@ -7004,10 +7043,10 @@
         <v>60</v>
       </c>
       <c r="V69" t="s">
-        <v>529</v>
+        <v>477</v>
       </c>
       <c r="W69" t="s">
-        <v>510</v>
+        <v>458</v>
       </c>
       <c r="X69">
         <v>150</v>
@@ -7016,63 +7055,63 @@
         <v>46043</v>
       </c>
       <c r="Z69" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="70" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>540</v>
+        <v>487</v>
       </c>
       <c r="B70" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="C70" t="s">
-        <v>537</v>
+        <v>484</v>
       </c>
       <c r="D70" t="s">
-        <v>538</v>
+        <v>485</v>
       </c>
       <c r="E70" t="s">
-        <v>420</v>
+        <v>369</v>
       </c>
       <c r="F70" t="s">
-        <v>406</v>
+        <v>355</v>
       </c>
       <c r="G70" t="s">
-        <v>392</v>
+        <v>343</v>
       </c>
       <c r="H70" t="s">
-        <v>482</v>
+        <v>431</v>
       </c>
       <c r="I70" t="s">
-        <v>549</v>
+        <v>496</v>
       </c>
       <c r="J70" t="s">
-        <v>366</v>
+        <v>317</v>
       </c>
       <c r="K70" t="s">
-        <v>513</v>
+        <v>461</v>
       </c>
       <c r="L70" t="s">
-        <v>345</v>
+        <v>296</v>
       </c>
       <c r="M70" t="s">
-        <v>539</v>
+        <v>486</v>
       </c>
       <c r="O70">
         <v>97</v>
       </c>
       <c r="P70" t="s">
-        <v>186</v>
+        <v>152</v>
       </c>
       <c r="Q70" t="s">
-        <v>187</v>
+        <v>153</v>
       </c>
       <c r="R70" t="s">
-        <v>349</v>
+        <v>300</v>
       </c>
       <c r="S70" t="s">
-        <v>424</v>
+        <v>373</v>
       </c>
       <c r="T70" s="1">
         <v>46071</v>
@@ -7081,10 +7120,10 @@
         <v>155</v>
       </c>
       <c r="V70" t="s">
-        <v>558</v>
+        <v>505</v>
       </c>
       <c r="W70" t="s">
-        <v>510</v>
+        <v>458</v>
       </c>
       <c r="X70">
         <v>200</v>
@@ -7093,63 +7132,63 @@
         <v>46071</v>
       </c>
       <c r="Z70" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="71" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>541</v>
+        <v>488</v>
       </c>
       <c r="B71" t="s">
-        <v>118</v>
+        <v>95</v>
       </c>
       <c r="C71" t="s">
-        <v>123</v>
+        <v>100</v>
       </c>
       <c r="D71" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="E71" t="s">
-        <v>440</v>
+        <v>389</v>
       </c>
       <c r="F71" t="s">
-        <v>350</v>
+        <v>301</v>
       </c>
       <c r="G71" t="s">
-        <v>441</v>
+        <v>390</v>
       </c>
       <c r="H71" t="s">
-        <v>471</v>
+        <v>420</v>
       </c>
       <c r="I71" t="s">
-        <v>550</v>
+        <v>497</v>
       </c>
       <c r="J71" t="s">
-        <v>348</v>
+        <v>299</v>
       </c>
       <c r="K71" t="s">
-        <v>371</v>
+        <v>322</v>
       </c>
       <c r="L71" t="s">
-        <v>345</v>
+        <v>296</v>
       </c>
       <c r="M71" t="s">
-        <v>544</v>
+        <v>491</v>
       </c>
       <c r="O71">
         <v>318</v>
       </c>
       <c r="P71" t="s">
-        <v>543</v>
+        <v>490</v>
       </c>
       <c r="Q71" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="R71" t="s">
-        <v>349</v>
+        <v>300</v>
       </c>
       <c r="S71" t="s">
-        <v>424</v>
+        <v>373</v>
       </c>
       <c r="T71" s="1">
         <v>46071</v>
@@ -7158,10 +7197,10 @@
         <v>60</v>
       </c>
       <c r="V71" t="s">
-        <v>551</v>
+        <v>498</v>
       </c>
       <c r="W71" t="s">
-        <v>510</v>
+        <v>458</v>
       </c>
       <c r="X71">
         <v>100</v>
@@ -7170,63 +7209,63 @@
         <v>46071</v>
       </c>
       <c r="Z71" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="72" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>542</v>
+        <v>489</v>
       </c>
       <c r="B72" t="s">
-        <v>545</v>
+        <v>492</v>
       </c>
       <c r="C72" t="s">
-        <v>546</v>
+        <v>493</v>
       </c>
       <c r="D72" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="E72" t="s">
-        <v>552</v>
+        <v>499</v>
       </c>
       <c r="F72" t="s">
-        <v>350</v>
+        <v>301</v>
       </c>
       <c r="G72" t="s">
-        <v>395</v>
+        <v>346</v>
       </c>
       <c r="H72" t="s">
-        <v>553</v>
+        <v>500</v>
       </c>
       <c r="I72" t="s">
-        <v>554</v>
+        <v>501</v>
       </c>
       <c r="J72" t="s">
-        <v>555</v>
+        <v>502</v>
       </c>
       <c r="K72" t="s">
-        <v>556</v>
+        <v>503</v>
       </c>
       <c r="L72" t="s">
-        <v>345</v>
+        <v>296</v>
       </c>
       <c r="M72" t="s">
-        <v>548</v>
+        <v>495</v>
       </c>
       <c r="O72">
         <v>47</v>
       </c>
       <c r="P72" t="s">
-        <v>547</v>
+        <v>494</v>
       </c>
       <c r="Q72" t="s">
-        <v>133</v>
+        <v>110</v>
       </c>
       <c r="R72" t="s">
-        <v>349</v>
+        <v>300</v>
       </c>
       <c r="S72" t="s">
-        <v>424</v>
+        <v>373</v>
       </c>
       <c r="T72" s="1">
         <v>46071</v>
@@ -7235,10 +7274,10 @@
         <v>60</v>
       </c>
       <c r="V72" t="s">
-        <v>557</v>
+        <v>504</v>
       </c>
       <c r="W72" t="s">
-        <v>510</v>
+        <v>458</v>
       </c>
       <c r="X72">
         <v>90</v>
@@ -7247,7 +7286,7 @@
         <v>46071</v>
       </c>
       <c r="Z72" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/Coleccion de minerales.xlsx
+++ b/Coleccion de minerales.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Mi Colección de Minerales\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Colección Minerales\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C5C977D-9FD8-452F-A55E-4761129B7E70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{058A903D-CF89-41A7-81CC-A119283C3027}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1334" uniqueCount="570">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1353" uniqueCount="575">
   <si>
     <t>Mineral</t>
   </si>
@@ -1865,6 +1865,21 @@
   </si>
   <si>
     <t>Mineral principal: Galena (cristales cúbicos, gris plomo, alto brillo metálico). Asociación: Pirita bien cristalizada (micro a pequeños cubos dorados). Presentación: pieza “escultural”, vertical.</t>
+  </si>
+  <si>
+    <t>M-072</t>
+  </si>
+  <si>
+    <t>590x300x440</t>
+  </si>
+  <si>
+    <t>Pentagonodecaédrico</t>
+  </si>
+  <si>
+    <t>Octaédrico</t>
+  </si>
+  <si>
+    <t>Agrupación compacta de cristales cúbicos y octaédricos, con desarrollo escalonado y fuerte predominio de caras bien definidas. Presenta brillo metálico muy intenso y color amarillo latón profundo, característico de la pirita de Huanzala. Las superficies muestran excelente reflectividad, con aristas nítidas y hábitos cristalinos robustos. Se observan leves contactos y pequeñas imperfecciones menores propias del crecimiento en matriz, sin comprometer la calidad estética global del conjunto.</t>
   </si>
 </sst>
 </file>
@@ -2318,7 +2333,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z72"/>
+  <dimension ref="A1:Z73"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
@@ -2331,7 +2346,7 @@
     <col min="9" max="10" width="13.140625" customWidth="1"/>
     <col min="11" max="11" width="37.140625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.140625" customWidth="1"/>
     <col min="14" max="14" width="10.5703125" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="44.85546875" customWidth="1"/>
     <col min="17" max="17" width="11.28515625" bestFit="1" customWidth="1"/>
@@ -2829,7 +2844,7 @@
         <v>345</v>
       </c>
       <c r="F8" t="s">
-        <v>301</v>
+        <v>572</v>
       </c>
       <c r="G8" t="s">
         <v>346</v>
@@ -7286,6 +7301,80 @@
         <v>46071</v>
       </c>
       <c r="Z72" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="73" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A73" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="B73" t="s">
+        <v>24</v>
+      </c>
+      <c r="C73" t="s">
+        <v>374</v>
+      </c>
+      <c r="E73" t="s">
+        <v>345</v>
+      </c>
+      <c r="F73" t="s">
+        <v>573</v>
+      </c>
+      <c r="G73" t="s">
+        <v>346</v>
+      </c>
+      <c r="H73" t="s">
+        <v>347</v>
+      </c>
+      <c r="I73" t="s">
+        <v>348</v>
+      </c>
+      <c r="J73" t="s">
+        <v>305</v>
+      </c>
+      <c r="K73" t="s">
+        <v>332</v>
+      </c>
+      <c r="L73" t="s">
+        <v>296</v>
+      </c>
+      <c r="M73" t="s">
+        <v>571</v>
+      </c>
+      <c r="O73">
+        <v>138</v>
+      </c>
+      <c r="P73" t="s">
+        <v>212</v>
+      </c>
+      <c r="Q73" t="s">
+        <v>28</v>
+      </c>
+      <c r="R73" t="s">
+        <v>300</v>
+      </c>
+      <c r="S73" t="s">
+        <v>373</v>
+      </c>
+      <c r="T73" s="6">
+        <v>46133</v>
+      </c>
+      <c r="U73">
+        <v>40</v>
+      </c>
+      <c r="V73" t="s">
+        <v>574</v>
+      </c>
+      <c r="W73" t="s">
+        <v>458</v>
+      </c>
+      <c r="X73">
+        <v>100</v>
+      </c>
+      <c r="Y73" s="6">
+        <v>46133</v>
+      </c>
+      <c r="Z73" t="s">
         <v>12</v>
       </c>
     </row>

--- a/Coleccion de minerales.xlsx
+++ b/Coleccion de minerales.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Colección Minerales\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{058A903D-CF89-41A7-81CC-A119283C3027}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCDC0287-D640-4AA6-A656-EA82535B2BB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1870,9 +1870,6 @@
     <t>M-072</t>
   </si>
   <si>
-    <t>590x300x440</t>
-  </si>
-  <si>
     <t>Pentagonodecaédrico</t>
   </si>
   <si>
@@ -1880,6 +1877,9 @@
   </si>
   <si>
     <t>Agrupación compacta de cristales cúbicos y octaédricos, con desarrollo escalonado y fuerte predominio de caras bien definidas. Presenta brillo metálico muy intenso y color amarillo latón profundo, característico de la pirita de Huanzala. Las superficies muestran excelente reflectividad, con aristas nítidas y hábitos cristalinos robustos. Se observan leves contactos y pequeñas imperfecciones menores propias del crecimiento en matriz, sin comprometer la calidad estética global del conjunto.</t>
+  </si>
+  <si>
+    <t>59x30x44</t>
   </si>
 </sst>
 </file>
@@ -2844,7 +2844,7 @@
         <v>345</v>
       </c>
       <c r="F8" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="G8" t="s">
         <v>346</v>
@@ -7318,7 +7318,7 @@
         <v>345</v>
       </c>
       <c r="F73" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="G73" t="s">
         <v>346</v>
@@ -7339,7 +7339,7 @@
         <v>296</v>
       </c>
       <c r="M73" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="O73">
         <v>138</v>
@@ -7363,7 +7363,7 @@
         <v>40</v>
       </c>
       <c r="V73" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="W73" t="s">
         <v>458</v>
